--- a/Assets/GameData/database.xlsx
+++ b/Assets/GameData/database.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="1078">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -794,739 +794,767 @@
     <t xml:space="preserve">enemy.Boss.description</t>
   </si>
   <si>
+    <t xml:space="preserve">Take fate into your own hands before the final countdown.</t>
+  </si>
+  <si>
     <t xml:space="preserve">在最后的倒计时前，掌握你自己的命运吧。</t>
   </si>
   <si>
-    <t xml:space="preserve">battle.roll.fate_prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是否决定{0}的命运？</t>
+    <t xml:space="preserve">最後のカウントダウンが始まる前に、自らの運命をその手に。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.roll.health_range_with_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}
+Roll {1}’s fate?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}
+是否要决定{1}的命运？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}
+{1}の運命を書き換えますか？</t>
   </si>
   <si>
     <t xml:space="preserve">battle.roll.button.roll</t>
   </si>
   <si>
-    <t xml:space="preserve">是</t>
+    <t xml:space="preserve">Yes
+Enemy HP will be randomized in this range: {0}–{1}
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是
+敌方血量会在{0}～{1}内随机取值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">はい
+敵のHPは{0}～{1}内でランダムに決まります。</t>
   </si>
   <si>
     <t xml:space="preserve">enemy.intent.escape_with</t>
   </si>
   <si>
-    <t xml:space="preserve">battle.roll.random_hint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敌方血量会在区间内随机取值</t>
+    <t xml:space="preserve">battle.roll.button.stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No
+Enemy HP will remain at {0}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">否
+敌方血量为 {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いいえ
+敵のHPは {0} のままです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.intent.peck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.roll.resolved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}’s HP is {1}. Good luck.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}的血量为{1}，祝你好运。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{0}のHPは{1}です。幸運を。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">填写范例：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗界面（玩家）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.player.skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.basic_attack.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">下劈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English: Intent: Attack -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.basic_attack.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗1点，对敌方造成3点伤害。冷却：0回合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chinese: 意图：攻击 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.bloodlust.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloodletting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">喋血</t>
+  </si>
+  <si>
+    <t xml:space="preserve">血戦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Japanese: 予告：攻撃 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.bloodlust.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The next 2 basic attacks deal 100% more damage. Additive item bonuses are applied before the multiplier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗1点，后两次下劈的伤害增加100%。\n冷却：2回合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次の通常攻撃2回のダメージが100%増加。\nアイテム等の加算後に倍率を適用。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.parasite.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parasite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寄生</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.parasite.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deal 6 damage. If this attack kills the enemy, restore 3 number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗4点，对敌方造成6点伤害。若此次攻击击败敌方，则额外回复3点。冷却：2回合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6ダメージ。この攻撃で敵を倒すと数字を3回復。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.revenge.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">复仇</t>
+  </si>
+  <si>
+    <t xml:space="preserve">復讐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.revenge.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attack 2–3 times for 4 damage each; 50% chance to attack 3 times.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗 3 点，对敌方连续攻击 2～3 次，每次造成 4 点伤害。冷却：3 回合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4ダメージで2～3回攻撃。50%の確率で3回攻撃。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.defense.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">防御</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill.defense.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">消耗 1 点，减免受到伤害的 45%。冷却：0 回合。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.player.items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">道具</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.player.button.back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">返回</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.wrench.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wrench</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扳手</t>
+  </si>
+  <si>
+    <t xml:space="preserve">レンチ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.wrench.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For the next 3 player actions, base attack +2. Stacks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接下来 3 次玩家行动中，下劈伤害 +2。可叠加。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次のプレイヤー行動3回、基礎攻撃力+2。重複可。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.girls_thoughts.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Girl's Thoughts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少女的心事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少女の想い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.girls_thoughts.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takes the next monster attack for you. Does not stack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">替你承受一次攻击后销毁。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次の敵攻撃を代わりに受ける。重複不可。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.guardian_shield.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guardian Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守护者之盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守護者の盾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.guardian_shield.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gain 6 shield for the next enemy phase. Does not stack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">增加6点护盾。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">次の敵フェーズにシールド6。重複不可。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.magic_potion.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic Potion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔药</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔法の薬</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.magic_potion.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immediately restore 6 number, up to the maximum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回复6点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字を即座に6回復。上限を超えない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.player.relics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">信物</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.lucky_coin.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lucky Coin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幸运硬币</t>
+  </si>
+  <si>
+    <t xml:space="preserve">幸運のコイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.lucky_coin.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each coin raises the first Greed success chance by 10%. Hold up to 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首次贪婪成功率增加 10%，最多持有 2 个。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1つにつき最初の欲張り成功率+10%。最大2つ。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.hungry_wolf.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hungry Wolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">饿狼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">飢えた狼</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.hungry_wolf.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changes the successful Greed multiplier from 2.5× to 3.5×.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贪婪成功时获得的奖励倍率变为 3.5 倍。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欲張り成功倍率を2.5倍から3.5倍に変更。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.broken_mirror.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broken Mirror</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破碎的镜子</t>
+  </si>
+  <si>
+    <t xml:space="preserve">割れた鏡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collectible.broken_mirror.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After the first successful Greed, you may continue. Extra success chances are 40%/30%/20%/10%; each gain is resolved independently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">首次贪婪成功后可再次贪婪；追加成功率依次为 40%/30%/20%/10%，每次收益独立结算。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最初の欲張り成功後も継続可能。追加成功率は40%/30%/20%/10%、各報酬は個別に精算。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗界面（怪物）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.SmallChicken.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluffy Chick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小绒鸡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふわふわヒヨコ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.DrunkenRaider.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clockwork Raider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">发条油掠夺者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ぜんまい略奪者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.HorrorBox.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horror Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">惊魂匣</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恐怖の箱</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.Hamster.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubby Hamster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鼓鼓仓鼠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ふっくらハムスター</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enemy.Boss.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哀叹之钟</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战斗结算面板</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你击败了{0}，是否进行贪婪检定？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.additional_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你成功了，就此收手，还是再赌一把？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.button.greedy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">贪婪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.greedy_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50% 概率获得 2.5 倍数字；50% 概率失去本轮全部数字收获（保留道具）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.button.safe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">见好就收</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.safe_description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">稳定获得奖励点数的 100%。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.button.again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再赌一把</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.mirror_hint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破碎的镜子给予你机会</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.result.success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检定成功，恭喜你，幸运之人。你获得了{0}点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.reward.result.failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检定失败，真可惜，你一无所有。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事件：获得物品</t>
+  </si>
+  <si>
+    <t xml:space="preserve">treasure.received_kind</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真幸运，你获得了{0}{1}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0：技能/道具/信物 1：具体是什么</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事件：交换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange.prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否用你拥有的道具换取另一个道具？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange.button.confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交换</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange.button.leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">离开</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange.result.success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以物易物，很划算吧。{0}属于你了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange.result.no_items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真遗憾，你没有足够的道具和我交换。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">事件：供奉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choose how much number to offer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是否为了信仰或回报，划动发条，献上你的祭品？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">捧げる数字を選んでください</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.button.confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">供奉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.button.leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.result.no_blessing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很可惜，你似乎并没有被赐福。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.result.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神的眷顾，你获得了{0}个道具{1}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.result.number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神的眷顾，你获得了{0}点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.result.return</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The altar returned {0} number.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">神似乎拒绝了你，返还了你{0}点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">祭壇から数字{0}が返されました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">offering.feedback.insufficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字不足，当前无法供奉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">休整</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rest.result.restore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">沐浴在神秘的力量下，你回复了{0}点。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商店</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.greeting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用你最宝贵的数字换取这些小玩意，很不错，不是吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.button.buy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">购买</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.button.leave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.state.sold_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">售罄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.button.sold_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已售罄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.number_preview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字：{0} → {1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.feedback.purchase_success</t>
+  </si>
+  <si>
+    <t xml:space="preserve">购买成功</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.feedback.sold_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这件商品已经售罄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shop.feedback.insufficient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数字不足，当前无法购买</t>
+  </si>
+  <si>
+    <t xml:space="preserve">胜利通关</t>
+  </si>
+  <si>
+    <t xml:space="preserve">game_over.reason.victory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You saved everyone beneath the ceaseless tolling of the clock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">恭喜你，在不断倒数的钟声里拯救了所有人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">鳴り続ける鐘の中で、あなたはすべての人を救った。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">失败</t>
+  </si>
+  <si>
+    <t xml:space="preserve">game_over.title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defeat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你死了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敗北</t>
+  </si>
+  <si>
+    <t xml:space="preserve">game_over.reason.default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">倒数的秒针追上了你，你再一次坠入了无尽的深渊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Attack -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：攻击 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：攻撃 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：蓄力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：チャージ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Heavy Attack -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：强力击 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：強攻撃 -{0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Steal Item (none: -{0} and Stun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：偷取道具（无道具：-{0}并眩晕）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：アイテムを盗む（所持なし：-{0}＋スタン）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Wait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：等待</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：待機</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Drink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：喝酒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：酒を飲む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intent: Escape with {0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">意图：携带 {0} 点逃跑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">予告：{0}を持って逃走</t>
   </si>
   <si>
     <t xml:space="preserve">enemy.intent.steal_number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.roll.button.stable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">否</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.intent.peck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.roll.stable_hint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敌方血量为区间中位数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.roll.resolved</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0}的血量为{1}，祝你好运。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">填写范例：</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战斗界面（玩家）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.player.skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">技能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.basic_attack.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">下劈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">English: Intent: Attack -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.basic_attack.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗1点，对敌方造成3点伤害。冷却：0回合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chinese: 意图：攻击 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.bloodlust.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bloodletting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">喋血</t>
-  </si>
-  <si>
-    <t xml:space="preserve">血戦</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Japanese: 予告：攻撃 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.bloodlust.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The next 2 basic attacks deal 100% more damage. Additive item bonuses are applied before the multiplier.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗1点，后两次下劈的伤害增加100%。\n冷却：2回合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">次の通常攻撃2回のダメージが100%増加。\nアイテム等の加算後に倍率を適用。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.parasite.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parasite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">寄生</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.parasite.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deal 6 damage. If this attack kills the enemy, restore 3 number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗4点，对敌方造成6点伤害。若此次攻击击败敌方，则额外回复3点。冷却：2回合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6ダメージ。この攻撃で敵を倒すと数字を3回復。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.revenge.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">复仇</t>
-  </si>
-  <si>
-    <t xml:space="preserve">復讐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.revenge.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Attack 2–3 times for 4 damage each; 50% chance to attack 3 times.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗 3 点，对敌方连续攻击 2～3 次，每次造成 4 点伤害。冷却：3 回合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4ダメージで2～3回攻撃。50%の確率で3回攻撃。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.defense.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">防御</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill.defense.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">消耗 1 点，减免受到伤害的 45%。冷却：0 回合。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.player.items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">道具</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.player.button.back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">返回</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.wrench.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wrench</t>
-  </si>
-  <si>
-    <t xml:space="preserve">扳手</t>
-  </si>
-  <si>
-    <t xml:space="preserve">レンチ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.wrench.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For the next 3 player actions, base attack +2. Stacks.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接下来 3 次玩家行动中，下劈伤害 +2。可叠加。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">次のプレイヤー行動3回、基礎攻撃力+2。重複可。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.girls_thoughts.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Girl's Thoughts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">少女的心事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">少女の想い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.girls_thoughts.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Takes the next monster attack for you. Does not stack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">替你承受一次攻击后销毁。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">次の敵攻撃を代わりに受ける。重複不可。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.guardian_shield.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardian Shield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">守护者之盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">守護者の盾</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.guardian_shield.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gain 6 shield for the next enemy phase. Does not stack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">增加6点护盾。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">次の敵フェーズにシールド6。重複不可。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.magic_potion.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic Potion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔药</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔法の薬</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.magic_potion.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immediately restore 6 number, up to the maximum.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回复6点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数字を即座に6回復。上限を超えない。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.player.relics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">信物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.lucky_coin.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lucky Coin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">幸运硬币</t>
-  </si>
-  <si>
-    <t xml:space="preserve">幸運のコイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.lucky_coin.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each coin raises the first Greed success chance by 10%. Hold up to 2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">首次贪婪成功率增加 10%，最多持有 2 个。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1つにつき最初の欲張り成功率+10%。最大2つ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.hungry_wolf.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hungry Wolf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">饿狼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">飢えた狼</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.hungry_wolf.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changes the successful Greed multiplier from 2.5× to 3.5×.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贪婪成功时获得的奖励倍率变为 3.5 倍。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欲張り成功倍率を2.5倍から3.5倍に変更。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.broken_mirror.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broken Mirror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">破碎的镜子</t>
-  </si>
-  <si>
-    <t xml:space="preserve">割れた鏡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">collectible.broken_mirror.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After the first successful Greed, you may continue. Extra success chances are 40%/30%/20%/10%; each gain is resolved independently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">首次贪婪成功后可再次贪婪；追加成功率依次为 40%/30%/20%/10%，每次收益独立结算。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最初の欲張り成功後も継続可能。追加成功率は40%/30%/20%/10%、各報酬は個別に精算。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战斗界面（怪物）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.SmallChicken.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluffy Chick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">小绒鸡</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふわふわヒヨコ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.DrunkenRaider.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clockwork Raider</t>
-  </si>
-  <si>
-    <t xml:space="preserve">发条油掠夺者</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ぜんまい略奪者</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.HorrorBox.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Horror Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">惊魂匣</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恐怖の箱</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.Hamster.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubby Hamster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鼓鼓仓鼠</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ふっくらハムスター</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enemy.Boss.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哀叹之钟</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战斗结算面板</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你击败了{0}，是否进行贪婪检定？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.additional_prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你成功了，就此收手，还是再赌一把？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.button.greedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">贪婪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.greedy_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50% 概率获得 2.5 倍数字；50% 概率失去本轮全部数字收获（保留道具）。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.button.safe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">见好就收</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.safe_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">稳定获得奖励点数的 100%。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.button.again</t>
-  </si>
-  <si>
-    <t xml:space="preserve">再赌一把</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.mirror_hint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">破碎的镜子给予你机会</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.result.success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检定成功，恭喜你，幸运之人。你获得了{0}点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.reward.result.failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检定失败，真可惜，你一无所有。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事件：获得物品</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treasure.received_kind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真幸运，你获得了{0}{1}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0：技能/道具/信物 1：具体是什么</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事件：交换</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exchange.prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是否用你拥有的道具换取另一个道具？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exchange.button.confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">交换</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exchange.button.leave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">离开</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exchange.result.success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以物易物，很划算吧。{0}属于你了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exchange.result.no_items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真遗憾，你没有足够的道具和我交换。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">事件：供奉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.prompt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choose how much number to offer.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是否为了信仰或回报，划动发条，献上你的祭品？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">捧げる数字を選んでください</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.button.confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">供奉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.button.leave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.result.no_blessing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很可惜，你似乎并没有被赐福。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.result.item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神的眷顾，你获得了{0}个道具{1}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.result.number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神的眷顾，你获得了{0}点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.result.return</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The altar returned {0} number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">神似乎拒绝了你，返还了你{0}点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">祭壇から数字{0}が返されました</t>
-  </si>
-  <si>
-    <t xml:space="preserve">offering.feedback.insufficient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数字不足，当前无法供奉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">休整</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rest.result.restore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">沐浴在神秘的力量下，你回复了{0}点。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商店</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.greeting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用你最宝贵的数字换取这些小玩意，很不错，不是吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.button.buy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">购买</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.button.leave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.state.sold_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">售罄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.button.sold_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已售罄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.number_preview</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数字：{0} → {1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.feedback.purchase_success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">购买成功</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.feedback.sold_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这件商品已经售罄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shop.feedback.insufficient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数字不足，当前无法购买</t>
-  </si>
-  <si>
-    <t xml:space="preserve">胜利通关</t>
-  </si>
-  <si>
-    <t xml:space="preserve">game_over.reason.victory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">You saved everyone beneath the ceaseless tolling of the clock.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">恭喜你，在不断倒数的钟声里拯救了所有人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鳴り続ける鐘の中で、あなたはすべての人を救った。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">失败</t>
-  </si>
-  <si>
-    <t xml:space="preserve">game_over.title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Defeat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你死了</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敗北</t>
-  </si>
-  <si>
-    <t xml:space="preserve">game_over.reason.default</t>
-  </si>
-  <si>
-    <t xml:space="preserve">倒数的秒针追上了你，你再一次坠入了无尽的深渊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Attack -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：攻击 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：攻撃 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Charge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：蓄力</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：チャージ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Heavy Attack -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：强力击 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：強攻撃 -{0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Steal Item (none: -{0} and Stun)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：偷取道具（无道具：-{0}并眩晕）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：アイテムを盗む（所持なし：-{0}＋スタン）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Wait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：等待</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：待機</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Drink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：喝酒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：酒を飲む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intent: Escape with {0}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">意图：携带 {0} 点逃跑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">予告：{0}を持って逃走</t>
   </si>
   <si>
     <t xml:space="preserve">Intent: Steal {0}</t>
@@ -1781,21 +1809,6 @@
   </si>
   <si>
     <t xml:space="preserve">HP範囲：{0}～{1}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">battle.roll.health_range_with_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0}
- Enemy health is randomized in this range: {1}–{2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0}
- 敌方血量会在区间内随机取值：{1}～{2}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{0}
- 敵のHPは範囲内でランダム：{1}～{2}</t>
   </si>
   <si>
     <t xml:space="preserve">battle.roll.reward</t>
@@ -3496,7 +3509,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3670,6 +3683,9 @@
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
@@ -6686,11 +6702,15 @@
       <c r="A17" s="57" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="50"/>
+      <c r="B17" s="58" t="s">
+        <v>248</v>
+      </c>
       <c r="C17" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="D17" s="50"/>
+        <v>249</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>250</v>
+      </c>
       <c r="E17" s="51"/>
       <c r="F17" s="51"/>
       <c r="G17" s="51"/>
@@ -6708,15 +6728,19 @@
       <c r="S17" s="51"/>
       <c r="T17" s="51"/>
     </row>
-    <row r="18">
+    <row customHeight="true" ht="60" r="18">
       <c r="A18" s="57" t="s">
-        <v>249</v>
-      </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="50"/>
+        <v>251</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="C18" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>254</v>
+      </c>
       <c r="E18" s="51"/>
       <c r="F18" s="51"/>
       <c r="G18" s="51"/>
@@ -6736,16 +6760,20 @@
     </row>
     <row r="19">
       <c r="A19" s="57" t="s">
-        <v>251</v>
-      </c>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="D19" s="50"/>
+        <v>255</v>
+      </c>
+      <c r="B19" s="59" t="s">
+        <v>256</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>258</v>
+      </c>
       <c r="E19" s="51"/>
       <c r="F19" s="51" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
@@ -6764,16 +6792,20 @@
     </row>
     <row r="20">
       <c r="A20" s="57" t="s">
-        <v>254</v>
-      </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50" t="s">
-        <v>255</v>
-      </c>
-      <c r="D20" s="50"/>
+        <v>260</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>263</v>
+      </c>
       <c r="E20" s="51"/>
       <c r="F20" s="51" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G20" s="51"/>
       <c r="H20" s="51"/>
@@ -6791,17 +6823,21 @@
       <c r="T20" s="51"/>
     </row>
     <row r="21">
-      <c r="A21" s="57" t="s">
-        <v>257</v>
-      </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50" t="s">
-        <v>258</v>
-      </c>
-      <c r="D21" s="50"/>
+      <c r="A21" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="B21" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="54" t="s">
+        <v>268</v>
+      </c>
       <c r="E21" s="51"/>
       <c r="F21" s="51" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
@@ -6819,44 +6855,40 @@
       <c r="T21" s="51"/>
     </row>
     <row r="22">
-      <c r="A22" s="57" t="s">
-        <v>260</v>
-      </c>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="51"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-      <c r="L22" s="51"/>
-      <c r="M22" s="51"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
+      <c r="A22" s="48"/>
+      <c r="B22" s="56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="49"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="49"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="49"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="s">
-        <v>262</v>
-      </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55" t="s">
-        <v>263</v>
-      </c>
-      <c r="D23" s="55"/>
+      <c r="A23" s="57" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" s="50"/>
       <c r="E23" s="51"/>
-      <c r="F23" s="51" t="s">
-        <v>264</v>
-      </c>
+      <c r="F23" s="51"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="51"/>
@@ -6873,40 +6905,46 @@
       <c r="T23" s="51"/>
     </row>
     <row r="24">
-      <c r="A24" s="48"/>
-      <c r="B24" s="56" t="s">
-        <v>265</v>
-      </c>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="49"/>
-      <c r="L24" s="49"/>
-      <c r="M24" s="49"/>
-      <c r="N24" s="49"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="49"/>
-      <c r="Q24" s="49"/>
-      <c r="R24" s="49"/>
-      <c r="S24" s="49"/>
-      <c r="T24" s="49"/>
+      <c r="A24" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50" t="s">
+        <v>274</v>
+      </c>
+      <c r="D24" s="50"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="51"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="51"/>
+      <c r="R24" s="51"/>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51"/>
     </row>
     <row r="25">
       <c r="A25" s="57" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B25" s="50"/>
       <c r="C25" s="50" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="D25" s="50"/>
       <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
+      <c r="F25" s="51" t="s">
+        <v>278</v>
+      </c>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
       <c r="I25" s="51"/>
@@ -6924,16 +6962,20 @@
     </row>
     <row r="26">
       <c r="A26" s="57" t="s">
-        <v>268</v>
-      </c>
-      <c r="B26" s="50"/>
+        <v>279</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>280</v>
+      </c>
       <c r="C26" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26" s="50"/>
+        <v>281</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>282</v>
+      </c>
       <c r="E26" s="51"/>
       <c r="F26" s="51" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
@@ -6952,17 +6994,19 @@
     </row>
     <row r="27">
       <c r="A27" s="57" t="s">
-        <v>271</v>
-      </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51" t="s">
-        <v>273</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="B27" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>287</v>
+      </c>
+      <c r="E27" s="60"/>
+      <c r="F27" s="51"/>
       <c r="G27" s="51"/>
       <c r="H27" s="51"/>
       <c r="I27" s="51"/>
@@ -6980,21 +7024,19 @@
     </row>
     <row r="28">
       <c r="A28" s="57" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51" t="s">
-        <v>278</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="E28" s="60"/>
+      <c r="F28" s="51"/>
       <c r="G28" s="51"/>
       <c r="H28" s="51"/>
       <c r="I28" s="51"/>
@@ -7012,18 +7054,18 @@
     </row>
     <row r="29">
       <c r="A29" s="57" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>280</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>281</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="59"/>
+        <v>292</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="E29" s="60"/>
       <c r="F29" s="51"/>
       <c r="G29" s="51"/>
       <c r="H29" s="51"/>
@@ -7042,18 +7084,18 @@
     </row>
     <row r="30">
       <c r="A30" s="57" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="B30" s="50" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="D30" s="50" t="s">
-        <v>285</v>
-      </c>
-      <c r="E30" s="59"/>
+        <v>298</v>
+      </c>
+      <c r="E30" s="51"/>
       <c r="F30" s="51"/>
       <c r="G30" s="51"/>
       <c r="H30" s="51"/>
@@ -7072,18 +7114,18 @@
     </row>
     <row r="31">
       <c r="A31" s="57" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B31" s="50" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C31" s="50" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>289</v>
-      </c>
-      <c r="E31" s="59"/>
+        <v>302</v>
+      </c>
+      <c r="E31" s="60"/>
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
@@ -7102,650 +7144,650 @@
     </row>
     <row r="32">
       <c r="A32" s="57" t="s">
-        <v>290</v>
-      </c>
-      <c r="B32" s="50" t="s">
-        <v>291</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="B32" s="50"/>
       <c r="C32" s="50" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-      <c r="L32" s="51"/>
-      <c r="M32" s="51"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="51"/>
-      <c r="T32" s="51"/>
+        <v>304</v>
+      </c>
+      <c r="D32" s="50"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
     </row>
     <row r="33">
       <c r="A33" s="57" t="s">
-        <v>294</v>
-      </c>
-      <c r="B33" s="50" t="s">
-        <v>295</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="B33" s="50"/>
       <c r="C33" s="50" t="s">
-        <v>296</v>
-      </c>
-      <c r="D33" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="E33" s="59"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-      <c r="L33" s="51"/>
-      <c r="M33" s="51"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="51"/>
-      <c r="T33" s="51"/>
+        <v>306</v>
+      </c>
+      <c r="D33" s="50"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
+      <c r="J33" s="60"/>
+      <c r="K33" s="60"/>
+      <c r="L33" s="60"/>
+      <c r="M33" s="60"/>
+      <c r="N33" s="60"/>
+      <c r="O33" s="60"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="60"/>
+      <c r="R33" s="60"/>
+      <c r="S33" s="60"/>
+      <c r="T33" s="60"/>
     </row>
     <row r="34">
       <c r="A34" s="57" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B34" s="50"/>
       <c r="C34" s="50" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="D34" s="50"/>
-      <c r="E34" s="59"/>
-      <c r="F34" s="59"/>
-      <c r="G34" s="59"/>
-      <c r="H34" s="59"/>
-      <c r="I34" s="59"/>
-      <c r="J34" s="59"/>
-      <c r="K34" s="59"/>
-      <c r="L34" s="59"/>
-      <c r="M34" s="59"/>
-      <c r="N34" s="59"/>
-      <c r="O34" s="59"/>
-      <c r="P34" s="59"/>
-      <c r="Q34" s="59"/>
-      <c r="R34" s="59"/>
-      <c r="S34" s="59"/>
-      <c r="T34" s="59"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
+      <c r="J34" s="60"/>
+      <c r="K34" s="60"/>
+      <c r="L34" s="60"/>
+      <c r="M34" s="60"/>
+      <c r="N34" s="60"/>
+      <c r="O34" s="60"/>
+      <c r="P34" s="60"/>
+      <c r="Q34" s="60"/>
+      <c r="R34" s="60"/>
+      <c r="S34" s="60"/>
+      <c r="T34" s="60"/>
     </row>
     <row r="35">
       <c r="A35" s="57" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B35" s="50"/>
       <c r="C35" s="50" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D35" s="50"/>
-      <c r="E35" s="59"/>
-      <c r="F35" s="59"/>
-      <c r="G35" s="59"/>
-      <c r="H35" s="59"/>
-      <c r="I35" s="59"/>
-      <c r="J35" s="59"/>
-      <c r="K35" s="59"/>
-      <c r="L35" s="59"/>
-      <c r="M35" s="59"/>
-      <c r="N35" s="59"/>
-      <c r="O35" s="59"/>
-      <c r="P35" s="59"/>
-      <c r="Q35" s="59"/>
-      <c r="R35" s="59"/>
-      <c r="S35" s="59"/>
-      <c r="T35" s="59"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="60"/>
+      <c r="K35" s="60"/>
+      <c r="L35" s="60"/>
+      <c r="M35" s="60"/>
+      <c r="N35" s="60"/>
+      <c r="O35" s="60"/>
+      <c r="P35" s="60"/>
+      <c r="Q35" s="60"/>
+      <c r="R35" s="60"/>
+      <c r="S35" s="60"/>
+      <c r="T35" s="60"/>
     </row>
     <row r="36">
       <c r="A36" s="57" t="s">
-        <v>302</v>
-      </c>
-      <c r="B36" s="50"/>
+        <v>311</v>
+      </c>
+      <c r="B36" s="50" t="s">
+        <v>312</v>
+      </c>
       <c r="C36" s="50" t="s">
-        <v>303</v>
-      </c>
-      <c r="D36" s="50"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
-      <c r="G36" s="59"/>
-      <c r="H36" s="59"/>
-      <c r="I36" s="59"/>
-      <c r="J36" s="59"/>
-      <c r="K36" s="59"/>
-      <c r="L36" s="59"/>
-      <c r="M36" s="59"/>
-      <c r="N36" s="59"/>
-      <c r="O36" s="59"/>
-      <c r="P36" s="59"/>
-      <c r="Q36" s="59"/>
-      <c r="R36" s="59"/>
-      <c r="S36" s="59"/>
-      <c r="T36" s="59"/>
+        <v>313</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
+      <c r="J36" s="60"/>
+      <c r="K36" s="60"/>
+      <c r="L36" s="60"/>
+      <c r="M36" s="60"/>
+      <c r="N36" s="60"/>
+      <c r="O36" s="60"/>
+      <c r="P36" s="60"/>
+      <c r="Q36" s="60"/>
+      <c r="R36" s="60"/>
+      <c r="S36" s="60"/>
+      <c r="T36" s="60"/>
     </row>
     <row r="37">
-      <c r="A37" s="57" t="s">
-        <v>304</v>
-      </c>
-      <c r="B37" s="50"/>
+      <c r="A37" s="61" t="s">
+        <v>315</v>
+      </c>
+      <c r="B37" s="62" t="s">
+        <v>316</v>
+      </c>
       <c r="C37" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="D37" s="50"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="59"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="59"/>
-      <c r="M37" s="59"/>
-      <c r="N37" s="59"/>
-      <c r="O37" s="59"/>
-      <c r="P37" s="59"/>
-      <c r="Q37" s="59"/>
-      <c r="R37" s="59"/>
-      <c r="S37" s="59"/>
-      <c r="T37" s="59"/>
+        <v>317</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
+      <c r="J37" s="60"/>
+      <c r="K37" s="60"/>
+      <c r="L37" s="60"/>
+      <c r="M37" s="60"/>
+      <c r="N37" s="60"/>
+      <c r="O37" s="60"/>
+      <c r="P37" s="60"/>
+      <c r="Q37" s="60"/>
+      <c r="R37" s="60"/>
+      <c r="S37" s="60"/>
+      <c r="T37" s="60"/>
     </row>
     <row r="38">
-      <c r="A38" s="57" t="s">
-        <v>306</v>
-      </c>
-      <c r="B38" s="50" t="s">
-        <v>307</v>
+      <c r="A38" s="61" t="s">
+        <v>319</v>
+      </c>
+      <c r="B38" s="62" t="s">
+        <v>320</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="D38" s="50" t="s">
-        <v>309</v>
-      </c>
-      <c r="E38" s="59"/>
-      <c r="F38" s="59"/>
-      <c r="G38" s="59"/>
-      <c r="H38" s="59"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="59"/>
-      <c r="K38" s="59"/>
-      <c r="L38" s="59"/>
-      <c r="M38" s="59"/>
-      <c r="N38" s="59"/>
-      <c r="O38" s="59"/>
-      <c r="P38" s="59"/>
-      <c r="Q38" s="59"/>
-      <c r="R38" s="59"/>
-      <c r="S38" s="59"/>
-      <c r="T38" s="59"/>
+        <v>322</v>
+      </c>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60"/>
+      <c r="J38" s="60"/>
+      <c r="K38" s="60"/>
+      <c r="L38" s="60"/>
+      <c r="M38" s="60"/>
+      <c r="N38" s="60"/>
+      <c r="O38" s="60"/>
+      <c r="P38" s="60"/>
+      <c r="Q38" s="60"/>
+      <c r="R38" s="60"/>
+      <c r="S38" s="60"/>
+      <c r="T38" s="60"/>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="s">
-        <v>310</v>
-      </c>
-      <c r="B39" s="61" t="s">
-        <v>311</v>
+      <c r="A39" s="61" t="s">
+        <v>323</v>
+      </c>
+      <c r="B39" s="62" t="s">
+        <v>324</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>313</v>
-      </c>
-      <c r="E39" s="59"/>
-      <c r="F39" s="59"/>
-      <c r="G39" s="59"/>
-      <c r="H39" s="59"/>
-      <c r="I39" s="59"/>
-      <c r="J39" s="59"/>
-      <c r="K39" s="59"/>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59"/>
-      <c r="O39" s="59"/>
-      <c r="P39" s="59"/>
-      <c r="Q39" s="59"/>
-      <c r="R39" s="59"/>
-      <c r="S39" s="59"/>
-      <c r="T39" s="59"/>
+        <v>326</v>
+      </c>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
+      <c r="K39" s="60"/>
+      <c r="L39" s="60"/>
+      <c r="M39" s="60"/>
+      <c r="N39" s="60"/>
+      <c r="O39" s="60"/>
+      <c r="P39" s="60"/>
+      <c r="Q39" s="60"/>
+      <c r="R39" s="60"/>
+      <c r="S39" s="60"/>
+      <c r="T39" s="60"/>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" s="61" t="s">
-        <v>315</v>
+      <c r="A40" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="B40" s="62" t="s">
+        <v>328</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="D40" s="50" t="s">
-        <v>317</v>
-      </c>
-      <c r="E40" s="59"/>
-      <c r="F40" s="59"/>
-      <c r="G40" s="59"/>
-      <c r="H40" s="59"/>
-      <c r="I40" s="59"/>
-      <c r="J40" s="59"/>
-      <c r="K40" s="59"/>
-      <c r="L40" s="59"/>
-      <c r="M40" s="59"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="59"/>
-      <c r="P40" s="59"/>
-      <c r="Q40" s="59"/>
-      <c r="R40" s="59"/>
-      <c r="S40" s="59"/>
-      <c r="T40" s="59"/>
+        <v>330</v>
+      </c>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="60"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+      <c r="R40" s="60"/>
+      <c r="S40" s="60"/>
+      <c r="T40" s="60"/>
     </row>
     <row r="41">
-      <c r="A41" s="60" t="s">
-        <v>318</v>
-      </c>
-      <c r="B41" s="61" t="s">
-        <v>319</v>
+      <c r="A41" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="B41" s="62" t="s">
+        <v>332</v>
       </c>
       <c r="C41" s="50" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="D41" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="E41" s="59"/>
-      <c r="F41" s="59"/>
-      <c r="G41" s="59"/>
-      <c r="H41" s="59"/>
-      <c r="I41" s="59"/>
-      <c r="J41" s="59"/>
-      <c r="K41" s="59"/>
-      <c r="L41" s="59"/>
-      <c r="M41" s="59"/>
-      <c r="N41" s="59"/>
-      <c r="O41" s="59"/>
-      <c r="P41" s="59"/>
-      <c r="Q41" s="59"/>
-      <c r="R41" s="59"/>
-      <c r="S41" s="59"/>
-      <c r="T41" s="59"/>
+        <v>334</v>
+      </c>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
     </row>
     <row r="42">
-      <c r="A42" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="B42" s="61" t="s">
-        <v>323</v>
+      <c r="A42" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="B42" s="62" t="s">
+        <v>336</v>
       </c>
       <c r="C42" s="50" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="D42" s="50" t="s">
-        <v>325</v>
-      </c>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="59"/>
-      <c r="H42" s="59"/>
-      <c r="I42" s="59"/>
-      <c r="J42" s="59"/>
-      <c r="K42" s="59"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="59"/>
-      <c r="O42" s="59"/>
-      <c r="P42" s="59"/>
-      <c r="Q42" s="59"/>
-      <c r="R42" s="59"/>
-      <c r="S42" s="59"/>
-      <c r="T42" s="59"/>
+        <v>338</v>
+      </c>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
+      <c r="J42" s="60"/>
+      <c r="K42" s="60"/>
+      <c r="L42" s="60"/>
+      <c r="M42" s="60"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="60"/>
+      <c r="P42" s="60"/>
+      <c r="Q42" s="60"/>
+      <c r="R42" s="60"/>
+      <c r="S42" s="60"/>
+      <c r="T42" s="60"/>
     </row>
     <row r="43">
       <c r="A43" s="57" t="s">
-        <v>326</v>
-      </c>
-      <c r="B43" s="61" t="s">
-        <v>327</v>
+        <v>339</v>
+      </c>
+      <c r="B43" s="50" t="s">
+        <v>340</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="D43" s="50" t="s">
-        <v>329</v>
-      </c>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
-      <c r="J43" s="59"/>
-      <c r="K43" s="59"/>
-      <c r="L43" s="59"/>
-      <c r="M43" s="59"/>
-      <c r="N43" s="59"/>
-      <c r="O43" s="59"/>
-      <c r="P43" s="59"/>
-      <c r="Q43" s="59"/>
-      <c r="R43" s="59"/>
-      <c r="S43" s="59"/>
-      <c r="T43" s="59"/>
+        <v>342</v>
+      </c>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+      <c r="R43" s="60"/>
+      <c r="S43" s="60"/>
+      <c r="T43" s="60"/>
     </row>
     <row r="44">
       <c r="A44" s="57" t="s">
-        <v>330</v>
-      </c>
-      <c r="B44" s="61" t="s">
-        <v>331</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="B44" s="62"/>
       <c r="C44" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="D44" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="59"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="59"/>
-      <c r="J44" s="59"/>
-      <c r="K44" s="59"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="59"/>
-      <c r="O44" s="59"/>
-      <c r="P44" s="59"/>
-      <c r="Q44" s="59"/>
-      <c r="R44" s="59"/>
-      <c r="S44" s="59"/>
-      <c r="T44" s="59"/>
+        <v>344</v>
+      </c>
+      <c r="D44" s="50"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="60"/>
+      <c r="J44" s="60"/>
+      <c r="K44" s="60"/>
+      <c r="L44" s="60"/>
+      <c r="M44" s="60"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="60"/>
+      <c r="P44" s="60"/>
+      <c r="Q44" s="60"/>
+      <c r="R44" s="60"/>
+      <c r="S44" s="60"/>
+      <c r="T44" s="60"/>
     </row>
     <row r="45">
       <c r="A45" s="57" t="s">
-        <v>334</v>
-      </c>
-      <c r="B45" s="50" t="s">
-        <v>335</v>
+        <v>345</v>
+      </c>
+      <c r="B45" s="62" t="s">
+        <v>346</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D45" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="59"/>
-      <c r="J45" s="59"/>
-      <c r="K45" s="59"/>
-      <c r="L45" s="59"/>
-      <c r="M45" s="59"/>
-      <c r="N45" s="59"/>
-      <c r="O45" s="59"/>
-      <c r="P45" s="59"/>
-      <c r="Q45" s="59"/>
-      <c r="R45" s="59"/>
-      <c r="S45" s="59"/>
-      <c r="T45" s="59"/>
+        <v>348</v>
+      </c>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="60"/>
+      <c r="J45" s="60"/>
+      <c r="K45" s="60"/>
+      <c r="L45" s="60"/>
+      <c r="M45" s="60"/>
+      <c r="N45" s="60"/>
+      <c r="O45" s="60"/>
+      <c r="P45" s="60"/>
+      <c r="Q45" s="60"/>
+      <c r="R45" s="60"/>
+      <c r="S45" s="60"/>
+      <c r="T45" s="60"/>
     </row>
     <row r="46">
       <c r="A46" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="B46" s="61"/>
+        <v>349</v>
+      </c>
+      <c r="B46" s="62" t="s">
+        <v>350</v>
+      </c>
       <c r="C46" s="50" t="s">
-        <v>339</v>
-      </c>
-      <c r="D46" s="50"/>
-      <c r="E46" s="59"/>
-      <c r="F46" s="59"/>
-      <c r="G46" s="59"/>
-      <c r="H46" s="59"/>
-      <c r="I46" s="59"/>
-      <c r="J46" s="59"/>
-      <c r="K46" s="59"/>
-      <c r="L46" s="59"/>
-      <c r="M46" s="59"/>
-      <c r="N46" s="59"/>
-      <c r="O46" s="59"/>
-      <c r="P46" s="59"/>
-      <c r="Q46" s="59"/>
-      <c r="R46" s="59"/>
-      <c r="S46" s="59"/>
-      <c r="T46" s="59"/>
+        <v>351</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>352</v>
+      </c>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="60"/>
+      <c r="J46" s="60"/>
+      <c r="K46" s="60"/>
+      <c r="L46" s="60"/>
+      <c r="M46" s="60"/>
+      <c r="N46" s="60"/>
+      <c r="O46" s="60"/>
+      <c r="P46" s="60"/>
+      <c r="Q46" s="60"/>
+      <c r="R46" s="60"/>
+      <c r="S46" s="60"/>
+      <c r="T46" s="60"/>
     </row>
     <row r="47">
       <c r="A47" s="57" t="s">
-        <v>340</v>
-      </c>
-      <c r="B47" s="61" t="s">
-        <v>341</v>
+        <v>353</v>
+      </c>
+      <c r="B47" s="62" t="s">
+        <v>354</v>
       </c>
       <c r="C47" s="50" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D47" s="50" t="s">
-        <v>343</v>
-      </c>
-      <c r="E47" s="59"/>
-      <c r="F47" s="59"/>
-      <c r="G47" s="59"/>
-      <c r="H47" s="59"/>
-      <c r="I47" s="59"/>
-      <c r="J47" s="59"/>
-      <c r="K47" s="59"/>
-      <c r="L47" s="59"/>
-      <c r="M47" s="59"/>
-      <c r="N47" s="59"/>
-      <c r="O47" s="59"/>
-      <c r="P47" s="59"/>
-      <c r="Q47" s="59"/>
-      <c r="R47" s="59"/>
-      <c r="S47" s="59"/>
-      <c r="T47" s="59"/>
+        <v>356</v>
+      </c>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
+      <c r="J47" s="60"/>
+      <c r="K47" s="60"/>
+      <c r="L47" s="60"/>
+      <c r="M47" s="60"/>
+      <c r="N47" s="60"/>
+      <c r="O47" s="60"/>
+      <c r="P47" s="60"/>
+      <c r="Q47" s="60"/>
+      <c r="R47" s="60"/>
+      <c r="S47" s="60"/>
+      <c r="T47" s="60"/>
     </row>
     <row r="48">
       <c r="A48" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="B48" s="61" t="s">
-        <v>345</v>
+        <v>357</v>
+      </c>
+      <c r="B48" s="62" t="s">
+        <v>358</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="D48" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="E48" s="59"/>
-      <c r="F48" s="59"/>
-      <c r="G48" s="59"/>
-      <c r="H48" s="59"/>
-      <c r="I48" s="59"/>
-      <c r="J48" s="59"/>
-      <c r="K48" s="59"/>
-      <c r="L48" s="59"/>
-      <c r="M48" s="59"/>
-      <c r="N48" s="59"/>
-      <c r="O48" s="59"/>
-      <c r="P48" s="59"/>
-      <c r="Q48" s="59"/>
-      <c r="R48" s="59"/>
-      <c r="S48" s="59"/>
-      <c r="T48" s="59"/>
+        <v>360</v>
+      </c>
+      <c r="E48" s="60"/>
+      <c r="F48" s="60"/>
+      <c r="G48" s="60"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="60"/>
+      <c r="J48" s="60"/>
+      <c r="K48" s="60"/>
+      <c r="L48" s="60"/>
+      <c r="M48" s="60"/>
+      <c r="N48" s="60"/>
+      <c r="O48" s="60"/>
+      <c r="P48" s="60"/>
+      <c r="Q48" s="60"/>
+      <c r="R48" s="60"/>
+      <c r="S48" s="60"/>
+      <c r="T48" s="60"/>
     </row>
     <row r="49">
       <c r="A49" s="57" t="s">
-        <v>348</v>
-      </c>
-      <c r="B49" s="61" t="s">
-        <v>349</v>
+        <v>361</v>
+      </c>
+      <c r="B49" s="50" t="s">
+        <v>362</v>
       </c>
       <c r="C49" s="50" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="D49" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="E49" s="59"/>
-      <c r="F49" s="59"/>
-      <c r="G49" s="59"/>
-      <c r="H49" s="59"/>
-      <c r="I49" s="59"/>
-      <c r="J49" s="59"/>
-      <c r="K49" s="59"/>
-      <c r="L49" s="59"/>
-      <c r="M49" s="59"/>
-      <c r="N49" s="59"/>
-      <c r="O49" s="59"/>
-      <c r="P49" s="59"/>
-      <c r="Q49" s="59"/>
-      <c r="R49" s="59"/>
-      <c r="S49" s="59"/>
-      <c r="T49" s="59"/>
+        <v>364</v>
+      </c>
+      <c r="E49" s="60"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="60"/>
+      <c r="J49" s="60"/>
+      <c r="K49" s="60"/>
+      <c r="L49" s="60"/>
+      <c r="M49" s="60"/>
+      <c r="N49" s="60"/>
+      <c r="O49" s="60"/>
+      <c r="P49" s="60"/>
+      <c r="Q49" s="60"/>
+      <c r="R49" s="60"/>
+      <c r="S49" s="60"/>
+      <c r="T49" s="60"/>
     </row>
     <row r="50">
-      <c r="A50" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="B50" s="61" t="s">
-        <v>353</v>
-      </c>
-      <c r="C50" s="50" t="s">
-        <v>354</v>
-      </c>
-      <c r="D50" s="50" t="s">
-        <v>355</v>
-      </c>
-      <c r="E50" s="59"/>
-      <c r="F50" s="59"/>
-      <c r="G50" s="59"/>
-      <c r="H50" s="59"/>
-      <c r="I50" s="59"/>
-      <c r="J50" s="59"/>
-      <c r="K50" s="59"/>
-      <c r="L50" s="59"/>
-      <c r="M50" s="59"/>
-      <c r="N50" s="59"/>
-      <c r="O50" s="59"/>
-      <c r="P50" s="59"/>
-      <c r="Q50" s="59"/>
-      <c r="R50" s="59"/>
-      <c r="S50" s="59"/>
-      <c r="T50" s="59"/>
+      <c r="A50" s="53" t="s">
+        <v>365</v>
+      </c>
+      <c r="B50" s="55" t="s">
+        <v>366</v>
+      </c>
+      <c r="C50" s="55" t="s">
+        <v>367</v>
+      </c>
+      <c r="D50" s="55" t="s">
+        <v>368</v>
+      </c>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="60"/>
+      <c r="J50" s="60"/>
+      <c r="K50" s="60"/>
+      <c r="L50" s="60"/>
+      <c r="M50" s="60"/>
+      <c r="N50" s="60"/>
+      <c r="O50" s="60"/>
+      <c r="P50" s="60"/>
+      <c r="Q50" s="60"/>
+      <c r="R50" s="60"/>
+      <c r="S50" s="60"/>
+      <c r="T50" s="60"/>
     </row>
     <row r="51">
-      <c r="A51" s="57" t="s">
-        <v>356</v>
-      </c>
-      <c r="B51" s="50" t="s">
-        <v>357</v>
-      </c>
-      <c r="C51" s="50" t="s">
-        <v>358</v>
-      </c>
-      <c r="D51" s="50" t="s">
-        <v>359</v>
-      </c>
-      <c r="E51" s="59"/>
-      <c r="F51" s="59"/>
-      <c r="G51" s="59"/>
-      <c r="H51" s="59"/>
-      <c r="I51" s="59"/>
-      <c r="J51" s="59"/>
-      <c r="K51" s="59"/>
-      <c r="L51" s="59"/>
-      <c r="M51" s="59"/>
-      <c r="N51" s="59"/>
-      <c r="O51" s="59"/>
-      <c r="P51" s="59"/>
-      <c r="Q51" s="59"/>
-      <c r="R51" s="59"/>
-      <c r="S51" s="59"/>
-      <c r="T51" s="59"/>
+      <c r="A51" s="56"/>
+      <c r="B51" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="49"/>
+      <c r="J51" s="49"/>
+      <c r="K51" s="49"/>
+      <c r="L51" s="49"/>
+      <c r="M51" s="49"/>
+      <c r="N51" s="49"/>
+      <c r="O51" s="49"/>
+      <c r="P51" s="49"/>
+      <c r="Q51" s="49"/>
+      <c r="R51" s="49"/>
+      <c r="S51" s="49"/>
+      <c r="T51" s="49"/>
     </row>
     <row r="52">
-      <c r="A52" s="53" t="s">
-        <v>360</v>
-      </c>
-      <c r="B52" s="55" t="s">
-        <v>361</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>362</v>
-      </c>
-      <c r="D52" s="55" t="s">
-        <v>363</v>
-      </c>
-      <c r="E52" s="59"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="59"/>
-      <c r="I52" s="59"/>
-      <c r="J52" s="59"/>
-      <c r="K52" s="59"/>
-      <c r="L52" s="59"/>
-      <c r="M52" s="59"/>
-      <c r="N52" s="59"/>
-      <c r="O52" s="59"/>
-      <c r="P52" s="59"/>
-      <c r="Q52" s="59"/>
-      <c r="R52" s="59"/>
-      <c r="S52" s="59"/>
-      <c r="T52" s="59"/>
+      <c r="A52" s="57" t="s">
+        <v>370</v>
+      </c>
+      <c r="B52" s="50" t="s">
+        <v>371</v>
+      </c>
+      <c r="C52" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D52" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="51"/>
+      <c r="H52" s="51"/>
+      <c r="I52" s="51"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="51"/>
+      <c r="L52" s="51"/>
+      <c r="M52" s="51"/>
+      <c r="N52" s="51"/>
+      <c r="O52" s="51"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="51"/>
+      <c r="R52" s="51"/>
+      <c r="S52" s="51"/>
+      <c r="T52" s="51"/>
     </row>
     <row r="53">
-      <c r="A53" s="56"/>
-      <c r="B53" s="48" t="s">
-        <v>364</v>
-      </c>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="49"/>
-      <c r="F53" s="49"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="49"/>
-      <c r="K53" s="49"/>
-      <c r="L53" s="49"/>
-      <c r="M53" s="49"/>
-      <c r="N53" s="49"/>
-      <c r="O53" s="49"/>
-      <c r="P53" s="49"/>
-      <c r="Q53" s="49"/>
-      <c r="R53" s="49"/>
-      <c r="S53" s="49"/>
-      <c r="T53" s="49"/>
+      <c r="A53" s="57" t="s">
+        <v>374</v>
+      </c>
+      <c r="B53" s="50" t="s">
+        <v>375</v>
+      </c>
+      <c r="C53" s="50" t="s">
+        <v>376</v>
+      </c>
+      <c r="D53" s="50" t="s">
+        <v>377</v>
+      </c>
+      <c r="E53" s="51"/>
+      <c r="F53" s="51"/>
+      <c r="G53" s="51"/>
+      <c r="H53" s="51"/>
+      <c r="I53" s="51"/>
+      <c r="J53" s="51"/>
+      <c r="K53" s="51"/>
+      <c r="L53" s="51"/>
+      <c r="M53" s="51"/>
+      <c r="N53" s="51"/>
+      <c r="O53" s="51"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="51"/>
+      <c r="R53" s="51"/>
+      <c r="S53" s="51"/>
+      <c r="T53" s="51"/>
     </row>
     <row r="54">
       <c r="A54" s="57" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="B54" s="50" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="D54" s="50" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="E54" s="51"/>
       <c r="F54" s="51"/>
@@ -7766,16 +7808,16 @@
     </row>
     <row r="55">
       <c r="A55" s="57" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="B55" s="50" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="C55" s="50" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="D55" s="50" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E55" s="51"/>
       <c r="F55" s="51"/>
@@ -7795,18 +7837,14 @@
       <c r="T55" s="51"/>
     </row>
     <row r="56">
-      <c r="A56" s="57" t="s">
-        <v>373</v>
-      </c>
-      <c r="B56" s="50" t="s">
-        <v>374</v>
-      </c>
-      <c r="C56" s="50" t="s">
-        <v>375</v>
-      </c>
-      <c r="D56" s="50" t="s">
-        <v>376</v>
-      </c>
+      <c r="A56" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="B56" s="55"/>
+      <c r="C56" s="55" t="s">
+        <v>387</v>
+      </c>
+      <c r="D56" s="55"/>
       <c r="E56" s="51"/>
       <c r="F56" s="51"/>
       <c r="G56" s="51"/>
@@ -7825,44 +7863,38 @@
       <c r="T56" s="51"/>
     </row>
     <row r="57">
-      <c r="A57" s="57" t="s">
-        <v>377</v>
-      </c>
-      <c r="B57" s="50" t="s">
-        <v>378</v>
-      </c>
-      <c r="C57" s="50" t="s">
-        <v>379</v>
-      </c>
-      <c r="D57" s="50" t="s">
-        <v>380</v>
-      </c>
-      <c r="E57" s="51"/>
-      <c r="F57" s="51"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="51"/>
-      <c r="K57" s="51"/>
-      <c r="L57" s="51"/>
-      <c r="M57" s="51"/>
-      <c r="N57" s="51"/>
-      <c r="O57" s="51"/>
-      <c r="P57" s="51"/>
-      <c r="Q57" s="51"/>
-      <c r="R57" s="51"/>
-      <c r="S57" s="51"/>
-      <c r="T57" s="51"/>
+      <c r="A57" s="56"/>
+      <c r="B57" s="48" t="s">
+        <v>388</v>
+      </c>
+      <c r="C57" s="48"/>
+      <c r="D57" s="48"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="49"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="49"/>
+      <c r="N57" s="49"/>
+      <c r="O57" s="49"/>
+      <c r="P57" s="49"/>
+      <c r="Q57" s="49"/>
+      <c r="R57" s="49"/>
+      <c r="S57" s="49"/>
+      <c r="T57" s="49"/>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="s">
-        <v>381</v>
-      </c>
-      <c r="B58" s="55"/>
-      <c r="C58" s="55" t="s">
-        <v>382</v>
-      </c>
-      <c r="D58" s="55"/>
+      <c r="A58" s="57" t="s">
+        <v>389</v>
+      </c>
+      <c r="B58" s="50"/>
+      <c r="C58" s="50" t="s">
+        <v>390</v>
+      </c>
+      <c r="D58" s="50"/>
       <c r="E58" s="51"/>
       <c r="F58" s="51"/>
       <c r="G58" s="51"/>
@@ -7881,36 +7913,38 @@
       <c r="T58" s="51"/>
     </row>
     <row r="59">
-      <c r="A59" s="56"/>
-      <c r="B59" s="48" t="s">
-        <v>383</v>
-      </c>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-      <c r="K59" s="49"/>
-      <c r="L59" s="49"/>
-      <c r="M59" s="49"/>
-      <c r="N59" s="49"/>
-      <c r="O59" s="49"/>
-      <c r="P59" s="49"/>
-      <c r="Q59" s="49"/>
-      <c r="R59" s="49"/>
-      <c r="S59" s="49"/>
-      <c r="T59" s="49"/>
+      <c r="A59" s="57" t="s">
+        <v>391</v>
+      </c>
+      <c r="B59" s="50"/>
+      <c r="C59" s="50" t="s">
+        <v>392</v>
+      </c>
+      <c r="D59" s="50"/>
+      <c r="E59" s="51"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="51"/>
+      <c r="I59" s="51"/>
+      <c r="J59" s="51"/>
+      <c r="K59" s="51"/>
+      <c r="L59" s="51"/>
+      <c r="M59" s="51"/>
+      <c r="N59" s="51"/>
+      <c r="O59" s="51"/>
+      <c r="P59" s="51"/>
+      <c r="Q59" s="51"/>
+      <c r="R59" s="51"/>
+      <c r="S59" s="51"/>
+      <c r="T59" s="51"/>
     </row>
     <row r="60">
       <c r="A60" s="57" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B60" s="50"/>
       <c r="C60" s="50" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="D60" s="50"/>
       <c r="E60" s="51"/>
@@ -7932,11 +7966,11 @@
     </row>
     <row r="61">
       <c r="A61" s="57" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B61" s="50"/>
       <c r="C61" s="50" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D61" s="50"/>
       <c r="E61" s="51"/>
@@ -7958,216 +7992,216 @@
     </row>
     <row r="62">
       <c r="A62" s="57" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B62" s="50"/>
       <c r="C62" s="50" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="D62" s="50"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51"/>
-      <c r="N62" s="51"/>
-      <c r="O62" s="51"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="51"/>
-      <c r="R62" s="51"/>
-      <c r="S62" s="51"/>
-      <c r="T62" s="51"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
+      <c r="J62" s="60"/>
+      <c r="K62" s="60"/>
+      <c r="L62" s="60"/>
+      <c r="M62" s="60"/>
+      <c r="N62" s="60"/>
+      <c r="O62" s="60"/>
+      <c r="P62" s="60"/>
+      <c r="Q62" s="60"/>
+      <c r="R62" s="60"/>
+      <c r="S62" s="60"/>
+      <c r="T62" s="60"/>
     </row>
     <row r="63">
       <c r="A63" s="57" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B63" s="50"/>
       <c r="C63" s="50" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="D63" s="50"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="51"/>
-      <c r="L63" s="51"/>
-      <c r="M63" s="51"/>
-      <c r="N63" s="51"/>
-      <c r="O63" s="51"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="51"/>
-      <c r="R63" s="51"/>
-      <c r="S63" s="51"/>
-      <c r="T63" s="51"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
+      <c r="J63" s="60"/>
+      <c r="K63" s="60"/>
+      <c r="L63" s="60"/>
+      <c r="M63" s="60"/>
+      <c r="N63" s="60"/>
+      <c r="O63" s="60"/>
+      <c r="P63" s="60"/>
+      <c r="Q63" s="60"/>
+      <c r="R63" s="60"/>
+      <c r="S63" s="60"/>
+      <c r="T63" s="60"/>
     </row>
     <row r="64">
       <c r="A64" s="57" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B64" s="50"/>
       <c r="C64" s="50" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D64" s="50"/>
-      <c r="E64" s="59"/>
-      <c r="F64" s="59"/>
-      <c r="G64" s="59"/>
-      <c r="H64" s="59"/>
-      <c r="I64" s="59"/>
-      <c r="J64" s="59"/>
-      <c r="K64" s="59"/>
-      <c r="L64" s="59"/>
-      <c r="M64" s="59"/>
-      <c r="N64" s="59"/>
-      <c r="O64" s="59"/>
-      <c r="P64" s="59"/>
-      <c r="Q64" s="59"/>
-      <c r="R64" s="59"/>
-      <c r="S64" s="59"/>
-      <c r="T64" s="59"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="60"/>
+      <c r="J64" s="60"/>
+      <c r="K64" s="60"/>
+      <c r="L64" s="60"/>
+      <c r="M64" s="60"/>
+      <c r="N64" s="60"/>
+      <c r="O64" s="60"/>
+      <c r="P64" s="60"/>
+      <c r="Q64" s="60"/>
+      <c r="R64" s="60"/>
+      <c r="S64" s="60"/>
+      <c r="T64" s="60"/>
     </row>
     <row r="65">
       <c r="A65" s="57" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B65" s="50"/>
       <c r="C65" s="50" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="D65" s="50"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="59"/>
-      <c r="H65" s="59"/>
-      <c r="I65" s="59"/>
-      <c r="J65" s="59"/>
-      <c r="K65" s="59"/>
-      <c r="L65" s="59"/>
-      <c r="M65" s="59"/>
-      <c r="N65" s="59"/>
-      <c r="O65" s="59"/>
-      <c r="P65" s="59"/>
-      <c r="Q65" s="59"/>
-      <c r="R65" s="59"/>
-      <c r="S65" s="59"/>
-      <c r="T65" s="59"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
+      <c r="J65" s="60"/>
+      <c r="K65" s="60"/>
+      <c r="L65" s="60"/>
+      <c r="M65" s="60"/>
+      <c r="N65" s="60"/>
+      <c r="O65" s="60"/>
+      <c r="P65" s="60"/>
+      <c r="Q65" s="60"/>
+      <c r="R65" s="60"/>
+      <c r="S65" s="60"/>
+      <c r="T65" s="60"/>
     </row>
     <row r="66">
       <c r="A66" s="57" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B66" s="50"/>
       <c r="C66" s="50" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D66" s="50"/>
-      <c r="E66" s="59"/>
-      <c r="F66" s="59"/>
-      <c r="G66" s="59"/>
-      <c r="H66" s="59"/>
-      <c r="I66" s="59"/>
-      <c r="J66" s="59"/>
-      <c r="K66" s="59"/>
-      <c r="L66" s="59"/>
-      <c r="M66" s="59"/>
-      <c r="N66" s="59"/>
-      <c r="O66" s="59"/>
-      <c r="P66" s="59"/>
-      <c r="Q66" s="59"/>
-      <c r="R66" s="59"/>
-      <c r="S66" s="59"/>
-      <c r="T66" s="59"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="60"/>
+      <c r="M66" s="60"/>
+      <c r="N66" s="60"/>
+      <c r="O66" s="60"/>
+      <c r="P66" s="60"/>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
     </row>
     <row r="67">
-      <c r="A67" s="57" t="s">
-        <v>398</v>
-      </c>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50" t="s">
-        <v>399</v>
-      </c>
-      <c r="D67" s="50"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="59"/>
-      <c r="G67" s="59"/>
-      <c r="H67" s="59"/>
-      <c r="I67" s="59"/>
-      <c r="J67" s="59"/>
-      <c r="K67" s="59"/>
-      <c r="L67" s="59"/>
-      <c r="M67" s="59"/>
-      <c r="N67" s="59"/>
-      <c r="O67" s="59"/>
-      <c r="P67" s="59"/>
-      <c r="Q67" s="59"/>
-      <c r="R67" s="59"/>
-      <c r="S67" s="59"/>
-      <c r="T67" s="59"/>
+      <c r="A67" s="53" t="s">
+        <v>407</v>
+      </c>
+      <c r="B67" s="55"/>
+      <c r="C67" s="55" t="s">
+        <v>408</v>
+      </c>
+      <c r="D67" s="55"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="60"/>
+      <c r="L67" s="60"/>
+      <c r="M67" s="60"/>
+      <c r="N67" s="60"/>
+      <c r="O67" s="60"/>
+      <c r="P67" s="60"/>
+      <c r="Q67" s="60"/>
+      <c r="R67" s="60"/>
+      <c r="S67" s="60"/>
+      <c r="T67" s="60"/>
     </row>
     <row r="68">
-      <c r="A68" s="57" t="s">
-        <v>400</v>
-      </c>
-      <c r="B68" s="50"/>
-      <c r="C68" s="50" t="s">
-        <v>401</v>
-      </c>
-      <c r="D68" s="50"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="59"/>
-      <c r="G68" s="59"/>
-      <c r="H68" s="59"/>
-      <c r="I68" s="59"/>
-      <c r="J68" s="59"/>
-      <c r="K68" s="59"/>
-      <c r="L68" s="59"/>
-      <c r="M68" s="59"/>
-      <c r="N68" s="59"/>
-      <c r="O68" s="59"/>
-      <c r="P68" s="59"/>
-      <c r="Q68" s="59"/>
-      <c r="R68" s="59"/>
-      <c r="S68" s="59"/>
-      <c r="T68" s="59"/>
+      <c r="A68" s="56"/>
+      <c r="B68" s="48" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="49"/>
+      <c r="L68" s="49"/>
+      <c r="M68" s="49"/>
+      <c r="N68" s="49"/>
+      <c r="O68" s="49"/>
+      <c r="P68" s="49"/>
+      <c r="Q68" s="49"/>
+      <c r="R68" s="49"/>
+      <c r="S68" s="49"/>
+      <c r="T68" s="49"/>
     </row>
     <row r="69">
       <c r="A69" s="53" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B69" s="55"/>
       <c r="C69" s="55" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="D69" s="55"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="59"/>
-      <c r="G69" s="59"/>
-      <c r="H69" s="59"/>
-      <c r="I69" s="59"/>
-      <c r="J69" s="59"/>
-      <c r="K69" s="59"/>
-      <c r="L69" s="59"/>
-      <c r="M69" s="59"/>
-      <c r="N69" s="59"/>
-      <c r="O69" s="59"/>
-      <c r="P69" s="59"/>
-      <c r="Q69" s="59"/>
-      <c r="R69" s="59"/>
-      <c r="S69" s="59"/>
-      <c r="T69" s="59"/>
+      <c r="E69" s="60" t="s">
+        <v>412</v>
+      </c>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
+      <c r="J69" s="60"/>
+      <c r="K69" s="60"/>
+      <c r="L69" s="60"/>
+      <c r="M69" s="60"/>
+      <c r="N69" s="60"/>
+      <c r="O69" s="60"/>
+      <c r="P69" s="60"/>
+      <c r="Q69" s="60"/>
+      <c r="R69" s="60"/>
+      <c r="S69" s="60"/>
+      <c r="T69" s="60"/>
     </row>
     <row r="70">
       <c r="A70" s="56"/>
       <c r="B70" s="48" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="C70" s="48"/>
       <c r="D70" s="48"/>
@@ -8189,64 +8223,64 @@
       <c r="T70" s="49"/>
     </row>
     <row r="71">
-      <c r="A71" s="53" t="s">
-        <v>405</v>
-      </c>
-      <c r="B71" s="55"/>
-      <c r="C71" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="D71" s="55"/>
-      <c r="E71" s="59" t="s">
-        <v>407</v>
-      </c>
-      <c r="F71" s="59"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="59"/>
-      <c r="J71" s="59"/>
-      <c r="K71" s="59"/>
-      <c r="L71" s="59"/>
-      <c r="M71" s="59"/>
-      <c r="N71" s="59"/>
-      <c r="O71" s="59"/>
-      <c r="P71" s="59"/>
-      <c r="Q71" s="59"/>
-      <c r="R71" s="59"/>
-      <c r="S71" s="59"/>
-      <c r="T71" s="59"/>
+      <c r="A71" s="57" t="s">
+        <v>414</v>
+      </c>
+      <c r="B71" s="50"/>
+      <c r="C71" s="50" t="s">
+        <v>415</v>
+      </c>
+      <c r="D71" s="50"/>
+      <c r="E71" s="51"/>
+      <c r="F71" s="51"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="51"/>
+      <c r="I71" s="51"/>
+      <c r="J71" s="51"/>
+      <c r="K71" s="51"/>
+      <c r="L71" s="51"/>
+      <c r="M71" s="51"/>
+      <c r="N71" s="51"/>
+      <c r="O71" s="51"/>
+      <c r="P71" s="51"/>
+      <c r="Q71" s="51"/>
+      <c r="R71" s="51"/>
+      <c r="S71" s="51"/>
+      <c r="T71" s="51"/>
     </row>
     <row r="72">
-      <c r="A72" s="56"/>
-      <c r="B72" s="48" t="s">
-        <v>408</v>
-      </c>
-      <c r="C72" s="48"/>
-      <c r="D72" s="48"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="49"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="49"/>
-      <c r="J72" s="49"/>
-      <c r="K72" s="49"/>
-      <c r="L72" s="49"/>
-      <c r="M72" s="49"/>
-      <c r="N72" s="49"/>
-      <c r="O72" s="49"/>
-      <c r="P72" s="49"/>
-      <c r="Q72" s="49"/>
-      <c r="R72" s="49"/>
-      <c r="S72" s="49"/>
-      <c r="T72" s="49"/>
+      <c r="A72" s="57" t="s">
+        <v>416</v>
+      </c>
+      <c r="B72" s="50"/>
+      <c r="C72" s="50" t="s">
+        <v>417</v>
+      </c>
+      <c r="D72" s="50"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="51"/>
+      <c r="I72" s="51"/>
+      <c r="J72" s="51"/>
+      <c r="K72" s="51"/>
+      <c r="L72" s="51"/>
+      <c r="M72" s="51"/>
+      <c r="N72" s="51"/>
+      <c r="O72" s="51"/>
+      <c r="P72" s="51"/>
+      <c r="Q72" s="51"/>
+      <c r="R72" s="51"/>
+      <c r="S72" s="51"/>
+      <c r="T72" s="51"/>
     </row>
     <row r="73">
-      <c r="A73" s="57" t="s">
-        <v>409</v>
-      </c>
-      <c r="B73" s="50"/>
+      <c r="A73" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="B73" s="62"/>
       <c r="C73" s="50" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D73" s="50"/>
       <c r="E73" s="51"/>
@@ -8267,12 +8301,12 @@
       <c r="T73" s="51"/>
     </row>
     <row r="74">
-      <c r="A74" s="57" t="s">
-        <v>411</v>
-      </c>
-      <c r="B74" s="50"/>
+      <c r="A74" s="61" t="s">
+        <v>420</v>
+      </c>
+      <c r="B74" s="62"/>
       <c r="C74" s="50" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="D74" s="50"/>
       <c r="E74" s="51"/>
@@ -8293,14 +8327,14 @@
       <c r="T74" s="51"/>
     </row>
     <row r="75">
-      <c r="A75" s="60" t="s">
-        <v>413</v>
-      </c>
-      <c r="B75" s="61"/>
-      <c r="C75" s="50" t="s">
-        <v>414</v>
-      </c>
-      <c r="D75" s="50"/>
+      <c r="A75" s="53" t="s">
+        <v>422</v>
+      </c>
+      <c r="B75" s="53"/>
+      <c r="C75" s="55" t="s">
+        <v>423</v>
+      </c>
+      <c r="D75" s="55"/>
       <c r="E75" s="51"/>
       <c r="F75" s="51"/>
       <c r="G75" s="51"/>
@@ -8319,40 +8353,42 @@
       <c r="T75" s="51"/>
     </row>
     <row r="76">
-      <c r="A76" s="60" t="s">
-        <v>415</v>
-      </c>
-      <c r="B76" s="61"/>
-      <c r="C76" s="50" t="s">
-        <v>416</v>
-      </c>
-      <c r="D76" s="50"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="51"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="J76" s="51"/>
-      <c r="K76" s="51"/>
-      <c r="L76" s="51"/>
-      <c r="M76" s="51"/>
-      <c r="N76" s="51"/>
-      <c r="O76" s="51"/>
-      <c r="P76" s="51"/>
-      <c r="Q76" s="51"/>
-      <c r="R76" s="51"/>
-      <c r="S76" s="51"/>
-      <c r="T76" s="51"/>
+      <c r="A76" s="56"/>
+      <c r="B76" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="49"/>
+      <c r="F76" s="49"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="49"/>
+      <c r="I76" s="49"/>
+      <c r="J76" s="49"/>
+      <c r="K76" s="49"/>
+      <c r="L76" s="49"/>
+      <c r="M76" s="49"/>
+      <c r="N76" s="49"/>
+      <c r="O76" s="49"/>
+      <c r="P76" s="49"/>
+      <c r="Q76" s="49"/>
+      <c r="R76" s="49"/>
+      <c r="S76" s="49"/>
+      <c r="T76" s="49"/>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="s">
-        <v>417</v>
-      </c>
-      <c r="B77" s="53"/>
-      <c r="C77" s="55" t="s">
-        <v>418</v>
-      </c>
-      <c r="D77" s="55"/>
+      <c r="A77" s="57" t="s">
+        <v>425</v>
+      </c>
+      <c r="B77" s="62" t="s">
+        <v>426</v>
+      </c>
+      <c r="C77" s="50" t="s">
+        <v>427</v>
+      </c>
+      <c r="D77" s="50" t="s">
+        <v>428</v>
+      </c>
       <c r="E77" s="51"/>
       <c r="F77" s="51"/>
       <c r="G77" s="51"/>
@@ -8371,42 +8407,40 @@
       <c r="T77" s="51"/>
     </row>
     <row r="78">
-      <c r="A78" s="56"/>
-      <c r="B78" s="56" t="s">
-        <v>419</v>
-      </c>
-      <c r="C78" s="48"/>
-      <c r="D78" s="48"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="49"/>
-      <c r="G78" s="49"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="49"/>
-      <c r="J78" s="49"/>
-      <c r="K78" s="49"/>
-      <c r="L78" s="49"/>
-      <c r="M78" s="49"/>
-      <c r="N78" s="49"/>
-      <c r="O78" s="49"/>
-      <c r="P78" s="49"/>
-      <c r="Q78" s="49"/>
-      <c r="R78" s="49"/>
-      <c r="S78" s="49"/>
-      <c r="T78" s="49"/>
+      <c r="A78" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="B78" s="62"/>
+      <c r="C78" s="50" t="s">
+        <v>430</v>
+      </c>
+      <c r="D78" s="50"/>
+      <c r="E78" s="51"/>
+      <c r="F78" s="51"/>
+      <c r="G78" s="51"/>
+      <c r="H78" s="51"/>
+      <c r="I78" s="51"/>
+      <c r="J78" s="51"/>
+      <c r="K78" s="51"/>
+      <c r="L78" s="51"/>
+      <c r="M78" s="51"/>
+      <c r="N78" s="51"/>
+      <c r="O78" s="51"/>
+      <c r="P78" s="51"/>
+      <c r="Q78" s="51"/>
+      <c r="R78" s="51"/>
+      <c r="S78" s="51"/>
+      <c r="T78" s="51"/>
     </row>
     <row r="79">
       <c r="A79" s="57" t="s">
-        <v>420</v>
-      </c>
-      <c r="B79" s="61" t="s">
-        <v>421</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="B79" s="62"/>
       <c r="C79" s="50" t="s">
-        <v>422</v>
-      </c>
-      <c r="D79" s="50" t="s">
-        <v>423</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="D79" s="50"/>
       <c r="E79" s="51"/>
       <c r="F79" s="51"/>
       <c r="G79" s="51"/>
@@ -8426,11 +8460,11 @@
     </row>
     <row r="80">
       <c r="A80" s="57" t="s">
-        <v>424</v>
-      </c>
-      <c r="B80" s="61"/>
+        <v>432</v>
+      </c>
+      <c r="B80" s="62"/>
       <c r="C80" s="50" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="D80" s="50"/>
       <c r="E80" s="51"/>
@@ -8452,11 +8486,11 @@
     </row>
     <row r="81">
       <c r="A81" s="57" t="s">
-        <v>426</v>
-      </c>
-      <c r="B81" s="61"/>
+        <v>434</v>
+      </c>
+      <c r="B81" s="62"/>
       <c r="C81" s="50" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="D81" s="50"/>
       <c r="E81" s="51"/>
@@ -8478,11 +8512,11 @@
     </row>
     <row r="82">
       <c r="A82" s="57" t="s">
-        <v>427</v>
-      </c>
-      <c r="B82" s="61"/>
+        <v>436</v>
+      </c>
+      <c r="B82" s="63"/>
       <c r="C82" s="50" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="D82" s="50"/>
       <c r="E82" s="51"/>
@@ -8504,13 +8538,17 @@
     </row>
     <row r="83">
       <c r="A83" s="57" t="s">
-        <v>429</v>
-      </c>
-      <c r="B83" s="61"/>
+        <v>438</v>
+      </c>
+      <c r="B83" s="63" t="s">
+        <v>439</v>
+      </c>
       <c r="C83" s="50" t="s">
-        <v>430</v>
-      </c>
-      <c r="D83" s="50"/>
+        <v>440</v>
+      </c>
+      <c r="D83" s="50" t="s">
+        <v>441</v>
+      </c>
       <c r="E83" s="51"/>
       <c r="F83" s="51"/>
       <c r="G83" s="51"/>
@@ -8529,14 +8567,14 @@
       <c r="T83" s="51"/>
     </row>
     <row r="84">
-      <c r="A84" s="57" t="s">
-        <v>431</v>
-      </c>
-      <c r="B84" s="62"/>
-      <c r="C84" s="50" t="s">
-        <v>432</v>
-      </c>
-      <c r="D84" s="50"/>
+      <c r="A84" s="53" t="s">
+        <v>442</v>
+      </c>
+      <c r="B84" s="64"/>
+      <c r="C84" s="55" t="s">
+        <v>443</v>
+      </c>
+      <c r="D84" s="55"/>
       <c r="E84" s="51"/>
       <c r="F84" s="51"/>
       <c r="G84" s="51"/>
@@ -8555,42 +8593,36 @@
       <c r="T84" s="51"/>
     </row>
     <row r="85">
-      <c r="A85" s="57" t="s">
-        <v>433</v>
-      </c>
-      <c r="B85" s="62" t="s">
-        <v>434</v>
-      </c>
-      <c r="C85" s="50" t="s">
-        <v>435</v>
-      </c>
-      <c r="D85" s="50" t="s">
-        <v>436</v>
-      </c>
-      <c r="E85" s="51"/>
-      <c r="F85" s="51"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="51"/>
-      <c r="K85" s="51"/>
-      <c r="L85" s="51"/>
-      <c r="M85" s="51"/>
-      <c r="N85" s="51"/>
-      <c r="O85" s="51"/>
-      <c r="P85" s="51"/>
-      <c r="Q85" s="51"/>
-      <c r="R85" s="51"/>
-      <c r="S85" s="51"/>
-      <c r="T85" s="51"/>
+      <c r="A85" s="56"/>
+      <c r="B85" s="56" t="s">
+        <v>444</v>
+      </c>
+      <c r="C85" s="48"/>
+      <c r="D85" s="48"/>
+      <c r="E85" s="49"/>
+      <c r="F85" s="49"/>
+      <c r="G85" s="49"/>
+      <c r="H85" s="49"/>
+      <c r="I85" s="49"/>
+      <c r="J85" s="49"/>
+      <c r="K85" s="49"/>
+      <c r="L85" s="49"/>
+      <c r="M85" s="49"/>
+      <c r="N85" s="49"/>
+      <c r="O85" s="49"/>
+      <c r="P85" s="49"/>
+      <c r="Q85" s="49"/>
+      <c r="R85" s="49"/>
+      <c r="S85" s="49"/>
+      <c r="T85" s="49"/>
     </row>
     <row r="86">
       <c r="A86" s="53" t="s">
-        <v>437</v>
-      </c>
-      <c r="B86" s="63"/>
+        <v>445</v>
+      </c>
+      <c r="B86" s="53"/>
       <c r="C86" s="55" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="D86" s="55"/>
       <c r="E86" s="51"/>
@@ -8612,8 +8644,8 @@
     </row>
     <row r="87">
       <c r="A87" s="56"/>
-      <c r="B87" s="56" t="s">
-        <v>439</v>
+      <c r="B87" s="48" t="s">
+        <v>447</v>
       </c>
       <c r="C87" s="48"/>
       <c r="D87" s="48"/>
@@ -8635,14 +8667,14 @@
       <c r="T87" s="49"/>
     </row>
     <row r="88">
-      <c r="A88" s="53" t="s">
-        <v>440</v>
-      </c>
-      <c r="B88" s="53"/>
-      <c r="C88" s="55" t="s">
-        <v>441</v>
-      </c>
-      <c r="D88" s="55"/>
+      <c r="A88" s="57" t="s">
+        <v>448</v>
+      </c>
+      <c r="B88" s="57"/>
+      <c r="C88" s="50" t="s">
+        <v>449</v>
+      </c>
+      <c r="D88" s="50"/>
       <c r="E88" s="51"/>
       <c r="F88" s="51"/>
       <c r="G88" s="51"/>
@@ -8661,36 +8693,38 @@
       <c r="T88" s="51"/>
     </row>
     <row r="89">
-      <c r="A89" s="56"/>
-      <c r="B89" s="48" t="s">
-        <v>442</v>
-      </c>
-      <c r="C89" s="48"/>
-      <c r="D89" s="48"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="49"/>
-      <c r="J89" s="49"/>
-      <c r="K89" s="49"/>
-      <c r="L89" s="49"/>
-      <c r="M89" s="49"/>
-      <c r="N89" s="49"/>
-      <c r="O89" s="49"/>
-      <c r="P89" s="49"/>
-      <c r="Q89" s="49"/>
-      <c r="R89" s="49"/>
-      <c r="S89" s="49"/>
-      <c r="T89" s="49"/>
+      <c r="A89" s="57" t="s">
+        <v>450</v>
+      </c>
+      <c r="B89" s="57"/>
+      <c r="C89" s="50" t="s">
+        <v>451</v>
+      </c>
+      <c r="D89" s="50"/>
+      <c r="E89" s="51"/>
+      <c r="F89" s="51"/>
+      <c r="G89" s="51"/>
+      <c r="H89" s="51"/>
+      <c r="I89" s="51"/>
+      <c r="J89" s="51"/>
+      <c r="K89" s="51"/>
+      <c r="L89" s="51"/>
+      <c r="M89" s="51"/>
+      <c r="N89" s="51"/>
+      <c r="O89" s="51"/>
+      <c r="P89" s="51"/>
+      <c r="Q89" s="51"/>
+      <c r="R89" s="51"/>
+      <c r="S89" s="51"/>
+      <c r="T89" s="51"/>
     </row>
     <row r="90">
       <c r="A90" s="57" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B90" s="57"/>
       <c r="C90" s="50" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="D90" s="50"/>
       <c r="E90" s="51"/>
@@ -8712,11 +8746,11 @@
     </row>
     <row r="91">
       <c r="A91" s="57" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B91" s="57"/>
       <c r="C91" s="50" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="D91" s="50"/>
       <c r="E91" s="51"/>
@@ -8738,11 +8772,11 @@
     </row>
     <row r="92">
       <c r="A92" s="57" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B92" s="57"/>
       <c r="C92" s="50" t="s">
-        <v>414</v>
+        <v>456</v>
       </c>
       <c r="D92" s="50"/>
       <c r="E92" s="51"/>
@@ -8764,37 +8798,37 @@
     </row>
     <row r="93">
       <c r="A93" s="57" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="B93" s="57"/>
       <c r="C93" s="50" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="D93" s="50"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="51"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="51"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="51"/>
-      <c r="K93" s="51"/>
-      <c r="L93" s="51"/>
-      <c r="M93" s="51"/>
-      <c r="N93" s="51"/>
-      <c r="O93" s="51"/>
-      <c r="P93" s="51"/>
-      <c r="Q93" s="51"/>
-      <c r="R93" s="51"/>
-      <c r="S93" s="51"/>
-      <c r="T93" s="51"/>
+      <c r="E93" s="60"/>
+      <c r="F93" s="60"/>
+      <c r="G93" s="60"/>
+      <c r="H93" s="60"/>
+      <c r="I93" s="60"/>
+      <c r="J93" s="60"/>
+      <c r="K93" s="60"/>
+      <c r="L93" s="60"/>
+      <c r="M93" s="60"/>
+      <c r="N93" s="60"/>
+      <c r="O93" s="60"/>
+      <c r="P93" s="60"/>
+      <c r="Q93" s="60"/>
+      <c r="R93" s="60"/>
+      <c r="S93" s="60"/>
+      <c r="T93" s="60"/>
     </row>
     <row r="94">
       <c r="A94" s="57" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B94" s="57"/>
       <c r="C94" s="50" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D94" s="50"/>
       <c r="E94" s="51"/>
@@ -8816,39 +8850,39 @@
     </row>
     <row r="95">
       <c r="A95" s="57" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B95" s="57"/>
       <c r="C95" s="50" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="D95" s="50"/>
-      <c r="E95" s="59"/>
-      <c r="F95" s="59"/>
-      <c r="G95" s="59"/>
-      <c r="H95" s="59"/>
-      <c r="I95" s="59"/>
-      <c r="J95" s="59"/>
-      <c r="K95" s="59"/>
-      <c r="L95" s="59"/>
-      <c r="M95" s="59"/>
-      <c r="N95" s="59"/>
-      <c r="O95" s="59"/>
-      <c r="P95" s="59"/>
-      <c r="Q95" s="59"/>
-      <c r="R95" s="59"/>
-      <c r="S95" s="59"/>
-      <c r="T95" s="59"/>
+      <c r="E95" s="51"/>
+      <c r="F95" s="51"/>
+      <c r="G95" s="51"/>
+      <c r="H95" s="51"/>
+      <c r="I95" s="51"/>
+      <c r="J95" s="51"/>
+      <c r="K95" s="51"/>
+      <c r="L95" s="51"/>
+      <c r="M95" s="51"/>
+      <c r="N95" s="51"/>
+      <c r="O95" s="51"/>
+      <c r="P95" s="51"/>
+      <c r="Q95" s="51"/>
+      <c r="R95" s="51"/>
+      <c r="S95" s="51"/>
+      <c r="T95" s="51"/>
     </row>
     <row r="96">
-      <c r="A96" s="57" t="s">
-        <v>454</v>
-      </c>
-      <c r="B96" s="57"/>
-      <c r="C96" s="50" t="s">
-        <v>455</v>
-      </c>
-      <c r="D96" s="50"/>
+      <c r="A96" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="B96" s="53"/>
+      <c r="C96" s="55" t="s">
+        <v>464</v>
+      </c>
+      <c r="D96" s="55"/>
       <c r="E96" s="51"/>
       <c r="F96" s="51"/>
       <c r="G96" s="51"/>
@@ -8867,40 +8901,42 @@
       <c r="T96" s="51"/>
     </row>
     <row r="97">
-      <c r="A97" s="57" t="s">
-        <v>456</v>
-      </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="50" t="s">
-        <v>457</v>
-      </c>
-      <c r="D97" s="50"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="51"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
-      <c r="J97" s="51"/>
-      <c r="K97" s="51"/>
-      <c r="L97" s="51"/>
-      <c r="M97" s="51"/>
-      <c r="N97" s="51"/>
-      <c r="O97" s="51"/>
-      <c r="P97" s="51"/>
-      <c r="Q97" s="51"/>
-      <c r="R97" s="51"/>
-      <c r="S97" s="51"/>
-      <c r="T97" s="51"/>
+      <c r="A97" s="56"/>
+      <c r="B97" s="56" t="s">
+        <v>465</v>
+      </c>
+      <c r="C97" s="48"/>
+      <c r="D97" s="48"/>
+      <c r="E97" s="49"/>
+      <c r="F97" s="49"/>
+      <c r="G97" s="49"/>
+      <c r="H97" s="49"/>
+      <c r="I97" s="49"/>
+      <c r="J97" s="49"/>
+      <c r="K97" s="49"/>
+      <c r="L97" s="49"/>
+      <c r="M97" s="49"/>
+      <c r="N97" s="49"/>
+      <c r="O97" s="49"/>
+      <c r="P97" s="49"/>
+      <c r="Q97" s="49"/>
+      <c r="R97" s="49"/>
+      <c r="S97" s="49"/>
+      <c r="T97" s="49"/>
     </row>
     <row r="98">
       <c r="A98" s="53" t="s">
-        <v>458</v>
-      </c>
-      <c r="B98" s="53"/>
+        <v>466</v>
+      </c>
+      <c r="B98" s="53" t="s">
+        <v>467</v>
+      </c>
       <c r="C98" s="55" t="s">
-        <v>459</v>
-      </c>
-      <c r="D98" s="55"/>
+        <v>468</v>
+      </c>
+      <c r="D98" s="55" t="s">
+        <v>469</v>
+      </c>
       <c r="E98" s="51"/>
       <c r="F98" s="51"/>
       <c r="G98" s="51"/>
@@ -8920,8 +8956,8 @@
     </row>
     <row r="99">
       <c r="A99" s="56"/>
-      <c r="B99" s="56" t="s">
-        <v>460</v>
+      <c r="B99" s="48" t="s">
+        <v>470</v>
       </c>
       <c r="C99" s="48"/>
       <c r="D99" s="48"/>
@@ -8943,17 +8979,17 @@
       <c r="T99" s="49"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="s">
-        <v>461</v>
-      </c>
-      <c r="B100" s="53" t="s">
-        <v>462</v>
-      </c>
-      <c r="C100" s="55" t="s">
-        <v>463</v>
-      </c>
-      <c r="D100" s="55" t="s">
-        <v>464</v>
+      <c r="A100" s="57" t="s">
+        <v>471</v>
+      </c>
+      <c r="B100" s="50" t="s">
+        <v>472</v>
+      </c>
+      <c r="C100" s="50" t="s">
+        <v>473</v>
+      </c>
+      <c r="D100" s="50" t="s">
+        <v>474</v>
       </c>
       <c r="E100" s="51"/>
       <c r="F100" s="51"/>
@@ -8973,42 +9009,36 @@
       <c r="T100" s="51"/>
     </row>
     <row r="101">
-      <c r="A101" s="56"/>
-      <c r="B101" s="48" t="s">
-        <v>465</v>
-      </c>
-      <c r="C101" s="48"/>
-      <c r="D101" s="48"/>
-      <c r="E101" s="49"/>
-      <c r="F101" s="49"/>
-      <c r="G101" s="49"/>
-      <c r="H101" s="49"/>
-      <c r="I101" s="49"/>
-      <c r="J101" s="49"/>
-      <c r="K101" s="49"/>
-      <c r="L101" s="49"/>
-      <c r="M101" s="49"/>
-      <c r="N101" s="49"/>
-      <c r="O101" s="49"/>
-      <c r="P101" s="49"/>
-      <c r="Q101" s="49"/>
-      <c r="R101" s="49"/>
-      <c r="S101" s="49"/>
-      <c r="T101" s="49"/>
+      <c r="A101" s="53" t="s">
+        <v>475</v>
+      </c>
+      <c r="B101" s="55"/>
+      <c r="C101" s="55" t="s">
+        <v>476</v>
+      </c>
+      <c r="D101" s="55"/>
+      <c r="E101" s="51"/>
+      <c r="F101" s="51"/>
+      <c r="G101" s="51"/>
+      <c r="H101" s="51"/>
+      <c r="I101" s="51"/>
+      <c r="J101" s="51"/>
+      <c r="K101" s="51"/>
+      <c r="L101" s="51"/>
+      <c r="M101" s="51"/>
+      <c r="N101" s="51"/>
+      <c r="O101" s="51"/>
+      <c r="P101" s="51"/>
+      <c r="Q101" s="51"/>
+      <c r="R101" s="51"/>
+      <c r="S101" s="51"/>
+      <c r="T101" s="51"/>
     </row>
     <row r="102">
-      <c r="A102" s="57" t="s">
-        <v>466</v>
-      </c>
-      <c r="B102" s="50" t="s">
-        <v>467</v>
-      </c>
-      <c r="C102" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="D102" s="50" t="s">
-        <v>469</v>
-      </c>
+      <c r="A102" s="65"/>
+      <c r="B102" s="66"/>
+      <c r="C102" s="66"/>
+      <c r="D102" s="66"/>
       <c r="E102" s="51"/>
       <c r="F102" s="51"/>
       <c r="G102" s="51"/>
@@ -9027,14 +9057,10 @@
       <c r="T102" s="51"/>
     </row>
     <row r="103">
-      <c r="A103" s="53" t="s">
-        <v>470</v>
-      </c>
-      <c r="B103" s="55"/>
-      <c r="C103" s="55" t="s">
-        <v>471</v>
-      </c>
-      <c r="D103" s="55"/>
+      <c r="A103" s="65"/>
+      <c r="B103" s="66"/>
+      <c r="C103" s="66"/>
+      <c r="D103" s="66"/>
       <c r="E103" s="51"/>
       <c r="F103" s="51"/>
       <c r="G103" s="51"/>
@@ -9053,10 +9079,10 @@
       <c r="T103" s="51"/>
     </row>
     <row r="104">
-      <c r="A104" s="64"/>
-      <c r="B104" s="65"/>
-      <c r="C104" s="65"/>
-      <c r="D104" s="65"/>
+      <c r="A104" s="65"/>
+      <c r="B104" s="66"/>
+      <c r="C104" s="66"/>
+      <c r="D104" s="66"/>
       <c r="E104" s="51"/>
       <c r="F104" s="51"/>
       <c r="G104" s="51"/>
@@ -9075,10 +9101,18 @@
       <c r="T104" s="51"/>
     </row>
     <row r="105">
-      <c r="A105" s="64"/>
-      <c r="B105" s="65"/>
-      <c r="C105" s="65"/>
-      <c r="D105" s="65"/>
+      <c r="A105" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="B105" s="57" t="s">
+        <v>477</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>478</v>
+      </c>
+      <c r="D105" s="50" t="s">
+        <v>479</v>
+      </c>
       <c r="E105" s="51"/>
       <c r="F105" s="51"/>
       <c r="G105" s="51"/>
@@ -9097,10 +9131,18 @@
       <c r="T105" s="51"/>
     </row>
     <row r="106">
-      <c r="A106" s="64"/>
-      <c r="B106" s="65"/>
-      <c r="C106" s="65"/>
-      <c r="D106" s="65"/>
+      <c r="A106" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" s="57" t="s">
+        <v>480</v>
+      </c>
+      <c r="C106" s="50" t="s">
+        <v>481</v>
+      </c>
+      <c r="D106" s="50" t="s">
+        <v>482</v>
+      </c>
       <c r="E106" s="51"/>
       <c r="F106" s="51"/>
       <c r="G106" s="51"/>
@@ -9120,16 +9162,16 @@
     </row>
     <row r="107">
       <c r="A107" s="57" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B107" s="57" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="D107" s="50" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="E107" s="51"/>
       <c r="F107" s="51"/>
@@ -9150,16 +9192,16 @@
     </row>
     <row r="108">
       <c r="A108" s="57" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B108" s="57" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="D108" s="50" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="E108" s="51"/>
       <c r="F108" s="51"/>
@@ -9180,16 +9222,16 @@
     </row>
     <row r="109">
       <c r="A109" s="57" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B109" s="57" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="D109" s="50" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="E109" s="51"/>
       <c r="F109" s="51"/>
@@ -9210,16 +9252,16 @@
     </row>
     <row r="110">
       <c r="A110" s="57" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B110" s="57" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D110" s="50" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="E110" s="51"/>
       <c r="F110" s="51"/>
@@ -9240,16 +9282,16 @@
     </row>
     <row r="111">
       <c r="A111" s="57" t="s">
-        <v>223</v>
-      </c>
-      <c r="B111" s="57" t="s">
-        <v>484</v>
+        <v>259</v>
+      </c>
+      <c r="B111" s="50" t="s">
+        <v>495</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="D111" s="50" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="E111" s="51"/>
       <c r="F111" s="51"/>
@@ -9270,16 +9312,16 @@
     </row>
     <row r="112">
       <c r="A112" s="57" t="s">
-        <v>229</v>
-      </c>
-      <c r="B112" s="57" t="s">
-        <v>487</v>
+        <v>498</v>
+      </c>
+      <c r="B112" s="50" t="s">
+        <v>499</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="D112" s="50" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="E112" s="51"/>
       <c r="F112" s="51"/>
@@ -9299,17 +9341,17 @@
       <c r="T112" s="51"/>
     </row>
     <row r="113">
-      <c r="A113" s="57" t="s">
-        <v>253</v>
-      </c>
-      <c r="B113" s="50" t="s">
-        <v>490</v>
-      </c>
-      <c r="C113" s="50" t="s">
-        <v>491</v>
-      </c>
-      <c r="D113" s="50" t="s">
-        <v>492</v>
+      <c r="A113" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="B113" s="55" t="s">
+        <v>502</v>
+      </c>
+      <c r="C113" s="55" t="s">
+        <v>503</v>
+      </c>
+      <c r="D113" s="55" t="s">
+        <v>504</v>
       </c>
       <c r="E113" s="51"/>
       <c r="F113" s="51"/>
@@ -9329,18 +9371,10 @@
       <c r="T113" s="51"/>
     </row>
     <row r="114">
-      <c r="A114" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="B114" s="50" t="s">
-        <v>493</v>
-      </c>
-      <c r="C114" s="50" t="s">
-        <v>494</v>
-      </c>
-      <c r="D114" s="50" t="s">
-        <v>495</v>
-      </c>
+      <c r="A114" s="65"/>
+      <c r="B114" s="66"/>
+      <c r="C114" s="66"/>
+      <c r="D114" s="66"/>
       <c r="E114" s="51"/>
       <c r="F114" s="51"/>
       <c r="G114" s="51"/>
@@ -9359,18 +9393,10 @@
       <c r="T114" s="51"/>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="B115" s="55" t="s">
-        <v>496</v>
-      </c>
-      <c r="C115" s="55" t="s">
-        <v>497</v>
-      </c>
-      <c r="D115" s="55" t="s">
-        <v>498</v>
-      </c>
+      <c r="A115" s="65"/>
+      <c r="B115" s="66"/>
+      <c r="C115" s="66"/>
+      <c r="D115" s="66"/>
       <c r="E115" s="51"/>
       <c r="F115" s="51"/>
       <c r="G115" s="51"/>
@@ -9389,10 +9415,12 @@
       <c r="T115" s="51"/>
     </row>
     <row r="116">
-      <c r="A116" s="64"/>
-      <c r="B116" s="65"/>
-      <c r="C116" s="65"/>
-      <c r="D116" s="65"/>
+      <c r="A116" s="65"/>
+      <c r="B116" s="56" t="s">
+        <v>505</v>
+      </c>
+      <c r="C116" s="56"/>
+      <c r="D116" s="56"/>
       <c r="E116" s="51"/>
       <c r="F116" s="51"/>
       <c r="G116" s="51"/>
@@ -9411,10 +9439,12 @@
       <c r="T116" s="51"/>
     </row>
     <row r="117">
-      <c r="A117" s="64"/>
-      <c r="B117" s="65"/>
-      <c r="C117" s="65"/>
-      <c r="D117" s="65"/>
+      <c r="A117" s="67"/>
+      <c r="B117" s="68"/>
+      <c r="C117" s="68" t="s">
+        <v>506</v>
+      </c>
+      <c r="D117" s="68"/>
       <c r="E117" s="51"/>
       <c r="F117" s="51"/>
       <c r="G117" s="51"/>
@@ -9433,12 +9463,18 @@
       <c r="T117" s="51"/>
     </row>
     <row r="118">
-      <c r="A118" s="64"/>
-      <c r="B118" s="56" t="s">
-        <v>499</v>
-      </c>
-      <c r="C118" s="56"/>
-      <c r="D118" s="56"/>
+      <c r="A118" s="57" t="s">
+        <v>507</v>
+      </c>
+      <c r="B118" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="C118" s="50" t="s">
+        <v>508</v>
+      </c>
+      <c r="D118" s="50" t="s">
+        <v>509</v>
+      </c>
       <c r="E118" s="51"/>
       <c r="F118" s="51"/>
       <c r="G118" s="51"/>
@@ -9457,12 +9493,18 @@
       <c r="T118" s="51"/>
     </row>
     <row r="119">
-      <c r="A119" s="66"/>
-      <c r="B119" s="67"/>
-      <c r="C119" s="67" t="s">
-        <v>500</v>
-      </c>
-      <c r="D119" s="67"/>
+      <c r="A119" s="57" t="s">
+        <v>510</v>
+      </c>
+      <c r="B119" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="C119" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="D119" s="50" t="s">
+        <v>511</v>
+      </c>
       <c r="E119" s="51"/>
       <c r="F119" s="51"/>
       <c r="G119" s="51"/>
@@ -9482,16 +9524,16 @@
     </row>
     <row r="120">
       <c r="A120" s="57" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B120" s="50" t="s">
-        <v>502</v>
+        <v>189</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>502</v>
+        <v>189</v>
       </c>
       <c r="D120" s="50" t="s">
-        <v>503</v>
+        <v>189</v>
       </c>
       <c r="E120" s="51"/>
       <c r="F120" s="51"/>
@@ -9512,16 +9554,16 @@
     </row>
     <row r="121">
       <c r="A121" s="57" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B121" s="50" t="s">
-        <v>182</v>
+        <v>514</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>182</v>
+        <v>515</v>
       </c>
       <c r="D121" s="50" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E121" s="51"/>
       <c r="F121" s="51"/>
@@ -9542,16 +9584,16 @@
     </row>
     <row r="122">
       <c r="A122" s="57" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B122" s="50" t="s">
-        <v>189</v>
+        <v>518</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>189</v>
+        <v>310</v>
       </c>
       <c r="D122" s="50" t="s">
-        <v>189</v>
+        <v>519</v>
       </c>
       <c r="E122" s="51"/>
       <c r="F122" s="51"/>
@@ -9572,16 +9614,16 @@
     </row>
     <row r="123">
       <c r="A123" s="57" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="B123" s="50" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>509</v>
+        <v>419</v>
       </c>
       <c r="D123" s="50" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E123" s="51"/>
       <c r="F123" s="51"/>
@@ -9602,16 +9644,16 @@
     </row>
     <row r="124">
       <c r="A124" s="57" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="B124" s="50" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>305</v>
+        <v>525</v>
       </c>
       <c r="D124" s="50" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="E124" s="51"/>
       <c r="F124" s="51"/>
@@ -9632,16 +9674,16 @@
     </row>
     <row r="125">
       <c r="A125" s="57" t="s">
-        <v>514</v>
+        <v>527</v>
       </c>
       <c r="B125" s="50" t="s">
-        <v>515</v>
+        <v>528</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>414</v>
+        <v>529</v>
       </c>
       <c r="D125" s="50" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="E125" s="51"/>
       <c r="F125" s="51"/>
@@ -9662,16 +9704,16 @@
     </row>
     <row r="126">
       <c r="A126" s="57" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="B126" s="50" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="D126" s="50" t="s">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="E126" s="51"/>
       <c r="F126" s="51"/>
@@ -9692,16 +9734,16 @@
     </row>
     <row r="127">
       <c r="A127" s="57" t="s">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="B127" s="50" t="s">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="D127" s="50" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="E127" s="51"/>
       <c r="F127" s="51"/>
@@ -9722,16 +9764,16 @@
     </row>
     <row r="128">
       <c r="A128" s="57" t="s">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B128" s="50" t="s">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="D128" s="50" t="s">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="E128" s="51"/>
       <c r="F128" s="51"/>
@@ -9752,16 +9794,16 @@
     </row>
     <row r="129">
       <c r="A129" s="57" t="s">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="B129" s="50" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="D129" s="50" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="E129" s="51"/>
       <c r="F129" s="51"/>
@@ -9782,16 +9824,16 @@
     </row>
     <row r="130">
       <c r="A130" s="57" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="B130" s="50" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="C130" s="50" t="s">
-        <v>535</v>
+        <v>308</v>
       </c>
       <c r="D130" s="50" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="E130" s="51"/>
       <c r="F130" s="51"/>
@@ -9812,16 +9854,16 @@
     </row>
     <row r="131">
       <c r="A131" s="57" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="B131" s="50" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C131" s="50" t="s">
-        <v>539</v>
+        <v>308</v>
       </c>
       <c r="D131" s="50" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="E131" s="51"/>
       <c r="F131" s="51"/>
@@ -9842,16 +9884,16 @@
     </row>
     <row r="132">
       <c r="A132" s="57" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B132" s="50" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="D132" s="50" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="E132" s="51"/>
       <c r="F132" s="51"/>
@@ -9872,16 +9914,16 @@
     </row>
     <row r="133">
       <c r="A133" s="57" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B133" s="50" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="D133" s="50" t="s">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="E133" s="51"/>
       <c r="F133" s="51"/>
@@ -9902,16 +9944,16 @@
     </row>
     <row r="134">
       <c r="A134" s="57" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B134" s="50" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>339</v>
+        <v>454</v>
       </c>
       <c r="D134" s="50" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="E134" s="51"/>
       <c r="F134" s="51"/>
@@ -9932,16 +9974,16 @@
     </row>
     <row r="135">
       <c r="A135" s="57" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B135" s="50" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>267</v>
+        <v>562</v>
       </c>
       <c r="D135" s="50" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="E135" s="51"/>
       <c r="F135" s="51"/>
@@ -9962,16 +10004,16 @@
     </row>
     <row r="136">
       <c r="A136" s="57" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="B136" s="50" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>449</v>
+        <v>566</v>
       </c>
       <c r="D136" s="50" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="E136" s="51"/>
       <c r="F136" s="51"/>
@@ -9992,16 +10034,16 @@
     </row>
     <row r="137">
       <c r="A137" s="57" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="B137" s="50" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="D137" s="50" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="E137" s="51"/>
       <c r="F137" s="51"/>
@@ -10022,16 +10064,16 @@
     </row>
     <row r="138">
       <c r="A138" s="57" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="B138" s="50" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="D138" s="50" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="E138" s="51"/>
       <c r="F138" s="51"/>
@@ -10052,16 +10094,16 @@
     </row>
     <row r="139">
       <c r="A139" s="57" t="s">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="B139" s="50" t="s">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="C139" s="50" t="s">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="D139" s="50" t="s">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="E139" s="51"/>
       <c r="F139" s="51"/>
@@ -10082,16 +10124,16 @@
     </row>
     <row r="140">
       <c r="A140" s="57" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="B140" s="50" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="C140" s="50" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="D140" s="50" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="E140" s="51"/>
       <c r="F140" s="51"/>
@@ -10112,16 +10154,16 @@
     </row>
     <row r="141">
       <c r="A141" s="57" t="s">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="B141" s="50" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="D141" s="50" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="E141" s="51"/>
       <c r="F141" s="51"/>
@@ -10142,16 +10184,16 @@
     </row>
     <row r="142">
       <c r="A142" s="57" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="B142" s="50" t="s">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="D142" s="50" t="s">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="E142" s="51"/>
       <c r="F142" s="51"/>
@@ -10172,16 +10214,16 @@
     </row>
     <row r="143">
       <c r="A143" s="57" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="B143" s="50" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="D143" s="50" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="E143" s="51"/>
       <c r="F143" s="51"/>
@@ -10202,16 +10244,16 @@
     </row>
     <row r="144">
       <c r="A144" s="57" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="B144" s="50" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D144" s="50" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="E144" s="51"/>
       <c r="F144" s="51"/>
@@ -10232,16 +10274,16 @@
     </row>
     <row r="145">
       <c r="A145" s="57" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="B145" s="50" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C145" s="50" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="D145" s="50" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="E145" s="51"/>
       <c r="F145" s="51"/>
@@ -10262,16 +10304,16 @@
     </row>
     <row r="146">
       <c r="A146" s="57" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="B146" s="50" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="C146" s="50" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="D146" s="50" t="s">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="E146" s="51"/>
       <c r="F146" s="51"/>
@@ -10292,16 +10334,16 @@
     </row>
     <row r="147">
       <c r="A147" s="57" t="s">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B147" s="50" t="s">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="C147" s="50" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="D147" s="50" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="E147" s="51"/>
       <c r="F147" s="51"/>
@@ -10322,16 +10364,16 @@
     </row>
     <row r="148">
       <c r="A148" s="57" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B148" s="50" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="C148" s="50" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="D148" s="50" t="s">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="E148" s="51"/>
       <c r="F148" s="51"/>
@@ -10352,16 +10394,16 @@
     </row>
     <row r="149">
       <c r="A149" s="57" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="B149" s="50" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="D149" s="50" t="s">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="E149" s="51"/>
       <c r="F149" s="51"/>
@@ -10382,16 +10424,16 @@
     </row>
     <row r="150">
       <c r="A150" s="57" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B150" s="50" t="s">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="D150" s="50" t="s">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="E150" s="51"/>
       <c r="F150" s="51"/>
@@ -10412,16 +10454,16 @@
     </row>
     <row r="151">
       <c r="A151" s="57" t="s">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B151" s="50" t="s">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="D151" s="50" t="s">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="E151" s="51"/>
       <c r="F151" s="51"/>
@@ -10442,16 +10484,16 @@
     </row>
     <row r="152">
       <c r="A152" s="57" t="s">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="B152" s="50" t="s">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>613</v>
+        <v>274</v>
       </c>
       <c r="D152" s="50" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="E152" s="51"/>
       <c r="F152" s="51"/>
@@ -10472,16 +10514,16 @@
     </row>
     <row r="153">
       <c r="A153" s="57" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="B153" s="50" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="C153" s="50" t="s">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="D153" s="50" t="s">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="E153" s="51"/>
       <c r="F153" s="51"/>
@@ -10502,16 +10544,16 @@
     </row>
     <row r="154">
       <c r="A154" s="57" t="s">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="B154" s="50" t="s">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="C154" s="50" t="s">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="D154" s="50" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
       <c r="E154" s="51"/>
       <c r="F154" s="51"/>
@@ -10532,16 +10574,16 @@
     </row>
     <row r="155">
       <c r="A155" s="57" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="B155" s="50" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>269</v>
+        <v>638</v>
       </c>
       <c r="D155" s="50" t="s">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="E155" s="51"/>
       <c r="F155" s="51"/>
@@ -10562,16 +10604,16 @@
     </row>
     <row r="156">
       <c r="A156" s="57" t="s">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="B156" s="50" t="s">
-        <v>627</v>
+        <v>641</v>
       </c>
       <c r="C156" s="50" t="s">
-        <v>628</v>
+        <v>642</v>
       </c>
       <c r="D156" s="50" t="s">
-        <v>629</v>
+        <v>643</v>
       </c>
       <c r="E156" s="51"/>
       <c r="F156" s="51"/>
@@ -10592,16 +10634,16 @@
     </row>
     <row r="157">
       <c r="A157" s="57" t="s">
-        <v>630</v>
+        <v>644</v>
       </c>
       <c r="B157" s="50" t="s">
-        <v>631</v>
+        <v>645</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>632</v>
+        <v>646</v>
       </c>
       <c r="D157" s="50" t="s">
-        <v>633</v>
+        <v>647</v>
       </c>
       <c r="E157" s="51"/>
       <c r="F157" s="51"/>
@@ -10622,16 +10664,16 @@
     </row>
     <row r="158">
       <c r="A158" s="57" t="s">
-        <v>634</v>
+        <v>648</v>
       </c>
       <c r="B158" s="50" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
       <c r="C158" s="50" t="s">
-        <v>636</v>
+        <v>650</v>
       </c>
       <c r="D158" s="50" t="s">
-        <v>637</v>
+        <v>651</v>
       </c>
       <c r="E158" s="51"/>
       <c r="F158" s="51"/>
@@ -10652,16 +10694,16 @@
     </row>
     <row r="159">
       <c r="A159" s="57" t="s">
-        <v>638</v>
+        <v>652</v>
       </c>
       <c r="B159" s="50" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="C159" s="50" t="s">
-        <v>640</v>
+        <v>654</v>
       </c>
       <c r="D159" s="50" t="s">
-        <v>641</v>
+        <v>655</v>
       </c>
       <c r="E159" s="51"/>
       <c r="F159" s="51"/>
@@ -10682,16 +10724,16 @@
     </row>
     <row r="160">
       <c r="A160" s="57" t="s">
-        <v>642</v>
+        <v>656</v>
       </c>
       <c r="B160" s="50" t="s">
-        <v>643</v>
+        <v>657</v>
       </c>
       <c r="C160" s="50" t="s">
-        <v>644</v>
+        <v>658</v>
       </c>
       <c r="D160" s="50" t="s">
-        <v>645</v>
+        <v>659</v>
       </c>
       <c r="E160" s="51"/>
       <c r="F160" s="51"/>
@@ -10712,16 +10754,16 @@
     </row>
     <row r="161">
       <c r="A161" s="57" t="s">
-        <v>646</v>
+        <v>660</v>
       </c>
       <c r="B161" s="50" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="C161" s="50" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="D161" s="50" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="E161" s="51"/>
       <c r="F161" s="51"/>
@@ -10742,16 +10784,16 @@
     </row>
     <row r="162">
       <c r="A162" s="57" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="B162" s="50" t="s">
-        <v>651</v>
+        <v>665</v>
       </c>
       <c r="C162" s="50" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="D162" s="50" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="E162" s="51"/>
       <c r="F162" s="51"/>
@@ -10772,16 +10814,16 @@
     </row>
     <row r="163">
       <c r="A163" s="57" t="s">
-        <v>654</v>
+        <v>668</v>
       </c>
       <c r="B163" s="50" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="C163" s="50" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="D163" s="50" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="E163" s="51"/>
       <c r="F163" s="51"/>
@@ -10802,16 +10844,16 @@
     </row>
     <row r="164">
       <c r="A164" s="57" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="B164" s="50" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="C164" s="50" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="D164" s="50" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="E164" s="51"/>
       <c r="F164" s="51"/>
@@ -10832,16 +10874,16 @@
     </row>
     <row r="165">
       <c r="A165" s="57" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="B165" s="50" t="s">
-        <v>663</v>
+        <v>677</v>
       </c>
       <c r="C165" s="50" t="s">
-        <v>664</v>
+        <v>678</v>
       </c>
       <c r="D165" s="50" t="s">
-        <v>665</v>
+        <v>679</v>
       </c>
       <c r="E165" s="51"/>
       <c r="F165" s="51"/>
@@ -10862,16 +10904,16 @@
     </row>
     <row r="166">
       <c r="A166" s="57" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="B166" s="50" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="C166" s="50" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="D166" s="50" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="E166" s="51"/>
       <c r="F166" s="51"/>
@@ -10892,16 +10934,16 @@
     </row>
     <row r="167">
       <c r="A167" s="57" t="s">
-        <v>670</v>
+        <v>684</v>
       </c>
       <c r="B167" s="50" t="s">
-        <v>671</v>
+        <v>685</v>
       </c>
       <c r="C167" s="50" t="s">
-        <v>672</v>
+        <v>686</v>
       </c>
       <c r="D167" s="50" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="E167" s="51"/>
       <c r="F167" s="51"/>
@@ -10922,16 +10964,16 @@
     </row>
     <row r="168">
       <c r="A168" s="57" t="s">
-        <v>674</v>
+        <v>688</v>
       </c>
       <c r="B168" s="50" t="s">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="C168" s="50" t="s">
-        <v>676</v>
+        <v>690</v>
       </c>
       <c r="D168" s="50" t="s">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="E168" s="51"/>
       <c r="F168" s="51"/>
@@ -10952,16 +10994,16 @@
     </row>
     <row r="169">
       <c r="A169" s="57" t="s">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="B169" s="50" t="s">
-        <v>679</v>
+        <v>693</v>
       </c>
       <c r="C169" s="50" t="s">
-        <v>680</v>
+        <v>398</v>
       </c>
       <c r="D169" s="50" t="s">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="E169" s="51"/>
       <c r="F169" s="51"/>
@@ -10982,16 +11024,16 @@
     </row>
     <row r="170">
       <c r="A170" s="57" t="s">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="B170" s="50" t="s">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="C170" s="50" t="s">
-        <v>684</v>
+        <v>394</v>
       </c>
       <c r="D170" s="50" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="E170" s="51"/>
       <c r="F170" s="51"/>
@@ -11012,16 +11054,16 @@
     </row>
     <row r="171">
       <c r="A171" s="57" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="B171" s="50" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="C171" s="50" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="D171" s="50" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="E171" s="51"/>
       <c r="F171" s="51"/>
@@ -11042,16 +11084,16 @@
     </row>
     <row r="172">
       <c r="A172" s="57" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="B172" s="50" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="C172" s="50" t="s">
-        <v>393</v>
+        <v>704</v>
       </c>
       <c r="D172" s="50" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="E172" s="51"/>
       <c r="F172" s="51"/>
@@ -11072,16 +11114,16 @@
     </row>
     <row r="173">
       <c r="A173" s="57" t="s">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="B173" s="50" t="s">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="C173" s="50" t="s">
-        <v>389</v>
+        <v>708</v>
       </c>
       <c r="D173" s="50" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="E173" s="51"/>
       <c r="F173" s="51"/>
@@ -11102,16 +11144,16 @@
     </row>
     <row r="174">
       <c r="A174" s="57" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="B174" s="50" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="C174" s="50" t="s">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="D174" s="50" t="s">
-        <v>699</v>
+        <v>713</v>
       </c>
       <c r="E174" s="51"/>
       <c r="F174" s="51"/>
@@ -11132,16 +11174,16 @@
     </row>
     <row r="175">
       <c r="A175" s="57" t="s">
-        <v>700</v>
+        <v>714</v>
       </c>
       <c r="B175" s="50" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="C175" s="50" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="D175" s="50" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="E175" s="51"/>
       <c r="F175" s="51"/>
@@ -11162,16 +11204,16 @@
     </row>
     <row r="176">
       <c r="A176" s="57" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="B176" s="50" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="C176" s="50" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="D176" s="50" t="s">
-        <v>707</v>
+        <v>721</v>
       </c>
       <c r="E176" s="51"/>
       <c r="F176" s="51"/>
@@ -11192,16 +11234,16 @@
     </row>
     <row r="177">
       <c r="A177" s="57" t="s">
-        <v>708</v>
+        <v>722</v>
       </c>
       <c r="B177" s="50" t="s">
-        <v>709</v>
+        <v>723</v>
       </c>
       <c r="C177" s="50" t="s">
-        <v>710</v>
+        <v>724</v>
       </c>
       <c r="D177" s="50" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="E177" s="51"/>
       <c r="F177" s="51"/>
@@ -11222,16 +11264,16 @@
     </row>
     <row r="178">
       <c r="A178" s="57" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="B178" s="50" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="C178" s="50" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="D178" s="50" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="E178" s="51"/>
       <c r="F178" s="51"/>
@@ -11252,16 +11294,16 @@
     </row>
     <row r="179">
       <c r="A179" s="57" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="B179" s="50" t="s">
-        <v>717</v>
+        <v>731</v>
       </c>
       <c r="C179" s="50" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="D179" s="50" t="s">
-        <v>719</v>
+        <v>733</v>
       </c>
       <c r="E179" s="51"/>
       <c r="F179" s="51"/>
@@ -11282,16 +11324,16 @@
     </row>
     <row r="180">
       <c r="A180" s="57" t="s">
-        <v>720</v>
+        <v>734</v>
       </c>
       <c r="B180" s="50" t="s">
-        <v>721</v>
+        <v>735</v>
       </c>
       <c r="C180" s="50" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="D180" s="50" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="E180" s="51"/>
       <c r="F180" s="51"/>
@@ -11312,16 +11354,16 @@
     </row>
     <row r="181">
       <c r="A181" s="57" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="B181" s="50" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="C181" s="50" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="D181" s="50" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="E181" s="51"/>
       <c r="F181" s="51"/>
@@ -11342,16 +11384,16 @@
     </row>
     <row r="182">
       <c r="A182" s="57" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="B182" s="50" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="C182" s="50" t="s">
-        <v>730</v>
+        <v>406</v>
       </c>
       <c r="D182" s="50" t="s">
-        <v>731</v>
+        <v>744</v>
       </c>
       <c r="E182" s="51"/>
       <c r="F182" s="51"/>
@@ -11372,16 +11414,16 @@
     </row>
     <row r="183">
       <c r="A183" s="57" t="s">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="B183" s="50" t="s">
-        <v>733</v>
+        <v>746</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="D183" s="50" t="s">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="E183" s="51"/>
       <c r="F183" s="51"/>
@@ -11402,16 +11444,16 @@
     </row>
     <row r="184">
       <c r="A184" s="57" t="s">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="B184" s="50" t="s">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="C184" s="50" t="s">
-        <v>738</v>
+        <v>408</v>
       </c>
       <c r="D184" s="50" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E184" s="51"/>
       <c r="F184" s="51"/>
@@ -11432,16 +11474,16 @@
     </row>
     <row r="185">
       <c r="A185" s="57" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="B185" s="50" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="C185" s="50" t="s">
-        <v>401</v>
+        <v>754</v>
       </c>
       <c r="D185" s="50" t="s">
-        <v>742</v>
+        <v>755</v>
       </c>
       <c r="E185" s="51"/>
       <c r="F185" s="51"/>
@@ -11462,16 +11504,16 @@
     </row>
     <row r="186">
       <c r="A186" s="57" t="s">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="B186" s="50" t="s">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="C186" s="50" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="D186" s="50" t="s">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="E186" s="51"/>
       <c r="F186" s="51"/>
@@ -11492,16 +11534,16 @@
     </row>
     <row r="187">
       <c r="A187" s="57" t="s">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="B187" s="50" t="s">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="C187" s="50" t="s">
-        <v>403</v>
+        <v>762</v>
       </c>
       <c r="D187" s="50" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="E187" s="51"/>
       <c r="F187" s="51"/>
@@ -11522,16 +11564,16 @@
     </row>
     <row r="188">
       <c r="A188" s="57" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="B188" s="50" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="C188" s="50" t="s">
-        <v>752</v>
+        <v>766</v>
       </c>
       <c r="D188" s="50" t="s">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="E188" s="51"/>
       <c r="F188" s="51"/>
@@ -11552,16 +11594,16 @@
     </row>
     <row r="189">
       <c r="A189" s="57" t="s">
-        <v>754</v>
+        <v>768</v>
       </c>
       <c r="B189" s="50" t="s">
-        <v>755</v>
+        <v>769</v>
       </c>
       <c r="C189" s="50" t="s">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="D189" s="50" t="s">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="E189" s="51"/>
       <c r="F189" s="51"/>
@@ -11582,16 +11624,16 @@
     </row>
     <row r="190">
       <c r="A190" s="57" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="B190" s="50" t="s">
-        <v>759</v>
+        <v>524</v>
       </c>
       <c r="C190" s="50" t="s">
-        <v>760</v>
+        <v>444</v>
       </c>
       <c r="D190" s="50" t="s">
-        <v>761</v>
+        <v>525</v>
       </c>
       <c r="E190" s="51"/>
       <c r="F190" s="51"/>
@@ -11612,16 +11654,16 @@
     </row>
     <row r="191">
       <c r="A191" s="57" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="B191" s="50" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="C191" s="50" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="D191" s="50" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="E191" s="51"/>
       <c r="F191" s="51"/>
@@ -11642,16 +11684,16 @@
     </row>
     <row r="192">
       <c r="A192" s="57" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="B192" s="50" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="C192" s="50" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="D192" s="50" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="E192" s="51"/>
       <c r="F192" s="51"/>
@@ -11672,16 +11714,16 @@
     </row>
     <row r="193">
       <c r="A193" s="57" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B193" s="50" t="s">
-        <v>518</v>
+        <v>782</v>
       </c>
       <c r="C193" s="50" t="s">
-        <v>439</v>
+        <v>783</v>
       </c>
       <c r="D193" s="50" t="s">
-        <v>519</v>
+        <v>784</v>
       </c>
       <c r="E193" s="51"/>
       <c r="F193" s="51"/>
@@ -11702,16 +11744,16 @@
     </row>
     <row r="194">
       <c r="A194" s="57" t="s">
-        <v>771</v>
+        <v>785</v>
       </c>
       <c r="B194" s="50" t="s">
-        <v>772</v>
+        <v>786</v>
       </c>
       <c r="C194" s="50" t="s">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="D194" s="50" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="E194" s="51"/>
       <c r="F194" s="51"/>
@@ -11732,16 +11774,16 @@
     </row>
     <row r="195">
       <c r="A195" s="57" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="B195" s="50" t="s">
-        <v>776</v>
+        <v>790</v>
       </c>
       <c r="C195" s="50" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="D195" s="50" t="s">
-        <v>778</v>
+        <v>792</v>
       </c>
       <c r="E195" s="51"/>
       <c r="F195" s="51"/>
@@ -11762,16 +11804,16 @@
     </row>
     <row r="196">
       <c r="A196" s="57" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="B196" s="50" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
       <c r="C196" s="50" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
       <c r="D196" s="50" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
       <c r="E196" s="51"/>
       <c r="F196" s="51"/>
@@ -11792,16 +11834,16 @@
     </row>
     <row r="197">
       <c r="A197" s="57" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
       <c r="B197" s="50" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
       <c r="C197" s="50" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
       <c r="D197" s="50" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
       <c r="E197" s="51"/>
       <c r="F197" s="51"/>
@@ -11822,16 +11864,16 @@
     </row>
     <row r="198">
       <c r="A198" s="57" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
       <c r="B198" s="50" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
       <c r="C198" s="50" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
       <c r="D198" s="50" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
       <c r="E198" s="51"/>
       <c r="F198" s="51"/>
@@ -11852,16 +11894,16 @@
     </row>
     <row r="199">
       <c r="A199" s="57" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
       <c r="B199" s="50" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
       <c r="C199" s="50" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="D199" s="50" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="E199" s="51"/>
       <c r="F199" s="51"/>
@@ -11882,16 +11924,16 @@
     </row>
     <row r="200">
       <c r="A200" s="57" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="B200" s="50" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="C200" s="50" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="D200" s="50" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="E200" s="51"/>
       <c r="F200" s="51"/>
@@ -11912,16 +11954,16 @@
     </row>
     <row r="201">
       <c r="A201" s="57" t="s">
-        <v>799</v>
+        <v>813</v>
       </c>
       <c r="B201" s="50" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
       <c r="C201" s="50" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="D201" s="50" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
       <c r="E201" s="51"/>
       <c r="F201" s="51"/>
@@ -11942,16 +11984,16 @@
     </row>
     <row r="202">
       <c r="A202" s="57" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
       <c r="B202" s="50" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="C202" s="50" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="D202" s="50" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
       <c r="E202" s="51"/>
       <c r="F202" s="51"/>
@@ -11972,16 +12014,16 @@
     </row>
     <row r="203">
       <c r="A203" s="57" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="B203" s="50" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="C203" s="50" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="D203" s="50" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
       <c r="E203" s="51"/>
       <c r="F203" s="51"/>
@@ -12002,16 +12044,16 @@
     </row>
     <row r="204">
       <c r="A204" s="57" t="s">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="B204" s="50" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
       <c r="C204" s="50" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="D204" s="50" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="E204" s="51"/>
       <c r="F204" s="51"/>
@@ -12032,16 +12074,16 @@
     </row>
     <row r="205">
       <c r="A205" s="57" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="B205" s="50" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="C205" s="50" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="D205" s="50" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
       <c r="E205" s="51"/>
       <c r="F205" s="51"/>
@@ -12062,16 +12104,16 @@
     </row>
     <row r="206">
       <c r="A206" s="57" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="B206" s="50" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="C206" s="50" t="s">
-        <v>821</v>
+        <v>460</v>
       </c>
       <c r="D206" s="50" t="s">
-        <v>822</v>
+        <v>835</v>
       </c>
       <c r="E206" s="51"/>
       <c r="F206" s="51"/>
@@ -12092,16 +12134,16 @@
     </row>
     <row r="207">
       <c r="A207" s="57" t="s">
-        <v>823</v>
+        <v>836</v>
       </c>
       <c r="B207" s="50" t="s">
-        <v>824</v>
+        <v>837</v>
       </c>
       <c r="C207" s="50" t="s">
-        <v>825</v>
+        <v>838</v>
       </c>
       <c r="D207" s="50" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="E207" s="51"/>
       <c r="F207" s="51"/>
@@ -12122,16 +12164,16 @@
     </row>
     <row r="208">
       <c r="A208" s="57" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="B208" s="50" t="s">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="C208" s="50" t="s">
-        <v>829</v>
+        <v>842</v>
       </c>
       <c r="D208" s="50" t="s">
-        <v>830</v>
+        <v>843</v>
       </c>
       <c r="E208" s="51"/>
       <c r="F208" s="51"/>
@@ -12152,16 +12194,16 @@
     </row>
     <row r="209">
       <c r="A209" s="57" t="s">
-        <v>831</v>
+        <v>844</v>
       </c>
       <c r="B209" s="50" t="s">
-        <v>832</v>
+        <v>845</v>
       </c>
       <c r="C209" s="50" t="s">
-        <v>455</v>
+        <v>846</v>
       </c>
       <c r="D209" s="50" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
       <c r="E209" s="51"/>
       <c r="F209" s="51"/>
@@ -12182,16 +12224,16 @@
     </row>
     <row r="210">
       <c r="A210" s="57" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="B210" s="50" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="C210" s="50" t="s">
-        <v>836</v>
+        <v>850</v>
       </c>
       <c r="D210" s="50" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="E210" s="51"/>
       <c r="F210" s="51"/>
@@ -12212,16 +12254,16 @@
     </row>
     <row r="211">
       <c r="A211" s="57" t="s">
-        <v>838</v>
+        <v>852</v>
       </c>
       <c r="B211" s="50" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="C211" s="50" t="s">
-        <v>840</v>
+        <v>462</v>
       </c>
       <c r="D211" s="50" t="s">
-        <v>841</v>
+        <v>854</v>
       </c>
       <c r="E211" s="51"/>
       <c r="F211" s="51"/>
@@ -12242,16 +12284,16 @@
     </row>
     <row r="212">
       <c r="A212" s="57" t="s">
-        <v>842</v>
+        <v>855</v>
       </c>
       <c r="B212" s="50" t="s">
-        <v>843</v>
+        <v>856</v>
       </c>
       <c r="C212" s="50" t="s">
-        <v>844</v>
+        <v>857</v>
       </c>
       <c r="D212" s="50" t="s">
-        <v>845</v>
+        <v>858</v>
       </c>
       <c r="E212" s="51"/>
       <c r="F212" s="51"/>
@@ -12272,16 +12314,16 @@
     </row>
     <row r="213">
       <c r="A213" s="57" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="B213" s="50" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="C213" s="50" t="s">
-        <v>848</v>
+        <v>861</v>
       </c>
       <c r="D213" s="50" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="E213" s="51"/>
       <c r="F213" s="51"/>
@@ -12302,16 +12344,16 @@
     </row>
     <row r="214">
       <c r="A214" s="57" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="B214" s="50" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="C214" s="50" t="s">
-        <v>457</v>
+        <v>864</v>
       </c>
       <c r="D214" s="50" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="E214" s="51"/>
       <c r="F214" s="51"/>
@@ -12332,16 +12374,16 @@
     </row>
     <row r="215">
       <c r="A215" s="57" t="s">
-        <v>853</v>
+        <v>866</v>
       </c>
       <c r="B215" s="50" t="s">
-        <v>854</v>
+        <v>867</v>
       </c>
       <c r="C215" s="50" t="s">
-        <v>855</v>
+        <v>417</v>
       </c>
       <c r="D215" s="50" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="E215" s="51"/>
       <c r="F215" s="51"/>
@@ -12362,16 +12404,16 @@
     </row>
     <row r="216">
       <c r="A216" s="57" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="B216" s="50" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="C216" s="50" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="D216" s="50" t="s">
-        <v>859</v>
+        <v>872</v>
       </c>
       <c r="E216" s="51"/>
       <c r="F216" s="51"/>
@@ -12392,16 +12434,16 @@
     </row>
     <row r="217">
       <c r="A217" s="57" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="B217" s="50" t="s">
-        <v>861</v>
+        <v>874</v>
       </c>
       <c r="C217" s="50" t="s">
-        <v>862</v>
+        <v>875</v>
       </c>
       <c r="D217" s="50" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="E217" s="51"/>
       <c r="F217" s="51"/>
@@ -12422,16 +12464,16 @@
     </row>
     <row r="218">
       <c r="A218" s="57" t="s">
-        <v>864</v>
+        <v>877</v>
       </c>
       <c r="B218" s="50" t="s">
-        <v>865</v>
+        <v>878</v>
       </c>
       <c r="C218" s="50" t="s">
-        <v>412</v>
+        <v>879</v>
       </c>
       <c r="D218" s="50" t="s">
-        <v>866</v>
+        <v>880</v>
       </c>
       <c r="E218" s="51"/>
       <c r="F218" s="51"/>
@@ -12452,16 +12494,16 @@
     </row>
     <row r="219">
       <c r="A219" s="57" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
       <c r="B219" s="50" t="s">
-        <v>868</v>
+        <v>882</v>
       </c>
       <c r="C219" s="50" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
       <c r="D219" s="50" t="s">
-        <v>870</v>
+        <v>884</v>
       </c>
       <c r="E219" s="51"/>
       <c r="F219" s="51"/>
@@ -12482,16 +12524,16 @@
     </row>
     <row r="220">
       <c r="A220" s="57" t="s">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="B220" s="50" t="s">
-        <v>872</v>
+        <v>886</v>
       </c>
       <c r="C220" s="50" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
       <c r="D220" s="50" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
       <c r="E220" s="51"/>
       <c r="F220" s="51"/>
@@ -12512,16 +12554,16 @@
     </row>
     <row r="221">
       <c r="A221" s="57" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
       <c r="B221" s="50" t="s">
-        <v>876</v>
+        <v>890</v>
       </c>
       <c r="C221" s="50" t="s">
-        <v>877</v>
+        <v>891</v>
       </c>
       <c r="D221" s="50" t="s">
-        <v>878</v>
+        <v>892</v>
       </c>
       <c r="E221" s="51"/>
       <c r="F221" s="51"/>
@@ -12542,16 +12584,16 @@
     </row>
     <row r="222">
       <c r="A222" s="57" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="B222" s="50" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="C222" s="50" t="s">
-        <v>881</v>
+        <v>895</v>
       </c>
       <c r="D222" s="50" t="s">
-        <v>882</v>
+        <v>896</v>
       </c>
       <c r="E222" s="51"/>
       <c r="F222" s="51"/>
@@ -12572,16 +12614,16 @@
     </row>
     <row r="223">
       <c r="A223" s="57" t="s">
-        <v>883</v>
+        <v>897</v>
       </c>
       <c r="B223" s="50" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="C223" s="50" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="D223" s="50" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="E223" s="51"/>
       <c r="F223" s="51"/>
@@ -12602,16 +12644,16 @@
     </row>
     <row r="224">
       <c r="A224" s="57" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="B224" s="50" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="C224" s="50" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="D224" s="50" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="E224" s="51"/>
       <c r="F224" s="51"/>
@@ -12632,16 +12674,16 @@
     </row>
     <row r="225">
       <c r="A225" s="57" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="B225" s="50" t="s">
-        <v>892</v>
+        <v>906</v>
       </c>
       <c r="C225" s="50" t="s">
-        <v>893</v>
+        <v>907</v>
       </c>
       <c r="D225" s="50" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="E225" s="51"/>
       <c r="F225" s="51"/>
@@ -12662,16 +12704,16 @@
     </row>
     <row r="226">
       <c r="A226" s="57" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="B226" s="50" t="s">
-        <v>896</v>
+        <v>910</v>
       </c>
       <c r="C226" s="50" t="s">
-        <v>897</v>
+        <v>911</v>
       </c>
       <c r="D226" s="50" t="s">
-        <v>898</v>
+        <v>912</v>
       </c>
       <c r="E226" s="51"/>
       <c r="F226" s="51"/>
@@ -12692,16 +12734,16 @@
     </row>
     <row r="227">
       <c r="A227" s="57" t="s">
-        <v>899</v>
+        <v>913</v>
       </c>
       <c r="B227" s="50" t="s">
-        <v>900</v>
+        <v>914</v>
       </c>
       <c r="C227" s="50" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="D227" s="50" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="E227" s="51"/>
       <c r="F227" s="51"/>
@@ -12722,16 +12764,16 @@
     </row>
     <row r="228">
       <c r="A228" s="57" t="s">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="B228" s="50" t="s">
-        <v>904</v>
+        <v>918</v>
       </c>
       <c r="C228" s="50" t="s">
-        <v>905</v>
+        <v>919</v>
       </c>
       <c r="D228" s="50" t="s">
-        <v>906</v>
+        <v>920</v>
       </c>
       <c r="E228" s="51"/>
       <c r="F228" s="51"/>
@@ -12752,16 +12794,16 @@
     </row>
     <row r="229">
       <c r="A229" s="57" t="s">
-        <v>907</v>
+        <v>921</v>
       </c>
       <c r="B229" s="50" t="s">
-        <v>908</v>
+        <v>922</v>
       </c>
       <c r="C229" s="50" t="s">
-        <v>909</v>
+        <v>923</v>
       </c>
       <c r="D229" s="50" t="s">
-        <v>910</v>
+        <v>924</v>
       </c>
       <c r="E229" s="51"/>
       <c r="F229" s="51"/>
@@ -12782,16 +12824,16 @@
     </row>
     <row r="230">
       <c r="A230" s="57" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="B230" s="50" t="s">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="C230" s="50" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="D230" s="50" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="E230" s="51"/>
       <c r="F230" s="51"/>
@@ -12812,16 +12854,16 @@
     </row>
     <row r="231">
       <c r="A231" s="57" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="B231" s="50" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="C231" s="50" t="s">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="D231" s="50" t="s">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="E231" s="51"/>
       <c r="F231" s="51"/>
@@ -12842,16 +12884,16 @@
     </row>
     <row r="232">
       <c r="A232" s="57" t="s">
-        <v>919</v>
+        <v>933</v>
       </c>
       <c r="B232" s="50" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
       <c r="C232" s="50" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="D232" s="50" t="s">
-        <v>922</v>
+        <v>936</v>
       </c>
       <c r="E232" s="51"/>
       <c r="F232" s="51"/>
@@ -12872,16 +12914,16 @@
     </row>
     <row r="233">
       <c r="A233" s="57" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="B233" s="50" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="C233" s="50" t="s">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="D233" s="50" t="s">
-        <v>926</v>
+        <v>940</v>
       </c>
       <c r="E233" s="51"/>
       <c r="F233" s="51"/>
@@ -12902,16 +12944,16 @@
     </row>
     <row r="234">
       <c r="A234" s="57" t="s">
-        <v>927</v>
+        <v>941</v>
       </c>
       <c r="B234" s="50" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="C234" s="50" t="s">
-        <v>929</v>
+        <v>943</v>
       </c>
       <c r="D234" s="50" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
       <c r="E234" s="51"/>
       <c r="F234" s="51"/>
@@ -12932,16 +12974,16 @@
     </row>
     <row r="235">
       <c r="A235" s="57" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="B235" s="50" t="s">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="C235" s="50" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="D235" s="50" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="E235" s="51"/>
       <c r="F235" s="51"/>
@@ -12962,16 +13004,16 @@
     </row>
     <row r="236">
       <c r="A236" s="57" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="B236" s="50" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="C236" s="50" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
       <c r="D236" s="50" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="E236" s="51"/>
       <c r="F236" s="51"/>
@@ -12992,16 +13034,16 @@
     </row>
     <row r="237">
       <c r="A237" s="57" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="B237" s="50" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
       <c r="C237" s="50" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="D237" s="50" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="E237" s="51"/>
       <c r="F237" s="51"/>
@@ -13022,16 +13064,16 @@
     </row>
     <row r="238">
       <c r="A238" s="57" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="B238" s="50" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
       <c r="C238" s="50" t="s">
-        <v>945</v>
+        <v>465</v>
       </c>
       <c r="D238" s="50" t="s">
-        <v>946</v>
+        <v>959</v>
       </c>
       <c r="E238" s="51"/>
       <c r="F238" s="51"/>
@@ -13052,16 +13094,16 @@
     </row>
     <row r="239">
       <c r="A239" s="57" t="s">
-        <v>947</v>
+        <v>960</v>
       </c>
       <c r="B239" s="50" t="s">
-        <v>948</v>
+        <v>961</v>
       </c>
       <c r="C239" s="50" t="s">
-        <v>949</v>
+        <v>962</v>
       </c>
       <c r="D239" s="50" t="s">
-        <v>950</v>
+        <v>963</v>
       </c>
       <c r="E239" s="51"/>
       <c r="F239" s="51"/>
@@ -13082,16 +13124,16 @@
     </row>
     <row r="240">
       <c r="A240" s="57" t="s">
-        <v>951</v>
+        <v>964</v>
       </c>
       <c r="B240" s="50" t="s">
-        <v>952</v>
+        <v>965</v>
       </c>
       <c r="C240" s="50" t="s">
-        <v>953</v>
+        <v>966</v>
       </c>
       <c r="D240" s="50" t="s">
-        <v>954</v>
+        <v>967</v>
       </c>
       <c r="E240" s="51"/>
       <c r="F240" s="51"/>
@@ -13112,16 +13154,16 @@
     </row>
     <row r="241">
       <c r="A241" s="57" t="s">
-        <v>955</v>
+        <v>968</v>
       </c>
       <c r="B241" s="50" t="s">
-        <v>956</v>
+        <v>969</v>
       </c>
       <c r="C241" s="50" t="s">
-        <v>460</v>
+        <v>970</v>
       </c>
       <c r="D241" s="50" t="s">
-        <v>957</v>
+        <v>971</v>
       </c>
       <c r="E241" s="51"/>
       <c r="F241" s="51"/>
@@ -13142,16 +13184,16 @@
     </row>
     <row r="242">
       <c r="A242" s="57" t="s">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="B242" s="50" t="s">
-        <v>959</v>
+        <v>973</v>
       </c>
       <c r="C242" s="50" t="s">
-        <v>960</v>
+        <v>476</v>
       </c>
       <c r="D242" s="50" t="s">
-        <v>961</v>
+        <v>974</v>
       </c>
       <c r="E242" s="51"/>
       <c r="F242" s="51"/>
@@ -13172,16 +13214,16 @@
     </row>
     <row r="243">
       <c r="A243" s="57" t="s">
-        <v>962</v>
+        <v>975</v>
       </c>
       <c r="B243" s="50" t="s">
-        <v>963</v>
+        <v>973</v>
       </c>
       <c r="C243" s="50" t="s">
-        <v>964</v>
+        <v>476</v>
       </c>
       <c r="D243" s="50" t="s">
-        <v>965</v>
+        <v>974</v>
       </c>
       <c r="E243" s="51"/>
       <c r="F243" s="51"/>
@@ -13202,16 +13244,16 @@
     </row>
     <row r="244">
       <c r="A244" s="57" t="s">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="B244" s="50" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="C244" s="50" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="D244" s="50" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="E244" s="51"/>
       <c r="F244" s="51"/>
@@ -13232,16 +13274,16 @@
     </row>
     <row r="245">
       <c r="A245" s="57" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="B245" s="50" t="s">
-        <v>971</v>
+        <v>981</v>
       </c>
       <c r="C245" s="50" t="s">
-        <v>471</v>
+        <v>981</v>
       </c>
       <c r="D245" s="50" t="s">
-        <v>972</v>
+        <v>981</v>
       </c>
       <c r="E245" s="51"/>
       <c r="F245" s="51"/>
@@ -13262,16 +13304,16 @@
     </row>
     <row r="246">
       <c r="A246" s="57" t="s">
-        <v>973</v>
+        <v>982</v>
       </c>
       <c r="B246" s="50" t="s">
-        <v>971</v>
+        <v>983</v>
       </c>
       <c r="C246" s="50" t="s">
-        <v>471</v>
+        <v>984</v>
       </c>
       <c r="D246" s="50" t="s">
-        <v>972</v>
+        <v>985</v>
       </c>
       <c r="E246" s="51"/>
       <c r="F246" s="51"/>
@@ -13292,16 +13334,16 @@
     </row>
     <row r="247">
       <c r="A247" s="57" t="s">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="B247" s="50" t="s">
-        <v>975</v>
+        <v>987</v>
       </c>
       <c r="C247" s="50" t="s">
-        <v>976</v>
+        <v>988</v>
       </c>
       <c r="D247" s="50" t="s">
-        <v>977</v>
+        <v>989</v>
       </c>
       <c r="E247" s="51"/>
       <c r="F247" s="51"/>
@@ -13322,16 +13364,16 @@
     </row>
     <row r="248">
       <c r="A248" s="57" t="s">
-        <v>978</v>
+        <v>990</v>
       </c>
       <c r="B248" s="50" t="s">
-        <v>979</v>
+        <v>991</v>
       </c>
       <c r="C248" s="50" t="s">
-        <v>979</v>
+        <v>992</v>
       </c>
       <c r="D248" s="50" t="s">
-        <v>979</v>
+        <v>993</v>
       </c>
       <c r="E248" s="51"/>
       <c r="F248" s="51"/>
@@ -13352,16 +13394,16 @@
     </row>
     <row r="249">
       <c r="A249" s="57" t="s">
-        <v>980</v>
+        <v>994</v>
       </c>
       <c r="B249" s="50" t="s">
-        <v>981</v>
+        <v>995</v>
       </c>
       <c r="C249" s="50" t="s">
-        <v>982</v>
+        <v>996</v>
       </c>
       <c r="D249" s="50" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="E249" s="51"/>
       <c r="F249" s="51"/>
@@ -13382,16 +13424,16 @@
     </row>
     <row r="250">
       <c r="A250" s="57" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
       <c r="B250" s="50" t="s">
-        <v>985</v>
+        <v>999</v>
       </c>
       <c r="C250" s="50" t="s">
-        <v>986</v>
+        <v>1000</v>
       </c>
       <c r="D250" s="50" t="s">
-        <v>987</v>
+        <v>1001</v>
       </c>
       <c r="E250" s="51"/>
       <c r="F250" s="51"/>
@@ -13412,16 +13454,16 @@
     </row>
     <row r="251">
       <c r="A251" s="57" t="s">
-        <v>988</v>
+        <v>1002</v>
       </c>
       <c r="B251" s="50" t="s">
-        <v>989</v>
+        <v>1003</v>
       </c>
       <c r="C251" s="50" t="s">
-        <v>990</v>
+        <v>1004</v>
       </c>
       <c r="D251" s="50" t="s">
-        <v>991</v>
+        <v>1005</v>
       </c>
       <c r="E251" s="51"/>
       <c r="F251" s="51"/>
@@ -13442,16 +13484,16 @@
     </row>
     <row r="252">
       <c r="A252" s="57" t="s">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="B252" s="50" t="s">
-        <v>993</v>
+        <v>1007</v>
       </c>
       <c r="C252" s="50" t="s">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="D252" s="50" t="s">
-        <v>995</v>
+        <v>1009</v>
       </c>
       <c r="E252" s="51"/>
       <c r="F252" s="51"/>
@@ -13472,16 +13514,16 @@
     </row>
     <row r="253">
       <c r="A253" s="57" t="s">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="B253" s="50" t="s">
-        <v>997</v>
+        <v>1011</v>
       </c>
       <c r="C253" s="50" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
       <c r="D253" s="50" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="E253" s="51"/>
       <c r="F253" s="51"/>
@@ -13502,16 +13544,16 @@
     </row>
     <row r="254">
       <c r="A254" s="57" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="B254" s="50" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="C254" s="50" t="s">
-        <v>1002</v>
+        <v>1016</v>
       </c>
       <c r="D254" s="50" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="E254" s="51"/>
       <c r="F254" s="51"/>
@@ -13532,16 +13574,16 @@
     </row>
     <row r="255">
       <c r="A255" s="57" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="B255" s="50" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
       <c r="C255" s="50" t="s">
-        <v>1006</v>
+        <v>1020</v>
       </c>
       <c r="D255" s="50" t="s">
-        <v>1007</v>
+        <v>1021</v>
       </c>
       <c r="E255" s="51"/>
       <c r="F255" s="51"/>
@@ -13562,16 +13604,16 @@
     </row>
     <row r="256">
       <c r="A256" s="57" t="s">
-        <v>1008</v>
+        <v>1022</v>
       </c>
       <c r="B256" s="50" t="s">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="C256" s="50" t="s">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="D256" s="50" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="E256" s="51"/>
       <c r="F256" s="51"/>
@@ -13592,16 +13634,16 @@
     </row>
     <row r="257">
       <c r="A257" s="57" t="s">
-        <v>1012</v>
+        <v>1026</v>
       </c>
       <c r="B257" s="50" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="C257" s="50" t="s">
-        <v>1014</v>
+        <v>1028</v>
       </c>
       <c r="D257" s="50" t="s">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="E257" s="51"/>
       <c r="F257" s="51"/>
@@ -13622,16 +13664,16 @@
     </row>
     <row r="258">
       <c r="A258" s="57" t="s">
-        <v>1016</v>
+        <v>1030</v>
       </c>
       <c r="B258" s="50" t="s">
-        <v>1017</v>
+        <v>1031</v>
       </c>
       <c r="C258" s="50" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="D258" s="50" t="s">
-        <v>1019</v>
+        <v>1033</v>
       </c>
       <c r="E258" s="51"/>
       <c r="F258" s="51"/>
@@ -13652,16 +13694,16 @@
     </row>
     <row r="259">
       <c r="A259" s="57" t="s">
-        <v>1020</v>
+        <v>1034</v>
       </c>
       <c r="B259" s="50" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="C259" s="50" t="s">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="D259" s="50" t="s">
-        <v>1023</v>
+        <v>1037</v>
       </c>
       <c r="E259" s="51"/>
       <c r="F259" s="51"/>
@@ -13682,16 +13724,16 @@
     </row>
     <row r="260">
       <c r="A260" s="57" t="s">
-        <v>1024</v>
+        <v>1038</v>
       </c>
       <c r="B260" s="50" t="s">
-        <v>1025</v>
+        <v>1039</v>
       </c>
       <c r="C260" s="50" t="s">
-        <v>1026</v>
+        <v>1040</v>
       </c>
       <c r="D260" s="50" t="s">
-        <v>1027</v>
+        <v>1041</v>
       </c>
       <c r="E260" s="51"/>
       <c r="F260" s="51"/>
@@ -13712,16 +13754,16 @@
     </row>
     <row r="261">
       <c r="A261" s="57" t="s">
-        <v>1028</v>
+        <v>1042</v>
       </c>
       <c r="B261" s="50" t="s">
-        <v>1029</v>
+        <v>1043</v>
       </c>
       <c r="C261" s="50" t="s">
-        <v>1030</v>
+        <v>1044</v>
       </c>
       <c r="D261" s="50" t="s">
-        <v>1031</v>
+        <v>1045</v>
       </c>
       <c r="E261" s="51"/>
       <c r="F261" s="51"/>
@@ -13742,16 +13784,16 @@
     </row>
     <row r="262">
       <c r="A262" s="57" t="s">
-        <v>1032</v>
+        <v>1046</v>
       </c>
       <c r="B262" s="50" t="s">
-        <v>1033</v>
+        <v>1047</v>
       </c>
       <c r="C262" s="50" t="s">
-        <v>1034</v>
+        <v>1048</v>
       </c>
       <c r="D262" s="50" t="s">
-        <v>1035</v>
+        <v>1049</v>
       </c>
       <c r="E262" s="51"/>
       <c r="F262" s="51"/>
@@ -13772,16 +13814,16 @@
     </row>
     <row r="263">
       <c r="A263" s="57" t="s">
-        <v>1036</v>
+        <v>1050</v>
       </c>
       <c r="B263" s="50" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="C263" s="50" t="s">
-        <v>1038</v>
+        <v>1052</v>
       </c>
       <c r="D263" s="50" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
       <c r="E263" s="51"/>
       <c r="F263" s="51"/>
@@ -13802,16 +13844,16 @@
     </row>
     <row r="264">
       <c r="A264" s="57" t="s">
-        <v>1040</v>
+        <v>1054</v>
       </c>
       <c r="B264" s="50" t="s">
-        <v>1041</v>
+        <v>1055</v>
       </c>
       <c r="C264" s="50" t="s">
-        <v>1042</v>
+        <v>1056</v>
       </c>
       <c r="D264" s="50" t="s">
-        <v>1043</v>
+        <v>1057</v>
       </c>
       <c r="E264" s="51"/>
       <c r="F264" s="51"/>
@@ -13832,16 +13874,16 @@
     </row>
     <row r="265">
       <c r="A265" s="57" t="s">
-        <v>1044</v>
+        <v>1058</v>
       </c>
       <c r="B265" s="50" t="s">
-        <v>1045</v>
+        <v>1059</v>
       </c>
       <c r="C265" s="50" t="s">
-        <v>1046</v>
+        <v>1060</v>
       </c>
       <c r="D265" s="50" t="s">
-        <v>1047</v>
+        <v>1061</v>
       </c>
       <c r="E265" s="51"/>
       <c r="F265" s="51"/>
@@ -13862,16 +13904,16 @@
     </row>
     <row r="266">
       <c r="A266" s="57" t="s">
-        <v>1048</v>
+        <v>1062</v>
       </c>
       <c r="B266" s="50" t="s">
-        <v>1049</v>
+        <v>1063</v>
       </c>
       <c r="C266" s="50" t="s">
-        <v>1050</v>
+        <v>1064</v>
       </c>
       <c r="D266" s="50" t="s">
-        <v>1051</v>
+        <v>1065</v>
       </c>
       <c r="E266" s="51"/>
       <c r="F266" s="51"/>
@@ -13892,16 +13934,16 @@
     </row>
     <row r="267">
       <c r="A267" s="57" t="s">
-        <v>1052</v>
+        <v>1066</v>
       </c>
       <c r="B267" s="50" t="s">
-        <v>1053</v>
+        <v>1067</v>
       </c>
       <c r="C267" s="50" t="s">
-        <v>1054</v>
+        <v>1068</v>
       </c>
       <c r="D267" s="50" t="s">
-        <v>1055</v>
+        <v>1069</v>
       </c>
       <c r="E267" s="51"/>
       <c r="F267" s="51"/>
@@ -13922,16 +13964,16 @@
     </row>
     <row r="268">
       <c r="A268" s="57" t="s">
-        <v>1056</v>
+        <v>1070</v>
       </c>
       <c r="B268" s="50" t="s">
-        <v>1057</v>
+        <v>1071</v>
       </c>
       <c r="C268" s="50" t="s">
-        <v>1058</v>
+        <v>249</v>
       </c>
       <c r="D268" s="50" t="s">
-        <v>1059</v>
+        <v>1072</v>
       </c>
       <c r="E268" s="51"/>
       <c r="F268" s="51"/>
@@ -13952,16 +13994,16 @@
     </row>
     <row r="269">
       <c r="A269" s="57" t="s">
-        <v>1060</v>
+        <v>1073</v>
       </c>
       <c r="B269" s="50" t="s">
-        <v>1061</v>
+        <v>1074</v>
       </c>
       <c r="C269" s="50" t="s">
-        <v>1062</v>
+        <v>1075</v>
       </c>
       <c r="D269" s="50" t="s">
-        <v>1063</v>
+        <v>1076</v>
       </c>
       <c r="E269" s="51"/>
       <c r="F269" s="51"/>
@@ -13981,17 +14023,17 @@
       <c r="T269" s="51"/>
     </row>
     <row r="270">
-      <c r="A270" s="57" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B270" s="50" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C270" s="50" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D270" s="50" t="s">
-        <v>1067</v>
+      <c r="A270" s="53" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B270" s="55" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C270" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D270" s="55" t="s">
+        <v>1072</v>
       </c>
       <c r="E270" s="51"/>
       <c r="F270" s="51"/>
@@ -14010,96 +14052,6 @@
       <c r="S270" s="51"/>
       <c r="T270" s="51"/>
     </row>
-    <row r="271">
-      <c r="A271" s="57" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B271" s="50" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C271" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="D271" s="50" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E271" s="51"/>
-      <c r="F271" s="51"/>
-      <c r="G271" s="51"/>
-      <c r="H271" s="51"/>
-      <c r="I271" s="51"/>
-      <c r="J271" s="51"/>
-      <c r="K271" s="51"/>
-      <c r="L271" s="51"/>
-      <c r="M271" s="51"/>
-      <c r="N271" s="51"/>
-      <c r="O271" s="51"/>
-      <c r="P271" s="51"/>
-      <c r="Q271" s="51"/>
-      <c r="R271" s="51"/>
-      <c r="S271" s="51"/>
-      <c r="T271" s="51"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="57" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B272" s="50" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C272" s="50" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D272" s="50" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E272" s="51"/>
-      <c r="F272" s="51"/>
-      <c r="G272" s="51"/>
-      <c r="H272" s="51"/>
-      <c r="I272" s="51"/>
-      <c r="J272" s="51"/>
-      <c r="K272" s="51"/>
-      <c r="L272" s="51"/>
-      <c r="M272" s="51"/>
-      <c r="N272" s="51"/>
-      <c r="O272" s="51"/>
-      <c r="P272" s="51"/>
-      <c r="Q272" s="51"/>
-      <c r="R272" s="51"/>
-      <c r="S272" s="51"/>
-      <c r="T272" s="51"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="53" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B273" s="55" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C273" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="D273" s="55" t="s">
-        <v>1070</v>
-      </c>
-      <c r="E273" s="51"/>
-      <c r="F273" s="51"/>
-      <c r="G273" s="51"/>
-      <c r="H273" s="51"/>
-      <c r="I273" s="51"/>
-      <c r="J273" s="51"/>
-      <c r="K273" s="51"/>
-      <c r="L273" s="51"/>
-      <c r="M273" s="51"/>
-      <c r="N273" s="51"/>
-      <c r="O273" s="51"/>
-      <c r="P273" s="51"/>
-      <c r="Q273" s="51"/>
-      <c r="R273" s="51"/>
-      <c r="S273" s="51"/>
-      <c r="T273" s="51"/>
-    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="F5:G5"/>
@@ -14116,14 +14068,13 @@
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:L12"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="F20:G20"/>
     <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="B118:D118"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/Assets/GameData/database.xlsx
+++ b/Assets/GameData/database.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization原始" sheetId="2" r:id="R313ca476662445e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="3" r:id="Rab2142660ec9402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization原始" sheetId="2" r:id="R16000d86134c4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Localization" sheetId="3" r:id="R26d37a12fe5f4489"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7881,17 +7881,17 @@
       <x:c r="T76" s="51"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="56" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="B77" s="62" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="C77" s="52" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D77" s="52" t="s">
-        <x:v>357</x:v>
+      <x:c r="A77" s="56" t="str">
+        <x:v>offering.title</x:v>
+      </x:c>
+      <x:c r="B77" s="62" t="str">
+        <x:v>Offering</x:v>
+      </x:c>
+      <x:c r="C77" s="52" t="str">
+        <x:v>供奉</x:v>
+      </x:c>
+      <x:c r="D77" s="52" t="str">
+        <x:v>捧げ物</x:v>
       </x:c>
       <x:c r="E77" s="53"/>
       <x:c r="F77" s="53"/>
@@ -7912,15 +7912,17 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="56" t="s">
-        <x:v>358</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B78" s="62" t="s">
-        <x:v>359</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C78" s="52" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D78" s="52"/>
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="D78" s="52" t="s">
+        <x:v>357</x:v>
+      </x:c>
       <x:c r="E78" s="53"/>
       <x:c r="F78" s="53"/>
       <x:c r="G78" s="53"/>
@@ -7940,13 +7942,13 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="56" t="s">
-        <x:v>360</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B79" s="62" t="s">
-        <x:v>350</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C79" s="52" t="s">
-        <x:v>116</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D79" s="52"/>
       <x:c r="E79" s="53"/>
@@ -7968,13 +7970,13 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="56" t="s">
-        <x:v>361</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B80" s="62" t="s">
-        <x:v>362</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C80" s="52" t="s">
-        <x:v>123</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D80" s="52"/>
       <x:c r="E80" s="53"/>
@@ -7996,13 +7998,13 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="56" t="s">
-        <x:v>363</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B81" s="62" t="s">
-        <x:v>364</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C81" s="52" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D81" s="52"/>
       <x:c r="E81" s="53"/>
@@ -8024,13 +8026,13 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="56" t="s">
-        <x:v>365</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B82" s="62" t="s">
-        <x:v>366</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C82" s="52" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D82" s="52"/>
       <x:c r="E82" s="53"/>
@@ -8052,17 +8054,15 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="56" t="s">
-        <x:v>367</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B83" s="62" t="s">
-        <x:v>368</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C83" s="52" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D83" s="52" t="s">
-        <x:v>369</x:v>
-      </x:c>
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="D83" s="52"/>
       <x:c r="E83" s="53"/>
       <x:c r="F83" s="53"/>
       <x:c r="G83" s="53"/>
@@ -8082,15 +8082,17 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="56" t="s">
-        <x:v>370</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B84" s="62" t="s">
-        <x:v>371</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C84" s="52" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="D84" s="52"/>
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D84" s="52" t="s">
+        <x:v>369</x:v>
+      </x:c>
       <x:c r="E84" s="53"/>
       <x:c r="F84" s="53"/>
       <x:c r="G84" s="53"/>
@@ -8109,11 +8111,15 @@
       <x:c r="T84" s="54"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="57"/>
+      <x:c r="A85" s="57" t="s">
+        <x:v>370</x:v>
+      </x:c>
       <x:c r="B85" s="57" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="C85" s="49"/>
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="C85" s="49" t="s">
+        <x:v>127</x:v>
+      </x:c>
       <x:c r="D85" s="49"/>
       <x:c r="E85" s="50"/>
       <x:c r="F85" s="50"/>
@@ -8133,15 +8139,11 @@
       <x:c r="T85" s="51"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="56" t="s">
-        <x:v>372</x:v>
-      </x:c>
+      <x:c r="A86" s="56"/>
       <x:c r="B86" s="62" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="C86" s="52" t="s">
-        <x:v>129</x:v>
-      </x:c>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C86" s="52"/>
       <x:c r="D86" s="52"/>
       <x:c r="E86" s="53"/>
       <x:c r="F86" s="53"/>
@@ -8161,11 +8163,15 @@
       <x:c r="T86" s="54"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="57"/>
+      <x:c r="A87" s="57" t="s">
+        <x:v>372</x:v>
+      </x:c>
       <x:c r="B87" s="49" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C87" s="49"/>
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C87" s="49" t="s">
+        <x:v>129</x:v>
+      </x:c>
       <x:c r="D87" s="49"/>
       <x:c r="E87" s="50"/>
       <x:c r="F87" s="50"/>
@@ -8185,15 +8191,11 @@
       <x:c r="T87" s="51"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="56" t="s">
-        <x:v>374</x:v>
-      </x:c>
+      <x:c r="A88" s="56"/>
       <x:c r="B88" s="63" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="C88" s="52" t="s">
-        <x:v>132</x:v>
-      </x:c>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C88" s="52"/>
       <x:c r="D88" s="52"/>
       <x:c r="E88" s="53"/>
       <x:c r="F88" s="53"/>
@@ -8214,13 +8216,13 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="56" t="s">
-        <x:v>376</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B89" s="63" t="s">
-        <x:v>377</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C89" s="52" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D89" s="52"/>
       <x:c r="E89" s="53"/>
@@ -8242,13 +8244,13 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="56" t="s">
-        <x:v>378</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B90" s="63" t="s">
-        <x:v>350</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C90" s="52" t="s">
-        <x:v>116</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D90" s="52"/>
       <x:c r="E90" s="53"/>
@@ -8270,13 +8272,13 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="56" t="s">
-        <x:v>379</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B91" s="63" t="s">
-        <x:v>380</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C91" s="52" t="s">
-        <x:v>137</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D91" s="52"/>
       <x:c r="E91" s="53"/>
@@ -8298,13 +8300,13 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="56" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B92" s="63" t="s">
         <x:v>380</x:v>
       </x:c>
       <x:c r="C92" s="52" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D92" s="52"/>
       <x:c r="E92" s="53"/>
@@ -8326,13 +8328,13 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="56" t="s">
-        <x:v>382</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B93" s="63" t="s">
-        <x:v>383</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C93" s="52" t="s">
-        <x:v>384</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D93" s="52"/>
       <x:c r="E93" s="58"/>
@@ -8354,13 +8356,13 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="56" t="s">
-        <x:v>385</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B94" s="63" t="s">
-        <x:v>386</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C94" s="52" t="s">
-        <x:v>143</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D94" s="52"/>
       <x:c r="E94" s="53"/>
@@ -8382,13 +8384,13 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="56" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B95" s="63" t="s">
-        <x:v>388</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C95" s="52" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D95" s="52"/>
       <x:c r="E95" s="53"/>
@@ -8410,13 +8412,13 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="56" t="s">
-        <x:v>389</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B96" s="63" t="s">
-        <x:v>390</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C96" s="52" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D96" s="52"/>
       <x:c r="E96" s="53"/>
@@ -8437,11 +8439,15 @@
       <x:c r="T96" s="54"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="57"/>
+      <x:c r="A97" s="57" t="s">
+        <x:v>389</x:v>
+      </x:c>
       <x:c r="B97" s="57" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="C97" s="49"/>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C97" s="49" t="s">
+        <x:v>147</x:v>
+      </x:c>
       <x:c r="D97" s="49"/>
       <x:c r="E97" s="50"/>
       <x:c r="F97" s="50"/>
@@ -8461,18 +8467,12 @@
       <x:c r="T97" s="51"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="56" t="s">
-        <x:v>391</x:v>
-      </x:c>
+      <x:c r="A98" s="56"/>
       <x:c r="B98" s="56" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="C98" s="52" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="D98" s="52" t="s">
-        <x:v>393</x:v>
-      </x:c>
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="C98" s="52"/>
+      <x:c r="D98" s="52"/>
       <x:c r="E98" s="53"/>
       <x:c r="F98" s="53"/>
       <x:c r="G98" s="53"/>
@@ -8491,12 +8491,18 @@
       <x:c r="T98" s="54"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="57"/>
+      <x:c r="A99" s="57" t="s">
+        <x:v>391</x:v>
+      </x:c>
       <x:c r="B99" s="49" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C99" s="49"/>
-      <x:c r="D99" s="49"/>
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="C99" s="49" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="D99" s="49" t="s">
+        <x:v>393</x:v>
+      </x:c>
       <x:c r="E99" s="50"/>
       <x:c r="F99" s="50"/>
       <x:c r="G99" s="50"/>
@@ -8515,18 +8521,12 @@
       <x:c r="T99" s="51"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="56" t="s">
-        <x:v>394</x:v>
-      </x:c>
+      <x:c r="A100" s="56"/>
       <x:c r="B100" s="52" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="C100" s="52" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="D100" s="52" t="s">
-        <x:v>396</x:v>
-      </x:c>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C100" s="52"/>
+      <x:c r="D100" s="52"/>
       <x:c r="E100" s="53"/>
       <x:c r="F100" s="53"/>
       <x:c r="G100" s="53"/>
@@ -8546,16 +8546,16 @@
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="56" t="s">
-        <x:v>397</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B101" s="52" t="s">
-        <x:v>398</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C101" s="52" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D101" s="52" t="s">
-        <x:v>399</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="E101" s="53"/>
       <x:c r="F101" s="53"/>
@@ -8576,16 +8576,16 @@
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="56" t="s">
-        <x:v>400</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B102" s="52" t="s">
-        <x:v>401</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C102" s="52" t="s">
-        <x:v>402</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D102" s="52" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E102" s="53"/>
       <x:c r="F102" s="53"/>
@@ -8606,16 +8606,16 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="56" t="s">
-        <x:v>404</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B103" s="52" t="s">
-        <x:v>405</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C103" s="52" t="s">
-        <x:v>406</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="D103" s="52" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="E103" s="53"/>
       <x:c r="F103" s="53"/>
@@ -8636,16 +8636,16 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="56" t="s">
-        <x:v>21</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B104" s="56" t="s">
-        <x:v>153</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C104" s="52" t="s">
-        <x:v>154</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="D104" s="52" t="s">
-        <x:v>155</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="E104" s="53"/>
       <x:c r="F104" s="53"/>
@@ -8666,16 +8666,16 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="56" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B105" s="56" t="s">
-        <x:v>156</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="52" t="s">
-        <x:v>157</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D105" s="52" t="s">
-        <x:v>158</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="E105" s="53"/>
       <x:c r="F105" s="53"/>
@@ -8696,16 +8696,16 @@
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="56" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B106" s="56" t="s">
-        <x:v>159</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C106" s="52" t="s">
-        <x:v>160</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="D106" s="52" t="s">
-        <x:v>161</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="E106" s="53"/>
       <x:c r="F106" s="53"/>
@@ -8726,16 +8726,16 @@
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="56" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B107" s="56" t="s">
-        <x:v>162</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C107" s="52" t="s">
-        <x:v>163</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D107" s="52" t="s">
-        <x:v>164</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="E107" s="53"/>
       <x:c r="F107" s="53"/>
@@ -8756,16 +8756,16 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="56" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B108" s="56" t="s">
-        <x:v>165</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C108" s="52" t="s">
-        <x:v>166</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D108" s="52" t="s">
-        <x:v>167</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E108" s="53"/>
       <x:c r="F108" s="53"/>
@@ -8786,16 +8786,16 @@
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="56" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B109" s="56" t="s">
-        <x:v>168</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C109" s="52" t="s">
-        <x:v>169</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="D109" s="52" t="s">
-        <x:v>170</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="E109" s="53"/>
       <x:c r="F109" s="53"/>
@@ -8816,16 +8816,16 @@
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="56" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B110" s="52" t="s">
-        <x:v>171</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C110" s="52" t="s">
-        <x:v>172</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="D110" s="52" t="s">
-        <x:v>173</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="E110" s="53"/>
       <x:c r="F110" s="53"/>
@@ -8846,16 +8846,16 @@
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="56" t="s">
-        <x:v>408</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B111" s="52" t="s">
-        <x:v>174</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C111" s="52" t="s">
-        <x:v>175</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="D111" s="52" t="s">
-        <x:v>176</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E111" s="53"/>
       <x:c r="F111" s="53"/>
@@ -8876,16 +8876,16 @@
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="56" t="s">
-        <x:v>52</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B112" s="52" t="s">
-        <x:v>177</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C112" s="52" t="s">
-        <x:v>178</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D112" s="52" t="s">
-        <x:v>179</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E112" s="53"/>
       <x:c r="F112" s="53"/>
@@ -8905,12 +8905,18 @@
       <x:c r="T112" s="54"/>
     </x:row>
     <x:row r="113">
-      <x:c r="A113" s="65"/>
+      <x:c r="A113" s="65" t="s">
+        <x:v>52</x:v>
+      </x:c>
       <x:c r="B113" s="57" t="s">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="C113" s="57"/>
-      <x:c r="D113" s="57"/>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C113" s="57" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="D113" s="57" t="s">
+        <x:v>179</x:v>
+      </x:c>
       <x:c r="E113" s="53"/>
       <x:c r="F113" s="53"/>
       <x:c r="G113" s="53"/>
@@ -8930,10 +8936,10 @@
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="66"/>
-      <x:c r="B114" s="67"/>
-      <x:c r="C114" s="67" t="s">
-        <x:v>410</x:v>
-      </x:c>
+      <x:c r="B114" s="67" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="C114" s="67"/>
       <x:c r="D114" s="67"/>
       <x:c r="E114" s="53"/>
       <x:c r="F114" s="53"/>
@@ -8953,18 +8959,12 @@
       <x:c r="T114" s="54"/>
     </x:row>
     <x:row r="115">
-      <x:c r="A115" s="56" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="B115" s="52" t="s">
-        <x:v>412</x:v>
-      </x:c>
+      <x:c r="A115" s="56"/>
+      <x:c r="B115" s="52"/>
       <x:c r="C115" s="52" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="D115" s="52" t="s">
-        <x:v>413</x:v>
-      </x:c>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="D115" s="52"/>
       <x:c r="E115" s="53"/>
       <x:c r="F115" s="53"/>
       <x:c r="G115" s="53"/>
@@ -8984,16 +8984,16 @@
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="56" t="s">
-        <x:v>414</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B116" s="52" t="s">
-        <x:v>1</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C116" s="52" t="s">
-        <x:v>1</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="D116" s="52" t="s">
-        <x:v>415</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="E116" s="53"/>
       <x:c r="F116" s="53"/>
@@ -9014,16 +9014,16 @@
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="56" t="s">
-        <x:v>416</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B117" s="52" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C117" s="52" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D117" s="52" t="s">
-        <x:v>8</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="E117" s="53"/>
       <x:c r="F117" s="53"/>
@@ -9044,16 +9044,16 @@
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="56" t="s">
-        <x:v>417</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B118" s="52" t="s">
-        <x:v>418</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C118" s="52" t="s">
-        <x:v>419</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D118" s="52" t="s">
-        <x:v>420</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E118" s="53"/>
       <x:c r="F118" s="53"/>
@@ -9074,16 +9074,16 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="56" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B119" s="52" t="s">
-        <x:v>256</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C119" s="52" t="s">
-        <x:v>72</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="D119" s="52" t="s">
-        <x:v>422</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="E119" s="53"/>
       <x:c r="F119" s="53"/>
@@ -9104,16 +9104,16 @@
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="56" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B120" s="52" t="s">
-        <x:v>350</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C120" s="52" t="s">
-        <x:v>116</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D120" s="52" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="E120" s="53"/>
       <x:c r="F120" s="53"/>
@@ -9134,16 +9134,16 @@
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="56" t="s">
-        <x:v>425</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B121" s="52" t="s">
-        <x:v>426</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C121" s="52" t="s">
-        <x:v>427</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D121" s="52" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="E121" s="53"/>
       <x:c r="F121" s="53"/>
@@ -9164,16 +9164,16 @@
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="56" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B122" s="52" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C122" s="52" t="s">
-        <x:v>431</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="D122" s="52" t="s">
-        <x:v>432</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="E122" s="53"/>
       <x:c r="F122" s="53"/>
@@ -9194,16 +9194,16 @@
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="56" t="s">
-        <x:v>433</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B123" s="52" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C123" s="52" t="s">
-        <x:v>435</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="D123" s="52" t="s">
-        <x:v>436</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="E123" s="53"/>
       <x:c r="F123" s="53"/>
@@ -9224,16 +9224,16 @@
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="56" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B124" s="52" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C124" s="52" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="D124" s="52" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="E124" s="53"/>
       <x:c r="F124" s="53"/>
@@ -9254,16 +9254,16 @@
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="68" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B125" s="69" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C125" s="69" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="D125" s="69" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="E125" s="70"/>
       <x:c r="F125" s="70"/>
@@ -9284,16 +9284,16 @@
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="56" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B126" s="52" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C126" s="52" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="D126" s="52" t="s">
-        <x:v>447</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="E126" s="53"/>
       <x:c r="F126" s="53"/>
@@ -9314,16 +9314,16 @@
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="56" t="s">
-        <x:v>448</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B127" s="52" t="s">
-        <x:v>449</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C127" s="52" t="s">
-        <x:v>71</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="D127" s="52" t="s">
-        <x:v>450</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E127" s="53"/>
       <x:c r="F127" s="53"/>
@@ -9344,10 +9344,10 @@
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="56" t="s">
-        <x:v>451</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B128" s="52" t="s">
-        <x:v>254</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C128" s="52" t="s">
         <x:v>71</x:v>
@@ -9374,16 +9374,16 @@
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="56" t="s">
-        <x:v>452</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B129" s="52" t="s">
-        <x:v>453</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C129" s="52" t="s">
-        <x:v>82</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D129" s="52" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="E129" s="53"/>
       <x:c r="F129" s="53"/>
@@ -9404,16 +9404,16 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="56" t="s">
-        <x:v>455</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B130" s="52" t="s">
-        <x:v>223</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C130" s="52" t="s">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D130" s="52" t="s">
-        <x:v>456</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="E130" s="53"/>
       <x:c r="F130" s="53"/>
@@ -9434,16 +9434,16 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="56" t="s">
-        <x:v>457</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B131" s="52" t="s">
-        <x:v>380</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C131" s="52" t="s">
-        <x:v>137</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D131" s="52" t="s">
-        <x:v>458</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="E131" s="53"/>
       <x:c r="F131" s="53"/>
@@ -9464,16 +9464,16 @@
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="68" t="s">
-        <x:v>459</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B132" s="69" t="s">
-        <x:v>460</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C132" s="69" t="s">
-        <x:v>461</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D132" s="69" t="s">
-        <x:v>462</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="E132" s="70"/>
       <x:c r="F132" s="70"/>
@@ -9494,16 +9494,16 @@
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="68" t="s">
-        <x:v>463</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B133" s="69" t="s">
-        <x:v>464</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C133" s="69" t="s">
-        <x:v>465</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="D133" s="69" t="s">
-        <x:v>466</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="E133" s="70"/>
       <x:c r="F133" s="70"/>
@@ -9524,16 +9524,16 @@
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="56" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B134" s="52" t="s">
-        <x:v>468</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C134" s="52" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="D134" s="52" t="s">
-        <x:v>470</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="E134" s="53"/>
       <x:c r="F134" s="53"/>
@@ -9554,16 +9554,16 @@
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="56" t="s">
-        <x:v>471</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="B135" s="52" t="s">
-        <x:v>472</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="C135" s="52" t="s">
-        <x:v>473</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="D135" s="52" t="s">
-        <x:v>473</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="E135" s="53"/>
       <x:c r="F135" s="53"/>
@@ -9584,16 +9584,16 @@
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="56" t="s">
-        <x:v>474</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="B136" s="52" t="s">
-        <x:v>475</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="C136" s="52" t="s">
-        <x:v>476</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="D136" s="52" t="s">
-        <x:v>477</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="E136" s="53"/>
       <x:c r="F136" s="53"/>
@@ -9614,16 +9614,16 @@
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="56" t="s">
-        <x:v>478</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B137" s="60" t="s">
-        <x:v>479</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C137" s="55" t="s">
-        <x:v>480</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D137" s="52" t="s">
-        <x:v>481</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E137" s="53"/>
       <x:c r="F137" s="53"/>
@@ -9644,16 +9644,16 @@
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="56" t="s">
-        <x:v>482</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B138" s="52" t="s">
-        <x:v>483</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C138" s="52" t="s">
-        <x:v>484</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D138" s="52" t="s">
-        <x:v>485</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E138" s="53"/>
       <x:c r="F138" s="53"/>
@@ -9674,16 +9674,16 @@
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="56" t="s">
-        <x:v>486</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B139" s="55" t="s">
-        <x:v>487</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C139" s="55" t="s">
-        <x:v>488</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D139" s="52" t="s">
-        <x:v>489</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E139" s="53"/>
       <x:c r="F139" s="53"/>
@@ -9704,16 +9704,16 @@
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="56" t="s">
-        <x:v>490</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B140" s="52" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="C140" s="52" t="s">
-        <x:v>491</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="D140" s="52" t="s">
-        <x:v>491</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="E140" s="53"/>
       <x:c r="F140" s="53"/>
@@ -9734,16 +9734,16 @@
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="56" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B141" s="52" t="s">
-        <x:v>493</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C141" s="52" t="s">
-        <x:v>494</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="D141" s="52" t="s">
-        <x:v>495</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="E141" s="53"/>
       <x:c r="F141" s="53"/>
@@ -9764,16 +9764,16 @@
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="56" t="s">
-        <x:v>496</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="B142" s="52" t="s">
-        <x:v>497</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="C142" s="52" t="s">
-        <x:v>498</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="D142" s="52" t="s">
-        <x:v>499</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="E142" s="53"/>
       <x:c r="F142" s="53"/>
@@ -9794,16 +9794,16 @@
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="56" t="s">
-        <x:v>500</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="B143" s="52" t="s">
-        <x:v>501</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C143" s="52" t="s">
-        <x:v>502</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="D143" s="52" t="s">
-        <x:v>503</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="E143" s="53"/>
       <x:c r="F143" s="53"/>
@@ -9824,16 +9824,16 @@
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="56" t="s">
-        <x:v>504</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="B144" s="55" t="s">
-        <x:v>505</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="C144" s="55" t="s">
-        <x:v>506</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="D144" s="52" t="s">
-        <x:v>507</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="E144" s="53"/>
       <x:c r="F144" s="53"/>
@@ -9854,16 +9854,16 @@
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="56" t="s">
-        <x:v>508</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="B145" s="55" t="s">
-        <x:v>509</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C145" s="52" t="s">
-        <x:v>510</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="D145" s="52" t="s">
-        <x:v>511</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="E145" s="53"/>
       <x:c r="F145" s="53"/>
@@ -9884,16 +9884,16 @@
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="56" t="s">
-        <x:v>512</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="B146" s="52" t="s">
-        <x:v>513</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="C146" s="52" t="s">
-        <x:v>514</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="D146" s="52" t="s">
-        <x:v>515</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="E146" s="53"/>
       <x:c r="F146" s="53"/>
@@ -9914,16 +9914,16 @@
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="56" t="s">
-        <x:v>516</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="B147" s="52" t="s">
-        <x:v>517</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C147" s="52" t="s">
-        <x:v>518</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="D147" s="52" t="s">
-        <x:v>519</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="E147" s="53"/>
       <x:c r="F147" s="53"/>
@@ -9944,16 +9944,16 @@
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="68" t="s">
-        <x:v>520</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B148" s="69" t="s">
-        <x:v>521</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C148" s="69" t="s">
-        <x:v>522</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="D148" s="69" t="s">
-        <x:v>523</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="E148" s="70"/>
       <x:c r="F148" s="70"/>
@@ -9974,16 +9974,16 @@
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="56" t="s">
-        <x:v>524</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B149" s="52" t="s">
-        <x:v>525</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="C149" s="52" t="s">
-        <x:v>58</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="D149" s="52" t="s">
-        <x:v>526</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="E149" s="53"/>
       <x:c r="F149" s="53"/>
@@ -10004,16 +10004,16 @@
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="56" t="s">
-        <x:v>527</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B150" s="52" t="s">
-        <x:v>528</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="C150" s="52" t="s">
-        <x:v>529</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D150" s="52" t="s">
-        <x:v>530</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="E150" s="53"/>
       <x:c r="F150" s="53"/>
@@ -10034,16 +10034,16 @@
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="56" t="s">
-        <x:v>531</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="B151" s="52" t="s">
-        <x:v>532</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="C151" s="52" t="s">
-        <x:v>533</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="D151" s="52" t="s">
-        <x:v>534</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="E151" s="53"/>
       <x:c r="F151" s="53"/>
@@ -10064,16 +10064,16 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="56" t="s">
-        <x:v>535</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B152" s="52" t="s">
-        <x:v>536</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C152" s="52" t="s">
-        <x:v>537</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D152" s="52" t="s">
-        <x:v>538</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="E152" s="53"/>
       <x:c r="F152" s="53"/>
@@ -10094,16 +10094,16 @@
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="56" t="s">
-        <x:v>539</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="B153" s="52" t="s">
-        <x:v>540</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="C153" s="52" t="s">
-        <x:v>541</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D153" s="52" t="s">
-        <x:v>542</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="E153" s="53"/>
       <x:c r="F153" s="53"/>
@@ -10124,16 +10124,16 @@
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="56" t="s">
-        <x:v>543</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="B154" s="52" t="s">
-        <x:v>544</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="C154" s="55" t="s">
-        <x:v>545</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="D154" s="52" t="s">
-        <x:v>546</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="E154" s="53"/>
       <x:c r="F154" s="53"/>
@@ -10154,16 +10154,16 @@
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="56" t="s">
-        <x:v>547</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="B155" s="52" t="s">
-        <x:v>548</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="C155" s="52" t="s">
-        <x:v>549</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="D155" s="52" t="s">
-        <x:v>550</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="E155" s="53"/>
       <x:c r="F155" s="53"/>
@@ -10184,16 +10184,16 @@
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="56" t="s">
-        <x:v>551</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="B156" s="52" t="s">
-        <x:v>552</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="C156" s="52" t="s">
-        <x:v>553</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="D156" s="52" t="s">
-        <x:v>554</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="E156" s="53"/>
       <x:c r="F156" s="53"/>
@@ -10214,16 +10214,16 @@
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="56" t="s">
-        <x:v>555</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="B157" s="52" t="s">
-        <x:v>556</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C157" s="52" t="s">
-        <x:v>557</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="D157" s="52" t="s">
-        <x:v>558</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="E157" s="53"/>
       <x:c r="F157" s="53"/>
@@ -10244,16 +10244,16 @@
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="56" t="s">
-        <x:v>559</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="B158" s="52" t="s">
-        <x:v>560</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="C158" s="52" t="s">
-        <x:v>561</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="D158" s="52" t="s">
-        <x:v>562</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="E158" s="53"/>
       <x:c r="F158" s="53"/>
@@ -10274,16 +10274,16 @@
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="56" t="s">
-        <x:v>563</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="B159" s="52" t="s">
-        <x:v>564</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="C159" s="52" t="s">
-        <x:v>565</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="D159" s="52" t="s">
-        <x:v>566</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="E159" s="53"/>
       <x:c r="F159" s="53"/>
@@ -10304,16 +10304,16 @@
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="56" t="s">
-        <x:v>567</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="B160" s="52" t="s">
-        <x:v>568</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C160" s="52" t="s">
-        <x:v>569</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D160" s="52" t="s">
-        <x:v>570</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="E160" s="53"/>
       <x:c r="F160" s="53"/>
@@ -10334,16 +10334,16 @@
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="56" t="s">
-        <x:v>571</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="B161" s="52" t="s">
-        <x:v>572</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C161" s="52" t="s">
-        <x:v>573</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="D161" s="52" t="s">
-        <x:v>574</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="E161" s="53"/>
       <x:c r="F161" s="53"/>
@@ -10364,16 +10364,16 @@
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="56" t="s">
-        <x:v>575</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="B162" s="52" t="s">
-        <x:v>576</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="C162" s="52" t="s">
-        <x:v>577</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="D162" s="52" t="s">
-        <x:v>578</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="E162" s="53"/>
       <x:c r="F162" s="53"/>
@@ -10394,16 +10394,16 @@
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="56" t="s">
-        <x:v>579</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="B163" s="52" t="s">
-        <x:v>580</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="C163" s="52" t="s">
-        <x:v>581</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="D163" s="52" t="s">
-        <x:v>582</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E163" s="53"/>
       <x:c r="F163" s="53"/>
@@ -10424,16 +10424,16 @@
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="56" t="s">
-        <x:v>583</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="B164" s="52" t="s">
-        <x:v>584</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C164" s="52" t="s">
-        <x:v>585</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="D164" s="52" t="s">
-        <x:v>586</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="E164" s="53"/>
       <x:c r="F164" s="53"/>
@@ -10454,16 +10454,16 @@
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="56" t="s">
-        <x:v>587</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="B165" s="52" t="s">
-        <x:v>588</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="C165" s="52" t="s">
-        <x:v>589</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="D165" s="52" t="s">
-        <x:v>590</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="E165" s="53"/>
       <x:c r="F165" s="53"/>
@@ -10484,16 +10484,16 @@
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="56" t="s">
-        <x:v>591</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="B166" s="52" t="s">
-        <x:v>592</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="C166" s="52" t="s">
-        <x:v>104</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="D166" s="52" t="s">
-        <x:v>593</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="E166" s="53"/>
       <x:c r="F166" s="53"/>
@@ -10514,16 +10514,16 @@
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="56" t="s">
-        <x:v>594</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="B167" s="55" t="s">
-        <x:v>324</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C167" s="52" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D167" s="52" t="s">
-        <x:v>595</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E167" s="53"/>
       <x:c r="F167" s="53"/>
@@ -10544,16 +10544,16 @@
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="56" t="s">
-        <x:v>596</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="B168" s="52" t="s">
-        <x:v>597</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C168" s="52" t="s">
-        <x:v>598</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D168" s="52" t="s">
-        <x:v>599</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="E168" s="53"/>
       <x:c r="F168" s="53"/>
@@ -10574,16 +10574,16 @@
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="56" t="s">
-        <x:v>600</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B169" s="52" t="s">
-        <x:v>601</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="C169" s="52" t="s">
-        <x:v>602</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="D169" s="52" t="s">
-        <x:v>603</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="E169" s="53"/>
       <x:c r="F169" s="53"/>
@@ -10604,16 +10604,16 @@
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="56" t="s">
-        <x:v>604</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="B170" s="52" t="s">
-        <x:v>605</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="C170" s="52" t="s">
-        <x:v>606</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="D170" s="52" t="s">
-        <x:v>607</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="E170" s="53"/>
       <x:c r="F170" s="53"/>
@@ -10634,16 +10634,16 @@
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="56" t="s">
-        <x:v>608</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="B171" s="52" t="s">
-        <x:v>609</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C171" s="52" t="s">
-        <x:v>610</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="D171" s="52" t="s">
-        <x:v>611</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="E171" s="53"/>
       <x:c r="F171" s="53"/>
@@ -10664,16 +10664,16 @@
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="56" t="s">
-        <x:v>612</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="B172" s="52" t="s">
-        <x:v>613</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C172" s="52" t="s">
-        <x:v>614</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D172" s="52" t="s">
-        <x:v>615</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="E172" s="53"/>
       <x:c r="F172" s="53"/>
@@ -10694,16 +10694,16 @@
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="56" t="s">
-        <x:v>616</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="B173" s="52" t="s">
-        <x:v>617</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="C173" s="52" t="s">
-        <x:v>618</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="D173" s="52" t="s">
-        <x:v>619</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="E173" s="53"/>
       <x:c r="F173" s="53"/>
@@ -10724,16 +10724,16 @@
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="56" t="s">
-        <x:v>620</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="B174" s="52" t="s">
-        <x:v>621</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C174" s="52" t="s">
-        <x:v>622</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="D174" s="52" t="s">
-        <x:v>623</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="E174" s="53"/>
       <x:c r="F174" s="53"/>
@@ -10754,16 +10754,16 @@
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="56" t="s">
-        <x:v>624</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="B175" s="52" t="s">
-        <x:v>625</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="C175" s="52" t="s">
-        <x:v>626</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="D175" s="52" t="s">
-        <x:v>627</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="E175" s="53"/>
       <x:c r="F175" s="53"/>
@@ -10784,16 +10784,16 @@
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="56" t="s">
-        <x:v>628</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B176" s="52" t="s">
-        <x:v>629</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="C176" s="52" t="s">
-        <x:v>630</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D176" s="52" t="s">
-        <x:v>631</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E176" s="53"/>
       <x:c r="F176" s="53"/>
@@ -10814,16 +10814,16 @@
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="56" t="s">
-        <x:v>632</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="B177" s="52" t="s">
-        <x:v>633</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="C177" s="52" t="s">
-        <x:v>634</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="D177" s="52" t="s">
-        <x:v>635</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="E177" s="53"/>
       <x:c r="F177" s="53"/>
@@ -10844,16 +10844,16 @@
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="56" t="s">
-        <x:v>636</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="B178" s="52" t="s">
-        <x:v>637</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="C178" s="52" t="s">
-        <x:v>638</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D178" s="52" t="s">
-        <x:v>639</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="E178" s="53"/>
       <x:c r="F178" s="53"/>
@@ -10874,16 +10874,16 @@
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="56" t="s">
-        <x:v>640</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="B179" s="52" t="s">
-        <x:v>641</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="C179" s="52" t="s">
-        <x:v>108</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="D179" s="52" t="s">
-        <x:v>642</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="E179" s="53"/>
       <x:c r="F179" s="53"/>
@@ -10904,16 +10904,16 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="56" t="s">
-        <x:v>643</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="B180" s="52" t="s">
-        <x:v>644</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="C180" s="52" t="s">
-        <x:v>645</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D180" s="52" t="s">
-        <x:v>646</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="E180" s="53"/>
       <x:c r="F180" s="53"/>
@@ -10934,16 +10934,16 @@
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="56" t="s">
-        <x:v>647</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="B181" s="52" t="s">
-        <x:v>648</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="C181" s="52" t="s">
-        <x:v>109</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="D181" s="52" t="s">
-        <x:v>649</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="E181" s="53"/>
       <x:c r="F181" s="53"/>
@@ -10964,16 +10964,16 @@
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="56" t="s">
-        <x:v>650</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="B182" s="52" t="s">
-        <x:v>651</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="C182" s="52" t="s">
-        <x:v>652</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D182" s="52" t="s">
-        <x:v>653</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="E182" s="53"/>
       <x:c r="F182" s="53"/>
@@ -10994,16 +10994,16 @@
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="56" t="s">
-        <x:v>654</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="B183" s="52" t="s">
-        <x:v>655</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="C183" s="52" t="s">
-        <x:v>656</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="D183" s="52" t="s">
-        <x:v>657</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="E183" s="53"/>
       <x:c r="F183" s="53"/>
@@ -11024,16 +11024,16 @@
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="56" t="s">
-        <x:v>658</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="B184" s="52" t="s">
-        <x:v>659</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="C184" s="52" t="s">
-        <x:v>660</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D184" s="52" t="s">
-        <x:v>661</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="E184" s="53"/>
       <x:c r="F184" s="53"/>
@@ -11054,16 +11054,16 @@
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="56" t="s">
-        <x:v>662</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="B185" s="52" t="s">
-        <x:v>663</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C185" s="52" t="s">
-        <x:v>664</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="D185" s="52" t="s">
-        <x:v>665</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="E185" s="53"/>
       <x:c r="F185" s="53"/>
@@ -11084,16 +11084,16 @@
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="56" t="s">
-        <x:v>666</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="B186" s="52" t="s">
-        <x:v>667</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="C186" s="52" t="s">
-        <x:v>668</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="D186" s="52" t="s">
-        <x:v>669</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="E186" s="53"/>
       <x:c r="F186" s="53"/>
@@ -11114,16 +11114,16 @@
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="56" t="s">
-        <x:v>670</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="B187" s="52" t="s">
-        <x:v>426</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="C187" s="52" t="s">
-        <x:v>128</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="D187" s="52" t="s">
-        <x:v>427</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="E187" s="53"/>
       <x:c r="F187" s="53"/>
@@ -11144,16 +11144,16 @@
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="56" t="s">
-        <x:v>671</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="B188" s="60" t="s">
-        <x:v>672</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C188" s="72" t="s">
-        <x:v>673</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D188" s="55" t="s">
-        <x:v>674</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E188" s="53"/>
       <x:c r="F188" s="53"/>
@@ -11174,16 +11174,16 @@
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="56" t="s">
-        <x:v>675</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="B189" s="52" t="s">
-        <x:v>676</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="C189" s="52" t="s">
-        <x:v>677</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="D189" s="52" t="s">
-        <x:v>678</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="E189" s="53"/>
       <x:c r="F189" s="53"/>
@@ -11204,16 +11204,16 @@
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="56" t="s">
-        <x:v>679</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="B190" s="52" t="s">
-        <x:v>680</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C190" s="52" t="s">
-        <x:v>681</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D190" s="52" t="s">
-        <x:v>682</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="E190" s="53"/>
       <x:c r="F190" s="53"/>
@@ -11234,16 +11234,16 @@
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="56" t="s">
-        <x:v>683</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="B191" s="52" t="s">
-        <x:v>684</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="C191" s="52" t="s">
-        <x:v>685</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="D191" s="52" t="s">
-        <x:v>686</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="E191" s="53"/>
       <x:c r="F191" s="53"/>
@@ -11264,16 +11264,16 @@
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="56" t="s">
-        <x:v>687</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="B192" s="52" t="s">
-        <x:v>688</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="C192" s="52" t="s">
-        <x:v>689</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="D192" s="52" t="s">
-        <x:v>690</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="E192" s="53"/>
       <x:c r="F192" s="53"/>
@@ -11294,16 +11294,16 @@
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="56" t="s">
-        <x:v>691</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="B193" s="52" t="s">
-        <x:v>692</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="C193" s="52" t="s">
-        <x:v>693</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="D193" s="52" t="s">
-        <x:v>694</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="E193" s="53"/>
       <x:c r="F193" s="53"/>
@@ -11324,16 +11324,16 @@
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="56" t="s">
-        <x:v>695</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="B194" s="52" t="s">
-        <x:v>696</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="C194" s="52" t="s">
-        <x:v>697</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="D194" s="52" t="s">
-        <x:v>698</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="E194" s="53"/>
       <x:c r="F194" s="53"/>
@@ -11354,16 +11354,16 @@
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="56" t="s">
-        <x:v>699</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="B195" s="52" t="s">
-        <x:v>700</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="C195" s="52" t="s">
-        <x:v>701</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="D195" s="52" t="s">
-        <x:v>702</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="E195" s="53"/>
       <x:c r="F195" s="53"/>
@@ -11384,16 +11384,16 @@
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="56" t="s">
-        <x:v>703</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="B196" s="52" t="s">
-        <x:v>704</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="C196" s="52" t="s">
-        <x:v>705</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D196" s="52" t="s">
-        <x:v>706</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="E196" s="53"/>
       <x:c r="F196" s="53"/>
@@ -11414,16 +11414,16 @@
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="56" t="s">
-        <x:v>707</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B197" s="52" t="s">
-        <x:v>708</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="C197" s="52" t="s">
-        <x:v>709</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="D197" s="52" t="s">
-        <x:v>710</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="E197" s="53"/>
       <x:c r="F197" s="53"/>
@@ -11444,16 +11444,16 @@
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="56" t="s">
-        <x:v>711</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="B198" s="52" t="s">
-        <x:v>712</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="C198" s="52" t="s">
-        <x:v>713</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="D198" s="52" t="s">
-        <x:v>714</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="E198" s="53"/>
       <x:c r="F198" s="53"/>
@@ -11474,16 +11474,16 @@
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="56" t="s">
-        <x:v>715</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="B199" s="52" t="s">
-        <x:v>716</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="C199" s="52" t="s">
-        <x:v>717</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="D199" s="52" t="s">
-        <x:v>718</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="E199" s="53"/>
       <x:c r="F199" s="53"/>
@@ -11504,16 +11504,16 @@
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="56" t="s">
-        <x:v>719</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="B200" s="52" t="s">
-        <x:v>720</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="C200" s="52" t="s">
-        <x:v>721</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="D200" s="52" t="s">
-        <x:v>722</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="E200" s="53"/>
       <x:c r="F200" s="53"/>
@@ -11534,16 +11534,16 @@
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="56" t="s">
-        <x:v>723</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="B201" s="52" t="s">
-        <x:v>724</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="C201" s="52" t="s">
-        <x:v>725</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="D201" s="52" t="s">
-        <x:v>726</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="E201" s="53"/>
       <x:c r="F201" s="53"/>
@@ -11564,16 +11564,16 @@
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="56" t="s">
-        <x:v>727</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="B202" s="52" t="s">
-        <x:v>728</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="C202" s="52" t="s">
-        <x:v>729</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="D202" s="52" t="s">
-        <x:v>730</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="E202" s="53"/>
       <x:c r="F202" s="53"/>
@@ -11594,16 +11594,16 @@
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="56" t="s">
-        <x:v>731</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="B203" s="52" t="s">
-        <x:v>732</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="C203" s="52" t="s">
-        <x:v>143</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="D203" s="52" t="s">
-        <x:v>733</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="E203" s="53"/>
       <x:c r="F203" s="53"/>
@@ -11624,16 +11624,16 @@
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="56" t="s">
-        <x:v>734</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="B204" s="52" t="s">
-        <x:v>735</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="C204" s="52" t="s">
-        <x:v>736</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D204" s="52" t="s">
-        <x:v>737</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="E204" s="53"/>
       <x:c r="F204" s="53"/>
@@ -11654,16 +11654,16 @@
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="56" t="s">
-        <x:v>738</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="B205" s="52" t="s">
-        <x:v>739</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="C205" s="52" t="s">
-        <x:v>740</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="D205" s="52" t="s">
-        <x:v>741</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="E205" s="53"/>
       <x:c r="F205" s="53"/>
@@ -11684,16 +11684,16 @@
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="56" t="s">
-        <x:v>742</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="B206" s="52" t="s">
-        <x:v>743</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="C206" s="52" t="s">
-        <x:v>744</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="D206" s="52" t="s">
-        <x:v>745</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="E206" s="53"/>
       <x:c r="F206" s="53"/>
@@ -11714,16 +11714,16 @@
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="56" t="s">
-        <x:v>746</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="B207" s="52" t="s">
-        <x:v>747</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="C207" s="52" t="s">
-        <x:v>748</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="D207" s="52" t="s">
-        <x:v>749</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="E207" s="53"/>
       <x:c r="F207" s="53"/>
@@ -11744,16 +11744,16 @@
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="56" t="s">
-        <x:v>750</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="B208" s="52" t="s">
-        <x:v>751</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C208" s="52" t="s">
-        <x:v>145</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="D208" s="52" t="s">
-        <x:v>752</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="E208" s="53"/>
       <x:c r="F208" s="53"/>
@@ -11774,16 +11774,16 @@
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="56" t="s">
-        <x:v>753</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="B209" s="52" t="s">
-        <x:v>754</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="C209" s="52" t="s">
-        <x:v>755</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D209" s="52" t="s">
-        <x:v>756</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="E209" s="53"/>
       <x:c r="F209" s="53"/>
@@ -11804,16 +11804,16 @@
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="56" t="s">
-        <x:v>757</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="B210" s="52" t="s">
-        <x:v>758</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="C210" s="52" t="s">
-        <x:v>759</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D210" s="52" t="s">
-        <x:v>759</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="E210" s="53"/>
       <x:c r="F210" s="53"/>
@@ -11834,16 +11834,16 @@
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="56" t="s">
-        <x:v>760</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="B211" s="52" t="s">
-        <x:v>761</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="C211" s="52" t="s">
-        <x:v>762</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="D211" s="52" t="s">
-        <x:v>763</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="E211" s="53"/>
       <x:c r="F211" s="53"/>
@@ -11864,16 +11864,16 @@
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="56" t="s">
-        <x:v>764</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="B212" s="55" t="s">
-        <x:v>348</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="C212" s="52" t="s">
-        <x:v>115</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="D212" s="52" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="E212" s="53"/>
       <x:c r="F212" s="53"/>
@@ -11894,16 +11894,16 @@
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="56" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="B213" s="52" t="s">
-        <x:v>767</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C213" s="52" t="s">
-        <x:v>768</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D213" s="52" t="s">
-        <x:v>769</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="E213" s="53"/>
       <x:c r="F213" s="53"/>
@@ -11924,16 +11924,16 @@
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="56" t="s">
-        <x:v>770</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="B214" s="55" t="s">
-        <x:v>771</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="C214" s="52" t="s">
-        <x:v>772</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="D214" s="52" t="s">
-        <x:v>773</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="E214" s="53"/>
       <x:c r="F214" s="53"/>
@@ -11954,16 +11954,16 @@
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="56" t="s">
-        <x:v>774</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="B215" s="55" t="s">
-        <x:v>775</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="C215" s="55" t="s">
-        <x:v>776</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="D215" s="52" t="s">
-        <x:v>777</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="E215" s="53"/>
       <x:c r="F215" s="53"/>
@@ -11984,16 +11984,16 @@
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="56" t="s">
-        <x:v>778</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="B216" s="52" t="s">
-        <x:v>779</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C216" s="52" t="s">
-        <x:v>780</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="D216" s="52" t="s">
-        <x:v>781</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="E216" s="53"/>
       <x:c r="F216" s="53"/>
@@ -12014,16 +12014,16 @@
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="56" t="s">
-        <x:v>782</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="B217" s="55" t="s">
-        <x:v>783</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="C217" s="52" t="s">
-        <x:v>784</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D217" s="52" t="s">
-        <x:v>785</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="E217" s="53"/>
       <x:c r="F217" s="53"/>
@@ -12044,16 +12044,16 @@
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="56" t="s">
-        <x:v>786</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="B218" s="55" t="s">
-        <x:v>787</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="C218" s="52" t="s">
-        <x:v>788</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="D218" s="52" t="s">
-        <x:v>789</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="E218" s="53"/>
       <x:c r="F218" s="53"/>
@@ -12074,16 +12074,16 @@
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="56" t="s">
-        <x:v>790</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="B219" s="52" t="s">
-        <x:v>359</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="C219" s="52" t="s">
-        <x:v>791</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="D219" s="52" t="s">
-        <x:v>792</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="E219" s="53"/>
       <x:c r="F219" s="53"/>
@@ -12104,16 +12104,16 @@
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="56" t="s">
-        <x:v>793</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="B220" s="55" t="s">
-        <x:v>794</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C220" s="52" t="s">
-        <x:v>795</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="D220" s="52" t="s">
-        <x:v>796</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="E220" s="53"/>
       <x:c r="F220" s="53"/>
@@ -12134,16 +12134,16 @@
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="56" t="s">
-        <x:v>797</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="B221" s="52" t="s">
-        <x:v>798</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="C221" s="52" t="s">
-        <x:v>799</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D221" s="52" t="s">
-        <x:v>800</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="E221" s="53"/>
       <x:c r="F221" s="53"/>
@@ -12164,16 +12164,16 @@
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="56" t="s">
-        <x:v>801</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B222" s="55" t="s">
-        <x:v>802</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="C222" s="52" t="s">
-        <x:v>803</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D222" s="52" t="s">
-        <x:v>804</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="E222" s="53"/>
       <x:c r="F222" s="53"/>
@@ -12194,16 +12194,16 @@
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="56" t="s">
-        <x:v>805</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B223" s="55" t="s">
-        <x:v>806</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="C223" s="52" t="s">
-        <x:v>807</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="D223" s="52" t="s">
-        <x:v>808</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="E223" s="53"/>
       <x:c r="F223" s="53"/>
@@ -12224,16 +12224,16 @@
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="56" t="s">
-        <x:v>809</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B224" s="52" t="s">
-        <x:v>810</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="C224" s="52" t="s">
-        <x:v>811</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="D224" s="52" t="s">
-        <x:v>812</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="E224" s="53"/>
       <x:c r="F224" s="53"/>
@@ -12254,16 +12254,16 @@
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="56" t="s">
-        <x:v>813</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="B225" s="52" t="s">
-        <x:v>814</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="C225" s="52" t="s">
-        <x:v>815</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="D225" s="52" t="s">
-        <x:v>816</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="E225" s="53"/>
       <x:c r="F225" s="53"/>
@@ -12284,16 +12284,16 @@
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="56" t="s">
-        <x:v>817</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="B226" s="52" t="s">
-        <x:v>818</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="C226" s="52" t="s">
-        <x:v>819</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="D226" s="52" t="s">
-        <x:v>820</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="E226" s="53"/>
       <x:c r="F226" s="53"/>
@@ -12314,16 +12314,16 @@
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="56" t="s">
-        <x:v>821</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="B227" s="52" t="s">
-        <x:v>822</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="C227" s="52" t="s">
-        <x:v>823</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="D227" s="52" t="s">
-        <x:v>824</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="E227" s="53"/>
       <x:c r="F227" s="53"/>
@@ -12344,16 +12344,16 @@
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="56" t="s">
-        <x:v>825</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="B228" s="52" t="s">
-        <x:v>826</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="C228" s="52" t="s">
-        <x:v>827</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="D228" s="52" t="s">
-        <x:v>828</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="E228" s="53"/>
       <x:c r="F228" s="53"/>
@@ -12374,16 +12374,16 @@
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="56" t="s">
-        <x:v>829</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="B229" s="52" t="s">
-        <x:v>830</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="C229" s="52" t="s">
-        <x:v>831</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D229" s="52" t="s">
-        <x:v>832</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="E229" s="53"/>
       <x:c r="F229" s="53"/>
@@ -12404,16 +12404,16 @@
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="56" t="s">
-        <x:v>833</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="B230" s="55" t="s">
-        <x:v>834</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="C230" s="52" t="s">
-        <x:v>835</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="D230" s="52" t="s">
-        <x:v>836</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="E230" s="53"/>
       <x:c r="F230" s="53"/>
@@ -12434,16 +12434,16 @@
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="56" t="s">
-        <x:v>837</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="B231" s="52" t="s">
-        <x:v>838</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="C231" s="52" t="s">
-        <x:v>839</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="D231" s="52" t="s">
-        <x:v>840</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="E231" s="53"/>
       <x:c r="F231" s="53"/>
@@ -12464,16 +12464,16 @@
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="56" t="s">
-        <x:v>841</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="B232" s="52" t="s">
-        <x:v>842</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="C232" s="52" t="s">
-        <x:v>843</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="D232" s="52" t="s">
-        <x:v>844</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="E232" s="53"/>
       <x:c r="F232" s="53"/>
@@ -12494,16 +12494,16 @@
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="56" t="s">
-        <x:v>845</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="B233" s="52" t="s">
-        <x:v>846</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="C233" s="52" t="s">
-        <x:v>847</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="D233" s="52" t="s">
-        <x:v>848</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="E233" s="53"/>
       <x:c r="F233" s="53"/>
@@ -12524,16 +12524,16 @@
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="56" t="s">
-        <x:v>849</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="B234" s="52" t="s">
-        <x:v>850</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="C234" s="52" t="s">
-        <x:v>851</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="D234" s="52" t="s">
-        <x:v>852</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="E234" s="53"/>
       <x:c r="F234" s="53"/>
@@ -12554,16 +12554,16 @@
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="56" t="s">
-        <x:v>853</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="B235" s="52" t="s">
-        <x:v>854</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="C235" s="52" t="s">
-        <x:v>148</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="D235" s="52" t="s">
-        <x:v>855</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="E235" s="53"/>
       <x:c r="F235" s="53"/>
@@ -12584,16 +12584,16 @@
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="56" t="s">
-        <x:v>856</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="B236" s="52" t="s">
-        <x:v>857</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="C236" s="52" t="s">
-        <x:v>858</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D236" s="52" t="s">
-        <x:v>859</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="E236" s="53"/>
       <x:c r="F236" s="53"/>
@@ -12614,16 +12614,16 @@
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="56" t="s">
-        <x:v>860</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="B237" s="52" t="s">
-        <x:v>398</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="C237" s="52" t="s">
-        <x:v>152</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="D237" s="52" t="s">
-        <x:v>399</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="E237" s="53"/>
       <x:c r="F237" s="53"/>
@@ -12644,7 +12644,7 @@
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="56" t="s">
-        <x:v>861</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="B238" s="52" t="s">
         <x:v>398</x:v>
@@ -12674,16 +12674,16 @@
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="56" t="s">
-        <x:v>862</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="B239" s="55" t="s">
-        <x:v>863</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C239" s="55" t="s">
-        <x:v>864</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="D239" s="52" t="s">
-        <x:v>865</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E239" s="53"/>
       <x:c r="F239" s="53"/>
@@ -12704,16 +12704,16 @@
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="56" t="s">
-        <x:v>866</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="B240" s="52" t="s">
-        <x:v>867</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="C240" s="52" t="s">
-        <x:v>867</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="D240" s="52" t="s">
-        <x:v>867</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="E240" s="53"/>
       <x:c r="F240" s="53"/>
@@ -12734,14 +12734,16 @@
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="73" t="s">
-        <x:v>868</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="B241" s="74" t="s">
-        <x:v>869</x:v>
-      </x:c>
-      <x:c r="C241" s="72"/>
+        <x:v>867</x:v>
+      </x:c>
+      <x:c r="C241" s="72" t="s">
+        <x:v>867</x:v>
+      </x:c>
       <x:c r="D241" s="74" t="s">
-        <x:v>870</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="E241" s="75"/>
       <x:c r="F241" s="75"/>
@@ -12762,16 +12764,14 @@
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="56" t="s">
-        <x:v>871</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="B242" s="52" t="s">
-        <x:v>872</x:v>
-      </x:c>
-      <x:c r="C242" s="52" t="s">
-        <x:v>873</x:v>
-      </x:c>
+        <x:v>869</x:v>
+      </x:c>
+      <x:c r="C242" s="52"/>
       <x:c r="D242" s="52" t="s">
-        <x:v>874</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="E242" s="53"/>
       <x:c r="F242" s="53"/>
@@ -12792,16 +12792,16 @@
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="56" t="s">
-        <x:v>875</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="B243" s="52" t="s">
-        <x:v>876</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="C243" s="52" t="s">
-        <x:v>877</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="D243" s="52" t="s">
-        <x:v>878</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="E243" s="53"/>
       <x:c r="F243" s="53"/>
@@ -12822,16 +12822,16 @@
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="56" t="s">
-        <x:v>879</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="B244" s="52" t="s">
-        <x:v>880</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="C244" s="52" t="s">
-        <x:v>881</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="D244" s="52" t="s">
-        <x:v>882</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="E244" s="53"/>
       <x:c r="F244" s="53"/>
@@ -12852,16 +12852,16 @@
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="56" t="s">
-        <x:v>883</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="B245" s="52" t="s">
-        <x:v>884</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="C245" s="52" t="s">
-        <x:v>885</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="D245" s="52" t="s">
-        <x:v>886</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="E245" s="53"/>
       <x:c r="F245" s="53"/>
@@ -12882,16 +12882,16 @@
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="73" t="s">
-        <x:v>887</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="B246" s="72" t="s">
-        <x:v>888</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="C246" s="72" t="s">
-        <x:v>889</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="D246" s="74" t="s">
-        <x:v>890</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="E246" s="75"/>
       <x:c r="F246" s="75"/>
@@ -12912,16 +12912,16 @@
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="56" t="s">
-        <x:v>891</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="B247" s="77" t="s">
-        <x:v>892</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="C247" s="72" t="s">
-        <x:v>893</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="D247" s="52" t="s">
-        <x:v>894</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="E247" s="53"/>
       <x:c r="F247" s="53"/>
@@ -12942,16 +12942,16 @@
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="56" t="s">
-        <x:v>895</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="B248" s="78" t="s">
-        <x:v>896</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="C248" s="72" t="s">
-        <x:v>897</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="D248" s="52" t="s">
-        <x:v>898</x:v>
+        <x:v>894</x:v>
       </x:c>
       <x:c r="E248" s="53"/>
       <x:c r="F248" s="53"/>
@@ -12971,17 +12971,17 @@
       <x:c r="T248" s="54"/>
     </x:row>
     <x:row r="249">
-      <x:c r="A249" s="56" t="str">
-        <x:v>enemy.action.basic_attack</x:v>
-      </x:c>
-      <x:c r="B249" s="77" t="str">
-        <x:v>Normal Attack: -{0}</x:v>
-      </x:c>
-      <x:c r="C249" s="72" t="str">
-        <x:v>普攻：-{0}</x:v>
-      </x:c>
-      <x:c r="D249" s="52" t="str">
-        <x:v>通常攻撃：-{0}</x:v>
+      <x:c r="A249" s="56" t="s">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="B249" s="77" t="s">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="C249" s="72" t="s">
+        <x:v>897</x:v>
+      </x:c>
+      <x:c r="D249" s="52" t="s">
+        <x:v>898</x:v>
       </x:c>
       <x:c r="E249" s="53"/>
       <x:c r="F249" s="53"/>
@@ -13001,17 +13001,17 @@
       <x:c r="T249" s="54"/>
     </x:row>
     <x:row r="250">
-      <x:c r="A250" s="56" t="s">
-        <x:v>899</x:v>
-      </x:c>
-      <x:c r="B250" s="77" t="s">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="C250" s="72" t="s">
-        <x:v>901</x:v>
-      </x:c>
-      <x:c r="D250" s="52" t="s">
-        <x:v>902</x:v>
+      <x:c r="A250" s="56" t="str">
+        <x:v>enemy.action.basic_attack</x:v>
+      </x:c>
+      <x:c r="B250" s="77" t="str">
+        <x:v>Normal Attack: -{0}</x:v>
+      </x:c>
+      <x:c r="C250" s="72" t="str">
+        <x:v>普攻：-{0}</x:v>
+      </x:c>
+      <x:c r="D250" s="52" t="str">
+        <x:v>通常攻撃：-{0}</x:v>
       </x:c>
       <x:c r="E250" s="53"/>
       <x:c r="F250" s="53"/>
@@ -13032,16 +13032,16 @@
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="56" t="s">
-        <x:v>903</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="B251" s="77" t="s">
-        <x:v>904</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="C251" s="72" t="s">
-        <x:v>905</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="D251" s="52" t="s">
-        <x:v>906</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="E251" s="53"/>
       <x:c r="F251" s="53"/>
@@ -13062,16 +13062,16 @@
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="56" t="s">
-        <x:v>907</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="B252" s="77" t="s">
-        <x:v>908</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="C252" s="72" t="s">
-        <x:v>909</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="D252" s="52" t="s">
-        <x:v>910</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="E252" s="53"/>
       <x:c r="F252" s="53"/>
@@ -13091,17 +13091,17 @@
       <x:c r="T252" s="54"/>
     </x:row>
     <x:row r="253">
-      <x:c r="A253" s="73" t="str">
-        <x:v>enemy.action.overload_explosion</x:v>
-      </x:c>
-      <x:c r="B253" s="77" t="str">
-        <x:v>Overload Explosion: -{0}</x:v>
-      </x:c>
-      <x:c r="C253" s="72" t="str">
-        <x:v>负荷爆炸：-{0}</x:v>
-      </x:c>
-      <x:c r="D253" s="74" t="str">
-        <x:v>過負荷爆発：-{0}</x:v>
+      <x:c r="A253" s="73" t="s">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="B253" s="77" t="s">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="C253" s="72" t="s">
+        <x:v>909</x:v>
+      </x:c>
+      <x:c r="D253" s="74" t="s">
+        <x:v>910</x:v>
       </x:c>
       <x:c r="E253" s="75"/>
       <x:c r="F253" s="75"/>
@@ -13121,17 +13121,17 @@
       <x:c r="T253" s="76"/>
     </x:row>
     <x:row r="254">
-      <x:c r="A254" s="73" t="s">
-        <x:v>911</x:v>
-      </x:c>
-      <x:c r="B254" s="77" t="s">
-        <x:v>912</x:v>
-      </x:c>
-      <x:c r="C254" s="72" t="s">
-        <x:v>913</x:v>
-      </x:c>
-      <x:c r="D254" s="74" t="s">
-        <x:v>914</x:v>
+      <x:c r="A254" s="73" t="str">
+        <x:v>enemy.action.overload_explosion</x:v>
+      </x:c>
+      <x:c r="B254" s="77" t="str">
+        <x:v>Overload Explosion: -{0}</x:v>
+      </x:c>
+      <x:c r="C254" s="72" t="str">
+        <x:v>负荷爆炸：-{0}</x:v>
+      </x:c>
+      <x:c r="D254" s="74" t="str">
+        <x:v>過負荷爆発：-{0}</x:v>
       </x:c>
       <x:c r="E254" s="75"/>
       <x:c r="F254" s="75"/>
@@ -13152,16 +13152,16 @@
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="56" t="s">
-        <x:v>915</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="B255" s="77" t="s">
-        <x:v>916</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="C255" s="72" t="s">
-        <x:v>917</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="D255" s="52" t="s">
-        <x:v>918</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="E255" s="53"/>
       <x:c r="F255" s="53"/>
@@ -13182,16 +13182,16 @@
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="56" t="s">
-        <x:v>919</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="B256" s="77" t="s">
-        <x:v>920</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="C256" s="72" t="s">
-        <x:v>921</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="D256" s="52" t="s">
-        <x:v>922</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="E256" s="53"/>
       <x:c r="F256" s="53"/>
@@ -13212,16 +13212,16 @@
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="56" t="s">
-        <x:v>923</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="B257" s="77" t="s">
-        <x:v>924</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="C257" s="74" t="s">
-        <x:v>925</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="D257" s="52" t="s">
-        <x:v>926</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="E257" s="53"/>
       <x:c r="F257" s="53"/>
@@ -13242,16 +13242,16 @@
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="56" t="s">
-        <x:v>927</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="B258" s="77" t="s">
-        <x:v>928</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="C258" s="72" t="s">
-        <x:v>929</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="D258" s="52" t="s">
-        <x:v>930</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="E258" s="53"/>
       <x:c r="F258" s="53"/>
@@ -13272,16 +13272,16 @@
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="56" t="s">
-        <x:v>931</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="B259" s="77" t="s">
-        <x:v>932</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="C259" s="72" t="s">
-        <x:v>933</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="D259" s="52" t="s">
-        <x:v>934</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="E259" s="53"/>
       <x:c r="F259" s="53"/>
@@ -13302,16 +13302,16 @@
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="56" t="s">
-        <x:v>935</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="B260" s="77" t="s">
-        <x:v>936</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="C260" s="72" t="s">
-        <x:v>937</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="D260" s="52" t="s">
-        <x:v>938</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="E260" s="53"/>
       <x:c r="F260" s="53"/>
@@ -13332,16 +13332,16 @@
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="56" t="s">
-        <x:v>939</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="B261" s="77" t="s">
-        <x:v>940</x:v>
+        <x:v>936</x:v>
       </x:c>
       <x:c r="C261" s="72" t="s">
-        <x:v>941</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="D261" s="52" t="s">
-        <x:v>942</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E261" s="53"/>
       <x:c r="F261" s="53"/>
@@ -13362,16 +13362,16 @@
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="56" t="s">
-        <x:v>943</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="B262" s="52" t="s">
-        <x:v>944</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="C262" s="52" t="s">
-        <x:v>945</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="D262" s="52" t="s">
-        <x:v>946</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="E262" s="53"/>
       <x:c r="F262" s="53"/>
@@ -13392,16 +13392,16 @@
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="56" t="s">
-        <x:v>947</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="B263" s="52" t="s">
-        <x:v>948</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="C263" s="52" t="s">
-        <x:v>949</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="D263" s="52" t="s">
-        <x:v>950</x:v>
+        <x:v>946</x:v>
       </x:c>
       <x:c r="E263" s="53"/>
       <x:c r="F263" s="53"/>
@@ -13422,16 +13422,16 @@
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="56" t="s">
-        <x:v>951</x:v>
+        <x:v>947</x:v>
       </x:c>
       <x:c r="B264" s="52" t="s">
-        <x:v>952</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="C264" s="52" t="s">
-        <x:v>953</x:v>
+        <x:v>949</x:v>
       </x:c>
       <x:c r="D264" s="52" t="s">
-        <x:v>954</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E264" s="53"/>
       <x:c r="F264" s="53"/>
@@ -13452,16 +13452,16 @@
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="56" t="s">
-        <x:v>955</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="B265" s="55" t="s">
-        <x:v>956</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="C265" s="55" t="s">
-        <x:v>45</x:v>
+        <x:v>953</x:v>
       </x:c>
       <x:c r="D265" s="52" t="s">
-        <x:v>957</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E265" s="53"/>
       <x:c r="F265" s="53"/>
@@ -13482,31 +13482,46 @@
     </x:row>
     <x:row r="266">
       <x:c r="A266" t="s">
-        <x:v>958</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="B266" t="s">
-        <x:v>959</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="C266" t="s">
-        <x:v>960</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D266" t="s">
-        <x:v>961</x:v>
+        <x:v>957</x:v>
       </x:c>
       <x:c r="E266"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" t="s">
+        <x:v>958</x:v>
+      </x:c>
+      <x:c r="B267" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="C267" t="s">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="D267" t="s">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="E267"/>
+    </x:row>
+    <x:row r="268">
+      <x:c r="A268" t="s">
         <x:v>962</x:v>
       </x:c>
-      <x:c r="B267" t="s">
+      <x:c r="B268" t="s">
         <x:v>963</x:v>
       </x:c>
-      <x:c r="C267" t="s">
+      <x:c r="C268" t="s">
         <x:v>964</x:v>
       </x:c>
-      <x:c r="D267"/>
-      <x:c r="E267"/>
+      <x:c r="D268"/>
+      <x:c r="E268"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Assets/GameData/database.xlsx
+++ b/Assets/GameData/database.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="1150">
   <si>
     <t xml:space="preserve">  </t>
   </si>
@@ -647,6 +647,9 @@
     <t xml:space="preserve">退出游戏</t>
   </si>
   <si>
+    <t xml:space="preserve">ゲームを終了</t>
+  </si>
+  <si>
     <t xml:space="preserve">title.settings</t>
   </si>
   <si>
@@ -656,12 +659,18 @@
     <t xml:space="preserve">设置</t>
   </si>
   <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
     <t xml:space="preserve">settings.volume</t>
   </si>
   <si>
     <t xml:space="preserve">Music</t>
   </si>
   <si>
+    <t xml:space="preserve">音乐</t>
+  </si>
+  <si>
     <t xml:space="preserve">音量</t>
   </si>
   <si>
@@ -674,6 +683,9 @@
     <t xml:space="preserve">音效</t>
   </si>
   <si>
+    <t xml:space="preserve">効果音</t>
+  </si>
+  <si>
     <t xml:space="preserve">settings.language</t>
   </si>
   <si>
@@ -681,6 +693,9 @@
   </si>
   <si>
     <t xml:space="preserve">语言</t>
+  </si>
+  <si>
+    <t xml:space="preserve">言語</t>
   </si>
   <si>
     <t xml:space="preserve">roll life</t>
@@ -828,6 +843,9 @@
     <t xml:space="preserve">技能</t>
   </si>
   <si>
+    <t xml:space="preserve">スキル</t>
+  </si>
+  <si>
     <t xml:space="preserve">skill.basic_attack.name</t>
   </si>
   <si>
@@ -835,6 +853,9 @@
   </si>
   <si>
     <t xml:space="preserve">下劈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">斬り</t>
   </si>
   <si>
     <t xml:space="preserve">skill.basic_attack.description</t>
@@ -848,6 +869,10 @@
 冷却：0回合。</t>
   </si>
   <si>
+    <t xml:space="preserve">コスト1。敵に3ダメージを与える。
+クールダウン：0ターン。</t>
+  </si>
+  <si>
     <t xml:space="preserve">skill.bloodlust.name</t>
   </si>
   <si>
@@ -940,6 +965,9 @@
     <t xml:space="preserve">消耗 1 点，减免受到伤害的 45%。冷却：0 回合。</t>
   </si>
   <si>
+    <t xml:space="preserve">コスト1。受けるダメージを45%軽減する。クールダウン：0ターン。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.player.items</t>
   </si>
   <si>
@@ -949,6 +977,9 @@
     <t xml:space="preserve">道具</t>
   </si>
   <si>
+    <t xml:space="preserve">アイテム</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.player.button.back</t>
   </si>
   <si>
@@ -958,6 +989,9 @@
     <t xml:space="preserve">返回</t>
   </si>
   <si>
+    <t xml:space="preserve">戻る</t>
+  </si>
+  <si>
     <t xml:space="preserve">collectible.wrench.name</t>
   </si>
   <si>
@@ -1195,6 +1229,9 @@
     <t xml:space="preserve">哀叹之钟</t>
   </si>
   <si>
+    <t xml:space="preserve">嘆きの鐘</t>
+  </si>
+  <si>
     <t xml:space="preserve">战斗结算面板</t>
   </si>
   <si>
@@ -1207,6 +1244,9 @@
     <t xml:space="preserve">你击败了{0}，是否进行贪婪检定？</t>
   </si>
   <si>
+    <t xml:space="preserve">{0}を倒しました。強欲判定に挑みますか？</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.additional_prompt</t>
   </si>
   <si>
@@ -1216,6 +1256,9 @@
     <t xml:space="preserve">你成功了，就此收手，还是再赌一把？</t>
   </si>
   <si>
+    <t xml:space="preserve">成功しました。ここで引き上げますか？ それとも、もう一度賭けますか？</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.button.greedy</t>
   </si>
   <si>
@@ -1225,6 +1268,9 @@
     <t xml:space="preserve">贪婪</t>
   </si>
   <si>
+    <t xml:space="preserve">欲張る</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.greedy_description</t>
   </si>
   <si>
@@ -1234,6 +1280,9 @@
     <t xml:space="preserve">50% 概率获得 2.5 倍点数；50% 概率失去本轮全部点数收获（保留道具）。</t>
   </si>
   <si>
+    <t xml:space="preserve">50%の確率でポイントを2.5倍獲得します。失敗すると、今回獲得したポイントをすべて失います（アイテムは保持されます）。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.button.safe</t>
   </si>
   <si>
@@ -1243,6 +1292,9 @@
     <t xml:space="preserve">见好就收</t>
   </si>
   <si>
+    <t xml:space="preserve">ここで引き上げる</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.safe_description</t>
   </si>
   <si>
@@ -1252,6 +1304,9 @@
     <t xml:space="preserve">稳定获得奖励点数的 100%。</t>
   </si>
   <si>
+    <t xml:space="preserve">報酬ポイントの100%を確実に獲得します。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.button.again</t>
   </si>
   <si>
@@ -1261,6 +1316,9 @@
     <t xml:space="preserve">再赌一把</t>
   </si>
   <si>
+    <t xml:space="preserve">もう一度賭ける</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.mirror_hint</t>
   </si>
   <si>
@@ -1270,6 +1328,9 @@
     <t xml:space="preserve">破碎的镜子给予你机会</t>
   </si>
   <si>
+    <t xml:space="preserve">割れた鏡が、もう一度チャンスを与えてくれます。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.result.success</t>
   </si>
   <si>
@@ -1279,6 +1340,9 @@
     <t xml:space="preserve">检定成功，恭喜你，幸运之人。你获得了{0}点。</t>
   </si>
   <si>
+    <t xml:space="preserve">判定成功。おめでとう、幸運な者よ。{0}ポイントを獲得しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.result.failed</t>
   </si>
   <si>
@@ -1288,6 +1352,9 @@
     <t xml:space="preserve">检定失败，真可惜，你一无所有。</t>
   </si>
   <si>
+    <t xml:space="preserve">判定失敗。残念ながら、あなたはすべてを失いました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">事件：获得物品</t>
   </si>
   <si>
@@ -1300,6 +1367,9 @@
     <t xml:space="preserve">真幸运，你获得了{0}！</t>
   </si>
   <si>
+    <t xml:space="preserve">{0}を獲得しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">0：技能/道具/信物 1：具体是什么</t>
   </si>
   <si>
@@ -1315,6 +1385,9 @@
     <t xml:space="preserve">是否用你拥有的道具换取另一个道具？</t>
   </si>
   <si>
+    <t xml:space="preserve">所持しているアイテムを別のアイテムと交換しますか？</t>
+  </si>
+  <si>
     <t xml:space="preserve">exchange.button.confirm</t>
   </si>
   <si>
@@ -1324,6 +1397,9 @@
     <t xml:space="preserve">交换</t>
   </si>
   <si>
+    <t xml:space="preserve">交換</t>
+  </si>
+  <si>
     <t xml:space="preserve">exchange.button.leave</t>
   </si>
   <si>
@@ -1333,6 +1409,9 @@
     <t xml:space="preserve">离开</t>
   </si>
   <si>
+    <t xml:space="preserve">立ち去る</t>
+  </si>
+  <si>
     <t xml:space="preserve">exchange.result.success</t>
   </si>
   <si>
@@ -1342,6 +1421,9 @@
     <t xml:space="preserve">以物易物，很划算吧。{0}属于你了。</t>
   </si>
   <si>
+    <t xml:space="preserve">物々交換ってお得でしょう？ {0}はあなたのものです。</t>
+  </si>
+  <si>
     <t xml:space="preserve">exchange.result.no_items</t>
   </si>
   <si>
@@ -1351,6 +1433,9 @@
     <t xml:space="preserve">真遗憾，你没有足够的道具和我交换。</t>
   </si>
   <si>
+    <t xml:space="preserve">残念ですが、交換できるアイテムを十分に持っていません。</t>
+  </si>
+  <si>
     <t xml:space="preserve">事件：供奉</t>
   </si>
   <si>
@@ -1399,6 +1484,9 @@
     <t xml:space="preserve">很可惜，你似乎并没有被赐福。</t>
   </si>
   <si>
+    <t xml:space="preserve">残念ながら、あなたは祝福を授からなかったようです。</t>
+  </si>
+  <si>
     <t xml:space="preserve">offering.result.item</t>
   </si>
   <si>
@@ -1408,6 +1496,9 @@
     <t xml:space="preserve">神的眷顾，你获得了{0}个道具{1}。</t>
   </si>
   <si>
+    <t xml:space="preserve">神の祝福により、アイテム「{1}」を{0}個獲得しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">offering.result.number</t>
   </si>
   <si>
@@ -1417,6 +1508,9 @@
     <t xml:space="preserve">神的眷顾，你获得了{0}点。</t>
   </si>
   <si>
+    <t xml:space="preserve">神の祝福により、{0}ポイントを獲得しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">offering.result.return</t>
   </si>
   <si>
@@ -1426,7 +1520,7 @@
     <t xml:space="preserve">神似乎拒绝了你，返还了你{0}点。</t>
   </si>
   <si>
-    <t xml:space="preserve">祭壇から点数{0}が返されました</t>
+    <t xml:space="preserve">神はあなたを拒んだようです。{0}ポイントが返還されました。</t>
   </si>
   <si>
     <t xml:space="preserve">offering.feedback.insufficient</t>
@@ -1438,6 +1532,9 @@
     <t xml:space="preserve">点数不足，当前无法供奉</t>
   </si>
   <si>
+    <t xml:space="preserve">ポイントが足りないため、今は捧げ物ができません。</t>
+  </si>
+  <si>
     <t xml:space="preserve">休整</t>
   </si>
   <si>
@@ -1450,6 +1547,9 @@
     <t xml:space="preserve">沐浴在神秘的力量下，你回复了{0}点。</t>
   </si>
   <si>
+    <t xml:space="preserve">神秘的な力に包まれ、{0}ポイント回復しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">商店</t>
   </si>
   <si>
@@ -1462,6 +1562,9 @@
     <t xml:space="preserve">用你最宝贵的点数换取这些小玩意，很不错，不是吗？</t>
   </si>
   <si>
+    <t xml:space="preserve">大切なポイントをこんな小物と交換するのも、悪くないでしょう？</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.button.buy</t>
   </si>
   <si>
@@ -1471,22 +1574,31 @@
     <t xml:space="preserve">购买</t>
   </si>
   <si>
+    <t xml:space="preserve">購入</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.button.leave</t>
   </si>
   <si>
+    <t xml:space="preserve">shop.button.sold_out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sold Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已售罄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">売り切れました</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.state.sold_out</t>
   </si>
   <si>
-    <t xml:space="preserve">Sold Out</t>
-  </si>
-  <si>
     <t xml:space="preserve">售罄</t>
   </si>
   <si>
-    <t xml:space="preserve">shop.button.sold_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已售罄</t>
+    <t xml:space="preserve">売り切れ</t>
   </si>
   <si>
     <t xml:space="preserve">shop.point_preview</t>
@@ -1498,6 +1610,9 @@
     <t xml:space="preserve">点数：{0} → {1}</t>
   </si>
   <si>
+    <t xml:space="preserve">ポイント：{0} → {1}</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.feedback.purchase_success</t>
   </si>
   <si>
@@ -1507,6 +1622,9 @@
     <t xml:space="preserve">购买成功</t>
   </si>
   <si>
+    <t xml:space="preserve">購入しました</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.feedback.sold_out</t>
   </si>
   <si>
@@ -1516,6 +1634,9 @@
     <t xml:space="preserve">这件商品已经售罄</t>
   </si>
   <si>
+    <t xml:space="preserve">この商品は売り切れです。</t>
+  </si>
+  <si>
     <t xml:space="preserve">shop.feedback.insufficient</t>
   </si>
   <si>
@@ -1525,6 +1646,9 @@
     <t xml:space="preserve">点数不足，当前无法购买</t>
   </si>
   <si>
+    <t xml:space="preserve">ポイントが足りないため、購入できません。</t>
+  </si>
+  <si>
     <t xml:space="preserve">胜利通关</t>
   </si>
   <si>
@@ -1738,15 +1862,9 @@
     <t xml:space="preserve">common.back</t>
   </si>
   <si>
-    <t xml:space="preserve">戻る</t>
-  </si>
-  <si>
     <t xml:space="preserve">common.leave</t>
   </si>
   <si>
-    <t xml:space="preserve">立ち去る</t>
-  </si>
-  <si>
     <t xml:space="preserve">common.rest</t>
   </si>
   <si>
@@ -1822,9 +1940,6 @@
     <t xml:space="preserve">Item</t>
   </si>
   <si>
-    <t xml:space="preserve">アイテム</t>
-  </si>
-  <si>
     <t xml:space="preserve">common.items</t>
   </si>
   <si>
@@ -1840,13 +1955,7 @@
     <t xml:space="preserve">common.skill</t>
   </si>
   <si>
-    <t xml:space="preserve">スキル</t>
-  </si>
-  <si>
     <t xml:space="preserve">common.sold_out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">売り切れ</t>
   </si>
   <si>
     <t xml:space="preserve">common.unknown_item</t>
@@ -2256,6 +2365,30 @@
     <t xml:space="preserve">アイテム数が変化しました。選び直してください</t>
   </si>
   <si>
+    <t xml:space="preserve">battle.item.shield_blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Guardian's Shield blocked {0} damage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守护者之盾抵挡了{0}点伤害。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">守護者の盾が{0}ダメージを防ぎました</t>
+  </si>
+  <si>
+    <t xml:space="preserve">battle.item.attack_negated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Maiden's Thoughts protected you from the attack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少女的心事保护了你，免疫了本次攻击。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">少女の想いがあなたを守り、攻撃を無効化しました。</t>
+  </si>
+  <si>
     <t xml:space="preserve">battle.reward.safe_button</t>
   </si>
   <si>
@@ -2266,9 +2399,6 @@
   </si>
   <si>
     <t xml:space="preserve">battle.reward.greedy_button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欲張る</t>
   </si>
   <si>
     <t xml:space="preserve">battle.reward.summary.turn</t>
@@ -2715,9 +2845,6 @@
     <t xml:space="preserve">Purchase successful.</t>
   </si>
   <si>
-    <t xml:space="preserve">購入しました</t>
-  </si>
-  <si>
     <t xml:space="preserve">shop.purchase.insufficient</t>
   </si>
   <si>
@@ -2813,9 +2940,6 @@
   </si>
   <si>
     <t xml:space="preserve">exchange.title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">交換</t>
   </si>
   <si>
     <t xml:space="preserve">exchange.no_items</t>
@@ -3529,6 +3653,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF032F62"/>
+      <name val="SFMono-Regular"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -3538,12 +3668,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF24292E"/>
-      <name val="SFMono-Regular"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF032F62"/>
       <name val="SFMono-Regular"/>
       <family val="2"/>
     </font>
@@ -3605,7 +3729,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
+        <fgColor rgb="FFFFEEF0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3617,7 +3741,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEEF0"/>
+        <fgColor rgb="FFFFF258"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3643,7 +3767,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3837,13 +3961,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
@@ -3866,11 +3993,14 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="6" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="11" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
@@ -3881,53 +4011,56 @@
     <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="9" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="6" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="8" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="9" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="6" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="6" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="6" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="6" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="8" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="9" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="9" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="12" numFmtId="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="6" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="8" numFmtId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="11" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="12" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="13" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="6" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0">
-      <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4249,10 +4382,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="57"/>
     <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="57"/>
     <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6413,11 +6546,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32"/>
     <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="36"/>
     <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6576,7 +6709,9 @@
       <c r="C6" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="D6" s="52"/>
+      <c r="D6" s="52" t="s">
+        <v>199</v>
+      </c>
       <c r="E6" s="53"/>
       <c r="F6" s="53"/>
       <c r="G6" s="53"/>
@@ -6596,15 +6731,17 @@
     </row>
     <row r="7">
       <c r="A7" s="52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="D7" s="52"/>
+        <v>202</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>203</v>
+      </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
       <c r="G7" s="53"/>
@@ -6624,15 +6761,17 @@
     </row>
     <row r="8">
       <c r="A8" s="52" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="52"/>
+        <v>205</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="E8" s="53"/>
       <c r="F8" s="53"/>
       <c r="G8" s="53"/>
@@ -6652,15 +6791,17 @@
     </row>
     <row r="9">
       <c r="A9" s="52" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" s="52"/>
+        <v>210</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>211</v>
+      </c>
       <c r="E9" s="53"/>
       <c r="F9" s="53"/>
       <c r="G9" s="53"/>
@@ -6680,15 +6821,17 @@
     </row>
     <row r="10">
       <c r="A10" s="56" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" s="52"/>
+        <v>214</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>215</v>
+      </c>
       <c r="E10" s="53"/>
       <c r="F10" s="53"/>
       <c r="G10" s="53"/>
@@ -6709,7 +6852,7 @@
     <row r="11">
       <c r="A11" s="49"/>
       <c r="B11" s="57" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="49"/>
@@ -6732,16 +6875,16 @@
     </row>
     <row r="12">
       <c r="A12" s="56" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E12" s="53"/>
       <c r="F12" s="53"/>
@@ -6762,16 +6905,16 @@
     </row>
     <row r="13">
       <c r="A13" s="56" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B13" s="52" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C13" s="52" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E13" s="53"/>
       <c r="F13" s="53"/>
@@ -6792,16 +6935,16 @@
     </row>
     <row r="14">
       <c r="A14" s="56" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E14" s="53"/>
       <c r="F14" s="53"/>
@@ -6822,16 +6965,16 @@
     </row>
     <row r="15">
       <c r="A15" s="56" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C15" s="52" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E15" s="53"/>
       <c r="F15" s="53"/>
@@ -6852,16 +6995,16 @@
     </row>
     <row r="16">
       <c r="A16" s="56" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="E16" s="53"/>
       <c r="F16" s="53"/>
@@ -6882,16 +7025,16 @@
     </row>
     <row r="17">
       <c r="A17" s="56" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C17" s="52" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D17" s="60" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="E17" s="53"/>
       <c r="F17" s="53"/>
@@ -6912,16 +7055,16 @@
     </row>
     <row customHeight="true" ht="60" r="18">
       <c r="A18" s="56" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C18" s="55" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D18" s="55" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E18" s="53"/>
       <c r="F18" s="53"/>
@@ -6942,16 +7085,16 @@
     </row>
     <row r="19">
       <c r="A19" s="56" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C19" s="55" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D19" s="55" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
@@ -6972,16 +7115,16 @@
     </row>
     <row r="20">
       <c r="A20" s="56" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B20" s="55" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C20" s="55" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D20" s="55" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
@@ -7002,16 +7145,16 @@
     </row>
     <row r="21">
       <c r="A21" s="56" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C21" s="52" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
@@ -7033,7 +7176,7 @@
     <row r="22">
       <c r="A22" s="49"/>
       <c r="B22" s="57" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="49"/>
@@ -7056,15 +7199,17 @@
     </row>
     <row r="23">
       <c r="A23" s="56" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B23" s="58" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D23" s="52"/>
+        <v>260</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>261</v>
+      </c>
       <c r="E23" s="53"/>
       <c r="F23" s="53"/>
       <c r="G23" s="53"/>
@@ -7084,15 +7229,17 @@
     </row>
     <row r="24">
       <c r="A24" s="56" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B24" s="58" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C24" s="52" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" s="52"/>
+        <v>264</v>
+      </c>
+      <c r="D24" s="55" t="s">
+        <v>265</v>
+      </c>
       <c r="E24" s="53"/>
       <c r="F24" s="53"/>
       <c r="G24" s="53"/>
@@ -7112,15 +7259,17 @@
     </row>
     <row r="25">
       <c r="A25" s="56" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="B25" s="59" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C25" s="55" t="s">
-        <v>261</v>
-      </c>
-      <c r="D25" s="52"/>
+        <v>268</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>269</v>
+      </c>
       <c r="E25" s="53"/>
       <c r="F25" s="53"/>
       <c r="G25" s="53"/>
@@ -7140,16 +7289,16 @@
     </row>
     <row r="26">
       <c r="A26" s="56" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B26" s="58" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C26" s="52" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="E26" s="53"/>
       <c r="F26" s="53"/>
@@ -7170,16 +7319,16 @@
     </row>
     <row r="27">
       <c r="A27" s="56" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B27" s="59" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C27" s="55" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="D27" s="55" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="E27" s="58"/>
       <c r="F27" s="53"/>
@@ -7200,16 +7349,16 @@
     </row>
     <row r="28">
       <c r="A28" s="56" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C28" s="52" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E28" s="58"/>
       <c r="F28" s="53"/>
@@ -7230,16 +7379,16 @@
     </row>
     <row r="29">
       <c r="A29" s="56" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B29" s="59" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C29" s="55" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="53"/>
@@ -7260,16 +7409,16 @@
     </row>
     <row r="30">
       <c r="A30" s="56" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B30" s="58" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C30" s="52" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
@@ -7290,16 +7439,16 @@
     </row>
     <row r="31">
       <c r="A31" s="56" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B31" s="59" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D31" s="52" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E31" s="58"/>
       <c r="F31" s="53"/>
@@ -7320,15 +7469,17 @@
     </row>
     <row r="32">
       <c r="A32" s="56" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B32" s="58" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C32" s="52" t="s">
-        <v>287</v>
-      </c>
-      <c r="D32" s="52"/>
+        <v>295</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>295</v>
+      </c>
       <c r="E32" s="58"/>
       <c r="F32" s="58"/>
       <c r="G32" s="58"/>
@@ -7348,15 +7499,17 @@
     </row>
     <row r="33">
       <c r="A33" s="56" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="B33" s="58" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>290</v>
-      </c>
-      <c r="D33" s="52"/>
+        <v>298</v>
+      </c>
+      <c r="D33" s="52" t="s">
+        <v>299</v>
+      </c>
       <c r="E33" s="58"/>
       <c r="F33" s="58"/>
       <c r="G33" s="58"/>
@@ -7376,15 +7529,17 @@
     </row>
     <row r="34">
       <c r="A34" s="56" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B34" s="58" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C34" s="52" t="s">
-        <v>293</v>
-      </c>
-      <c r="D34" s="52"/>
+        <v>302</v>
+      </c>
+      <c r="D34" s="52" t="s">
+        <v>303</v>
+      </c>
       <c r="E34" s="58"/>
       <c r="F34" s="58"/>
       <c r="G34" s="58"/>
@@ -7404,15 +7559,17 @@
     </row>
     <row r="35">
       <c r="A35" s="56" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B35" s="58" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C35" s="52" t="s">
-        <v>296</v>
-      </c>
-      <c r="D35" s="52"/>
+        <v>306</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>307</v>
+      </c>
       <c r="E35" s="58"/>
       <c r="F35" s="58"/>
       <c r="G35" s="58"/>
@@ -7432,16 +7589,16 @@
     </row>
     <row r="36">
       <c r="A36" s="56" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B36" s="58" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C36" s="52" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D36" s="52" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="E36" s="58"/>
       <c r="F36" s="58"/>
@@ -7462,16 +7619,16 @@
     </row>
     <row r="37">
       <c r="A37" s="56" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="B37" s="62" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="C37" s="52" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="E37" s="58"/>
       <c r="F37" s="58"/>
@@ -7492,16 +7649,16 @@
     </row>
     <row r="38">
       <c r="A38" s="56" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B38" s="62" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D38" s="52" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E38" s="58"/>
       <c r="F38" s="58"/>
@@ -7522,16 +7679,16 @@
     </row>
     <row r="39">
       <c r="A39" s="56" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C39" s="52" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D39" s="52" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E39" s="58"/>
       <c r="F39" s="58"/>
@@ -7552,16 +7709,16 @@
     </row>
     <row r="40">
       <c r="A40" s="56" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B40" s="62" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C40" s="52" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D40" s="52" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E40" s="58"/>
       <c r="F40" s="58"/>
@@ -7582,16 +7739,16 @@
     </row>
     <row r="41">
       <c r="A41" s="56" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B41" s="62" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C41" s="52" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D41" s="52" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="E41" s="58"/>
       <c r="F41" s="58"/>
@@ -7612,16 +7769,16 @@
     </row>
     <row r="42">
       <c r="A42" s="56" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B42" s="62" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C42" s="52" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D42" s="52" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E42" s="58"/>
       <c r="F42" s="58"/>
@@ -7642,16 +7799,16 @@
     </row>
     <row r="43">
       <c r="A43" s="56" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B43" s="63" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="C43" s="52" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="D43" s="52" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E43" s="58"/>
       <c r="F43" s="58"/>
@@ -7672,13 +7829,13 @@
     </row>
     <row r="44">
       <c r="A44" s="56" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B44" s="62" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="C44" s="52" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D44" s="52"/>
       <c r="E44" s="58"/>
@@ -7700,16 +7857,16 @@
     </row>
     <row r="45">
       <c r="A45" s="56" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B45" s="62" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="C45" s="52" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="D45" s="52" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="E45" s="58"/>
       <c r="F45" s="58"/>
@@ -7730,16 +7887,16 @@
     </row>
     <row r="46">
       <c r="A46" s="56" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="B46" s="62" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="C46" s="52" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="D46" s="52" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="E46" s="58"/>
       <c r="F46" s="58"/>
@@ -7760,16 +7917,16 @@
     </row>
     <row r="47">
       <c r="A47" s="56" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B47" s="62" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C47" s="52" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D47" s="52" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="E47" s="58"/>
       <c r="F47" s="58"/>
@@ -7790,16 +7947,16 @@
     </row>
     <row r="48">
       <c r="A48" s="56" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B48" s="62" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="C48" s="52" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D48" s="52" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="E48" s="58"/>
       <c r="F48" s="58"/>
@@ -7820,16 +7977,16 @@
     </row>
     <row r="49">
       <c r="A49" s="56" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="C49" s="52" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="D49" s="52" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="E49" s="58"/>
       <c r="F49" s="58"/>
@@ -7850,16 +8007,16 @@
     </row>
     <row r="50">
       <c r="A50" s="56" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C50" s="52" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D50" s="52" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E50" s="58"/>
       <c r="F50" s="58"/>
@@ -7881,7 +8038,7 @@
     <row r="51">
       <c r="A51" s="57"/>
       <c r="B51" s="49" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="C51" s="49"/>
       <c r="D51" s="49"/>
@@ -7904,16 +8061,16 @@
     </row>
     <row r="52">
       <c r="A52" s="56" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C52" s="52" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="D52" s="52" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E52" s="53"/>
       <c r="F52" s="53"/>
@@ -7934,16 +8091,16 @@
     </row>
     <row r="53">
       <c r="A53" s="56" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C53" s="52" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D53" s="52" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E53" s="53"/>
       <c r="F53" s="53"/>
@@ -7964,16 +8121,16 @@
     </row>
     <row r="54">
       <c r="A54" s="56" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="B54" s="58" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="C54" s="52" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="D54" s="52" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E54" s="53"/>
       <c r="F54" s="53"/>
@@ -7994,16 +8151,16 @@
     </row>
     <row r="55">
       <c r="A55" s="56" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="B55" s="58" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="C55" s="52" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D55" s="52" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E55" s="53"/>
       <c r="F55" s="53"/>
@@ -8024,15 +8181,17 @@
     </row>
     <row r="56">
       <c r="A56" s="56" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B56" s="58" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C56" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="D56" s="52"/>
+        <v>386</v>
+      </c>
+      <c r="D56" s="64" t="s">
+        <v>387</v>
+      </c>
       <c r="E56" s="53"/>
       <c r="F56" s="53"/>
       <c r="G56" s="53"/>
@@ -8053,7 +8212,7 @@
     <row r="57">
       <c r="A57" s="57"/>
       <c r="B57" s="49" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C57" s="49"/>
       <c r="D57" s="49"/>
@@ -8076,15 +8235,17 @@
     </row>
     <row r="58">
       <c r="A58" s="56" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B58" s="58" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C58" s="52" t="s">
-        <v>379</v>
-      </c>
-      <c r="D58" s="52"/>
+        <v>391</v>
+      </c>
+      <c r="D58" s="55" t="s">
+        <v>392</v>
+      </c>
       <c r="E58" s="53"/>
       <c r="F58" s="53"/>
       <c r="G58" s="53"/>
@@ -8104,15 +8265,17 @@
     </row>
     <row r="59">
       <c r="A59" s="56" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B59" s="58" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="C59" s="52" t="s">
-        <v>382</v>
-      </c>
-      <c r="D59" s="52"/>
+        <v>395</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>396</v>
+      </c>
       <c r="E59" s="53"/>
       <c r="F59" s="53"/>
       <c r="G59" s="53"/>
@@ -8132,15 +8295,17 @@
     </row>
     <row r="60">
       <c r="A60" s="56" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B60" s="58" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C60" s="52" t="s">
-        <v>385</v>
-      </c>
-      <c r="D60" s="52"/>
+        <v>399</v>
+      </c>
+      <c r="D60" s="52" t="s">
+        <v>400</v>
+      </c>
       <c r="E60" s="53"/>
       <c r="F60" s="53"/>
       <c r="G60" s="53"/>
@@ -8160,15 +8325,17 @@
     </row>
     <row r="61">
       <c r="A61" s="56" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="B61" s="58" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="C61" s="52" t="s">
-        <v>388</v>
-      </c>
-      <c r="D61" s="52"/>
+        <v>403</v>
+      </c>
+      <c r="D61" s="52" t="s">
+        <v>404</v>
+      </c>
       <c r="E61" s="53"/>
       <c r="F61" s="53"/>
       <c r="G61" s="53"/>
@@ -8188,15 +8355,17 @@
     </row>
     <row r="62">
       <c r="A62" s="56" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="B62" s="58" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C62" s="52" t="s">
-        <v>391</v>
-      </c>
-      <c r="D62" s="52"/>
+        <v>407</v>
+      </c>
+      <c r="D62" s="52" t="s">
+        <v>408</v>
+      </c>
       <c r="E62" s="58"/>
       <c r="F62" s="58"/>
       <c r="G62" s="58"/>
@@ -8216,15 +8385,17 @@
     </row>
     <row r="63">
       <c r="A63" s="56" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="B63" s="58" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>394</v>
-      </c>
-      <c r="D63" s="52"/>
+        <v>411</v>
+      </c>
+      <c r="D63" s="52" t="s">
+        <v>412</v>
+      </c>
       <c r="E63" s="58"/>
       <c r="F63" s="58"/>
       <c r="G63" s="58"/>
@@ -8244,15 +8415,17 @@
     </row>
     <row r="64">
       <c r="A64" s="56" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B64" s="58" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C64" s="52" t="s">
-        <v>397</v>
-      </c>
-      <c r="D64" s="52"/>
+        <v>415</v>
+      </c>
+      <c r="D64" s="55" t="s">
+        <v>416</v>
+      </c>
       <c r="E64" s="58"/>
       <c r="F64" s="58"/>
       <c r="G64" s="58"/>
@@ -8272,15 +8445,17 @@
     </row>
     <row r="65">
       <c r="A65" s="56" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="B65" s="58" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="C65" s="52" t="s">
-        <v>400</v>
-      </c>
-      <c r="D65" s="52"/>
+        <v>419</v>
+      </c>
+      <c r="D65" s="52" t="s">
+        <v>420</v>
+      </c>
       <c r="E65" s="58"/>
       <c r="F65" s="58"/>
       <c r="G65" s="58"/>
@@ -8300,15 +8475,17 @@
     </row>
     <row r="66">
       <c r="A66" s="56" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="B66" s="58" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="C66" s="52" t="s">
-        <v>403</v>
-      </c>
-      <c r="D66" s="52"/>
+        <v>423</v>
+      </c>
+      <c r="D66" s="55" t="s">
+        <v>424</v>
+      </c>
       <c r="E66" s="58"/>
       <c r="F66" s="58"/>
       <c r="G66" s="58"/>
@@ -8328,15 +8505,17 @@
     </row>
     <row r="67">
       <c r="A67" s="56" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="B67" s="58" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C67" s="52" t="s">
-        <v>406</v>
-      </c>
-      <c r="D67" s="52"/>
+        <v>427</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>428</v>
+      </c>
       <c r="E67" s="58"/>
       <c r="F67" s="58"/>
       <c r="G67" s="58"/>
@@ -8357,7 +8536,7 @@
     <row r="68">
       <c r="A68" s="57"/>
       <c r="B68" s="49" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C68" s="49"/>
       <c r="D68" s="49"/>
@@ -8380,17 +8559,19 @@
     </row>
     <row r="69">
       <c r="A69" s="56" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="B69" s="59" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C69" s="55" t="s">
-        <v>410</v>
-      </c>
-      <c r="D69" s="52"/>
+        <v>432</v>
+      </c>
+      <c r="D69" s="65" t="s">
+        <v>433</v>
+      </c>
       <c r="E69" s="58" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="F69" s="58"/>
       <c r="G69" s="58"/>
@@ -8411,7 +8592,7 @@
     <row r="70">
       <c r="A70" s="57"/>
       <c r="B70" s="49" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C70" s="49"/>
       <c r="D70" s="49"/>
@@ -8434,15 +8615,17 @@
     </row>
     <row r="71">
       <c r="A71" s="56" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="B71" s="58" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C71" s="52" t="s">
-        <v>415</v>
-      </c>
-      <c r="D71" s="52"/>
+        <v>438</v>
+      </c>
+      <c r="D71" s="52" t="s">
+        <v>439</v>
+      </c>
       <c r="E71" s="53"/>
       <c r="F71" s="53"/>
       <c r="G71" s="53"/>
@@ -8462,15 +8645,17 @@
     </row>
     <row r="72">
       <c r="A72" s="56" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="B72" s="58" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="C72" s="52" t="s">
-        <v>418</v>
-      </c>
-      <c r="D72" s="52"/>
+        <v>442</v>
+      </c>
+      <c r="D72" s="52" t="s">
+        <v>443</v>
+      </c>
       <c r="E72" s="53"/>
       <c r="F72" s="53"/>
       <c r="G72" s="53"/>
@@ -8490,15 +8675,17 @@
     </row>
     <row r="73">
       <c r="A73" s="56" t="s">
-        <v>419</v>
+        <v>444</v>
       </c>
       <c r="B73" s="62" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C73" s="52" t="s">
-        <v>421</v>
-      </c>
-      <c r="D73" s="52"/>
+        <v>446</v>
+      </c>
+      <c r="D73" s="52" t="s">
+        <v>447</v>
+      </c>
       <c r="E73" s="53"/>
       <c r="F73" s="53"/>
       <c r="G73" s="53"/>
@@ -8518,15 +8705,17 @@
     </row>
     <row r="74">
       <c r="A74" s="56" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="B74" s="62" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="C74" s="52" t="s">
-        <v>424</v>
-      </c>
-      <c r="D74" s="52"/>
+        <v>450</v>
+      </c>
+      <c r="D74" s="52" t="s">
+        <v>451</v>
+      </c>
       <c r="E74" s="53"/>
       <c r="F74" s="53"/>
       <c r="G74" s="53"/>
@@ -8546,15 +8735,17 @@
     </row>
     <row r="75">
       <c r="A75" s="56" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="B75" s="62" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="C75" s="52" t="s">
-        <v>427</v>
-      </c>
-      <c r="D75" s="52"/>
+        <v>454</v>
+      </c>
+      <c r="D75" s="52" t="s">
+        <v>455</v>
+      </c>
       <c r="E75" s="53"/>
       <c r="F75" s="53"/>
       <c r="G75" s="53"/>
@@ -8575,7 +8766,7 @@
     <row r="76">
       <c r="A76" s="57"/>
       <c r="B76" s="57" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="C76" s="49"/>
       <c r="D76" s="49"/>
@@ -8597,17 +8788,17 @@
       <c r="T76" s="51"/>
     </row>
     <row customHeight="true" ht="18" r="77">
-      <c r="A77" s="64" t="s">
-        <v>429</v>
-      </c>
-      <c r="B77" s="65" t="s">
-        <v>430</v>
+      <c r="A77" s="66" t="s">
+        <v>457</v>
+      </c>
+      <c r="B77" s="67" t="s">
+        <v>458</v>
       </c>
       <c r="C77" s="55" t="s">
-        <v>431</v>
-      </c>
-      <c r="D77" s="66" t="s">
-        <v>432</v>
+        <v>459</v>
+      </c>
+      <c r="D77" s="55" t="s">
+        <v>460</v>
       </c>
       <c r="E77" s="53"/>
       <c r="F77" s="53"/>
@@ -8628,16 +8819,16 @@
     </row>
     <row r="78">
       <c r="A78" s="56" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B78" s="62" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="C78" s="52" t="s">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="D78" s="52" t="s">
-        <v>436</v>
+        <v>464</v>
       </c>
       <c r="E78" s="53"/>
       <c r="F78" s="53"/>
@@ -8658,16 +8849,16 @@
     </row>
     <row r="79">
       <c r="A79" s="56" t="s">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="B79" s="62" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="C79" s="52" t="s">
-        <v>431</v>
-      </c>
-      <c r="D79" s="66" t="s">
-        <v>439</v>
+        <v>459</v>
+      </c>
+      <c r="D79" s="55" t="s">
+        <v>467</v>
       </c>
       <c r="E79" s="53"/>
       <c r="F79" s="53"/>
@@ -8688,15 +8879,17 @@
     </row>
     <row r="80">
       <c r="A80" s="56" t="s">
-        <v>440</v>
+        <v>468</v>
       </c>
       <c r="B80" s="62" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C80" s="52" t="s">
-        <v>421</v>
-      </c>
-      <c r="D80" s="52"/>
+        <v>446</v>
+      </c>
+      <c r="D80" s="52" t="s">
+        <v>447</v>
+      </c>
       <c r="E80" s="53"/>
       <c r="F80" s="53"/>
       <c r="G80" s="53"/>
@@ -8716,15 +8909,17 @@
     </row>
     <row r="81">
       <c r="A81" s="56" t="s">
-        <v>441</v>
+        <v>469</v>
       </c>
       <c r="B81" s="62" t="s">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C81" s="52" t="s">
-        <v>443</v>
-      </c>
-      <c r="D81" s="52"/>
+        <v>471</v>
+      </c>
+      <c r="D81" s="52" t="s">
+        <v>472</v>
+      </c>
       <c r="E81" s="53"/>
       <c r="F81" s="53"/>
       <c r="G81" s="53"/>
@@ -8744,15 +8939,17 @@
     </row>
     <row r="82">
       <c r="A82" s="56" t="s">
-        <v>444</v>
+        <v>473</v>
       </c>
       <c r="B82" s="62" t="s">
-        <v>445</v>
+        <v>474</v>
       </c>
       <c r="C82" s="52" t="s">
-        <v>446</v>
-      </c>
-      <c r="D82" s="52"/>
+        <v>475</v>
+      </c>
+      <c r="D82" s="52" t="s">
+        <v>476</v>
+      </c>
       <c r="E82" s="53"/>
       <c r="F82" s="53"/>
       <c r="G82" s="53"/>
@@ -8772,15 +8969,17 @@
     </row>
     <row r="83">
       <c r="A83" s="56" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="B83" s="62" t="s">
-        <v>448</v>
+        <v>478</v>
       </c>
       <c r="C83" s="52" t="s">
-        <v>449</v>
-      </c>
-      <c r="D83" s="52"/>
+        <v>479</v>
+      </c>
+      <c r="D83" s="52" t="s">
+        <v>480</v>
+      </c>
       <c r="E83" s="53"/>
       <c r="F83" s="53"/>
       <c r="G83" s="53"/>
@@ -8800,16 +8999,16 @@
     </row>
     <row r="84">
       <c r="A84" s="56" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
       <c r="B84" s="62" t="s">
-        <v>451</v>
+        <v>482</v>
       </c>
       <c r="C84" s="52" t="s">
-        <v>452</v>
+        <v>483</v>
       </c>
       <c r="D84" s="52" t="s">
-        <v>453</v>
+        <v>484</v>
       </c>
       <c r="E84" s="53"/>
       <c r="F84" s="53"/>
@@ -8830,15 +9029,17 @@
     </row>
     <row r="85">
       <c r="A85" s="56" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="B85" s="62" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="C85" s="52" t="s">
-        <v>456</v>
-      </c>
-      <c r="D85" s="52"/>
+        <v>487</v>
+      </c>
+      <c r="D85" s="52" t="s">
+        <v>488</v>
+      </c>
       <c r="E85" s="53"/>
       <c r="F85" s="53"/>
       <c r="G85" s="53"/>
@@ -8859,7 +9060,7 @@
     <row r="86">
       <c r="A86" s="57"/>
       <c r="B86" s="57" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="C86" s="49"/>
       <c r="D86" s="49"/>
@@ -8882,15 +9083,17 @@
     </row>
     <row r="87">
       <c r="A87" s="56" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="B87" s="62" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="C87" s="52" t="s">
-        <v>460</v>
-      </c>
-      <c r="D87" s="52"/>
+        <v>492</v>
+      </c>
+      <c r="D87" s="52" t="s">
+        <v>493</v>
+      </c>
       <c r="E87" s="53"/>
       <c r="F87" s="53"/>
       <c r="G87" s="53"/>
@@ -8911,7 +9114,7 @@
     <row r="88">
       <c r="A88" s="57"/>
       <c r="B88" s="49" t="s">
-        <v>461</v>
+        <v>494</v>
       </c>
       <c r="C88" s="49"/>
       <c r="D88" s="49"/>
@@ -8934,15 +9137,17 @@
     </row>
     <row r="89">
       <c r="A89" s="56" t="s">
-        <v>462</v>
+        <v>495</v>
       </c>
       <c r="B89" s="63" t="s">
-        <v>463</v>
+        <v>496</v>
       </c>
       <c r="C89" s="52" t="s">
-        <v>464</v>
-      </c>
-      <c r="D89" s="52"/>
+        <v>497</v>
+      </c>
+      <c r="D89" s="52" t="s">
+        <v>498</v>
+      </c>
       <c r="E89" s="53"/>
       <c r="F89" s="53"/>
       <c r="G89" s="53"/>
@@ -8962,15 +9167,17 @@
     </row>
     <row r="90">
       <c r="A90" s="56" t="s">
-        <v>465</v>
+        <v>499</v>
       </c>
       <c r="B90" s="63" t="s">
-        <v>466</v>
+        <v>500</v>
       </c>
       <c r="C90" s="52" t="s">
-        <v>467</v>
-      </c>
-      <c r="D90" s="52"/>
+        <v>501</v>
+      </c>
+      <c r="D90" s="52" t="s">
+        <v>502</v>
+      </c>
       <c r="E90" s="53"/>
       <c r="F90" s="53"/>
       <c r="G90" s="53"/>
@@ -8990,15 +9197,17 @@
     </row>
     <row r="91">
       <c r="A91" s="56" t="s">
-        <v>468</v>
+        <v>503</v>
       </c>
       <c r="B91" s="63" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C91" s="52" t="s">
-        <v>421</v>
-      </c>
-      <c r="D91" s="52"/>
+        <v>446</v>
+      </c>
+      <c r="D91" s="52" t="s">
+        <v>447</v>
+      </c>
       <c r="E91" s="53"/>
       <c r="F91" s="53"/>
       <c r="G91" s="53"/>
@@ -9018,15 +9227,17 @@
     </row>
     <row r="92">
       <c r="A92" s="56" t="s">
-        <v>469</v>
+        <v>504</v>
       </c>
       <c r="B92" s="63" t="s">
-        <v>470</v>
+        <v>505</v>
       </c>
       <c r="C92" s="52" t="s">
-        <v>471</v>
-      </c>
-      <c r="D92" s="52"/>
+        <v>506</v>
+      </c>
+      <c r="D92" s="52" t="s">
+        <v>507</v>
+      </c>
       <c r="E92" s="53"/>
       <c r="F92" s="53"/>
       <c r="G92" s="53"/>
@@ -9046,15 +9257,17 @@
     </row>
     <row r="93">
       <c r="A93" s="56" t="s">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="B93" s="63" t="s">
-        <v>470</v>
+        <v>505</v>
       </c>
       <c r="C93" s="52" t="s">
-        <v>473</v>
-      </c>
-      <c r="D93" s="52"/>
+        <v>509</v>
+      </c>
+      <c r="D93" s="52" t="s">
+        <v>510</v>
+      </c>
       <c r="E93" s="53"/>
       <c r="F93" s="53"/>
       <c r="G93" s="53"/>
@@ -9074,15 +9287,17 @@
     </row>
     <row r="94">
       <c r="A94" s="56" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="B94" s="63" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="C94" s="52" t="s">
-        <v>476</v>
-      </c>
-      <c r="D94" s="52"/>
+        <v>513</v>
+      </c>
+      <c r="D94" s="52" t="s">
+        <v>514</v>
+      </c>
       <c r="E94" s="58"/>
       <c r="F94" s="58"/>
       <c r="G94" s="58"/>
@@ -9102,15 +9317,17 @@
     </row>
     <row r="95">
       <c r="A95" s="56" t="s">
-        <v>477</v>
+        <v>515</v>
       </c>
       <c r="B95" s="63" t="s">
-        <v>478</v>
+        <v>516</v>
       </c>
       <c r="C95" s="52" t="s">
-        <v>479</v>
-      </c>
-      <c r="D95" s="52"/>
+        <v>517</v>
+      </c>
+      <c r="D95" s="52" t="s">
+        <v>518</v>
+      </c>
       <c r="E95" s="53"/>
       <c r="F95" s="53"/>
       <c r="G95" s="53"/>
@@ -9130,15 +9347,17 @@
     </row>
     <row r="96">
       <c r="A96" s="56" t="s">
-        <v>480</v>
+        <v>519</v>
       </c>
       <c r="B96" s="63" t="s">
-        <v>481</v>
+        <v>520</v>
       </c>
       <c r="C96" s="52" t="s">
-        <v>482</v>
-      </c>
-      <c r="D96" s="52"/>
+        <v>521</v>
+      </c>
+      <c r="D96" s="55" t="s">
+        <v>522</v>
+      </c>
       <c r="E96" s="53"/>
       <c r="F96" s="53"/>
       <c r="G96" s="53"/>
@@ -9158,15 +9377,17 @@
     </row>
     <row r="97">
       <c r="A97" s="56" t="s">
-        <v>483</v>
+        <v>523</v>
       </c>
       <c r="B97" s="63" t="s">
-        <v>484</v>
+        <v>524</v>
       </c>
       <c r="C97" s="52" t="s">
-        <v>485</v>
-      </c>
-      <c r="D97" s="52"/>
+        <v>525</v>
+      </c>
+      <c r="D97" s="55" t="s">
+        <v>526</v>
+      </c>
       <c r="E97" s="53"/>
       <c r="F97" s="53"/>
       <c r="G97" s="53"/>
@@ -9187,7 +9408,7 @@
     <row r="98">
       <c r="A98" s="57"/>
       <c r="B98" s="57" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="C98" s="49"/>
       <c r="D98" s="49"/>
@@ -9210,16 +9431,16 @@
     </row>
     <row r="99">
       <c r="A99" s="56" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="B99" s="56" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="C99" s="52" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="D99" s="52" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="E99" s="53"/>
       <c r="F99" s="53"/>
@@ -9241,7 +9462,7 @@
     <row r="100">
       <c r="A100" s="57"/>
       <c r="B100" s="49" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="C100" s="49"/>
       <c r="D100" s="49"/>
@@ -9264,16 +9485,16 @@
     </row>
     <row r="101">
       <c r="A101" s="56" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="B101" s="52" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="C101" s="52" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="D101" s="52" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="E101" s="53"/>
       <c r="F101" s="53"/>
@@ -9294,16 +9515,16 @@
     </row>
     <row r="102">
       <c r="A102" s="56" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="B102" s="52" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C102" s="52" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="D102" s="52" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="E102" s="53"/>
       <c r="F102" s="53"/>
@@ -9324,16 +9545,16 @@
     </row>
     <row r="103">
       <c r="A103" s="56" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="B103" s="52" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="C103" s="52" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="D103" s="52" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="E103" s="53"/>
       <c r="F103" s="53"/>
@@ -9354,16 +9575,16 @@
     </row>
     <row r="104">
       <c r="A104" s="56" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="B104" s="52" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="C104" s="52" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="D104" s="52" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="E104" s="53"/>
       <c r="F104" s="53"/>
@@ -9384,16 +9605,16 @@
     </row>
     <row r="105">
       <c r="A105" s="56" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="B105" s="56" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="C105" s="52" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="D105" s="52" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="E105" s="53"/>
       <c r="F105" s="53"/>
@@ -9414,16 +9635,16 @@
     </row>
     <row r="106">
       <c r="A106" s="56" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="B106" s="56" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="C106" s="52" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="D106" s="52" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="E106" s="53"/>
       <c r="F106" s="53"/>
@@ -9444,16 +9665,16 @@
     </row>
     <row r="107">
       <c r="A107" s="56" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="B107" s="56" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="C107" s="52" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="D107" s="52" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="E107" s="53"/>
       <c r="F107" s="53"/>
@@ -9474,16 +9695,16 @@
     </row>
     <row r="108">
       <c r="A108" s="56" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="B108" s="56" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="C108" s="52" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="D108" s="52" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="E108" s="53"/>
       <c r="F108" s="53"/>
@@ -9504,16 +9725,16 @@
     </row>
     <row r="109">
       <c r="A109" s="56" t="s">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="B109" s="56" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="C109" s="52" t="s">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="D109" s="52" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="E109" s="53"/>
       <c r="F109" s="53"/>
@@ -9534,16 +9755,16 @@
     </row>
     <row r="110">
       <c r="A110" s="56" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="B110" s="56" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="C110" s="52" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="D110" s="52" t="s">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="E110" s="53"/>
       <c r="F110" s="53"/>
@@ -9564,16 +9785,16 @@
     </row>
     <row r="111">
       <c r="A111" s="56" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="B111" s="52" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="C111" s="52" t="s">
-        <v>534</v>
+        <v>575</v>
       </c>
       <c r="D111" s="52" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="E111" s="53"/>
       <c r="F111" s="53"/>
@@ -9594,16 +9815,16 @@
     </row>
     <row r="112">
       <c r="A112" s="56" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="B112" s="52" t="s">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="C112" s="52" t="s">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="D112" s="52" t="s">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="E112" s="53"/>
       <c r="F112" s="53"/>
@@ -9624,16 +9845,16 @@
     </row>
     <row r="113">
       <c r="A113" s="56" t="s">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="B113" s="52" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="C113" s="52" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="D113" s="52" t="s">
-        <v>543</v>
+        <v>584</v>
       </c>
       <c r="E113" s="53"/>
       <c r="F113" s="53"/>
@@ -9653,9 +9874,9 @@
       <c r="T113" s="54"/>
     </row>
     <row r="114">
-      <c r="A114" s="67"/>
+      <c r="A114" s="68"/>
       <c r="B114" s="57" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="C114" s="57"/>
       <c r="D114" s="57"/>
@@ -9677,12 +9898,12 @@
       <c r="T114" s="54"/>
     </row>
     <row r="115">
-      <c r="A115" s="68"/>
-      <c r="B115" s="69"/>
-      <c r="C115" s="69" t="s">
-        <v>545</v>
-      </c>
-      <c r="D115" s="69"/>
+      <c r="A115" s="69"/>
+      <c r="B115" s="70"/>
+      <c r="C115" s="70" t="s">
+        <v>586</v>
+      </c>
+      <c r="D115" s="70"/>
       <c r="E115" s="53"/>
       <c r="F115" s="53"/>
       <c r="G115" s="53"/>
@@ -9702,16 +9923,16 @@
     </row>
     <row r="116">
       <c r="A116" s="56" t="s">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="B116" s="52" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="C116" s="52" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="D116" s="52" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="E116" s="53"/>
       <c r="F116" s="53"/>
@@ -9732,7 +9953,7 @@
     </row>
     <row r="117">
       <c r="A117" s="56" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="B117" s="52" t="s">
         <v>182</v>
@@ -9741,7 +9962,7 @@
         <v>182</v>
       </c>
       <c r="D117" s="52" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="E117" s="53"/>
       <c r="F117" s="53"/>
@@ -9762,7 +9983,7 @@
     </row>
     <row r="118">
       <c r="A118" s="56" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="B118" s="52" t="s">
         <v>189</v>
@@ -9792,16 +10013,16 @@
     </row>
     <row r="119">
       <c r="A119" s="56" t="s">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="B119" s="52" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="C119" s="52" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="D119" s="52" t="s">
-        <v>555</v>
+        <v>596</v>
       </c>
       <c r="E119" s="53"/>
       <c r="F119" s="53"/>
@@ -9822,16 +10043,16 @@
     </row>
     <row r="120">
       <c r="A120" s="56" t="s">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="B120" s="52" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="C120" s="52" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="D120" s="52" t="s">
-        <v>557</v>
+        <v>307</v>
       </c>
       <c r="E120" s="53"/>
       <c r="F120" s="53"/>
@@ -9852,16 +10073,16 @@
     </row>
     <row r="121">
       <c r="A121" s="56" t="s">
-        <v>558</v>
+        <v>598</v>
       </c>
       <c r="B121" s="52" t="s">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="C121" s="52" t="s">
-        <v>421</v>
+        <v>446</v>
       </c>
       <c r="D121" s="52" t="s">
-        <v>559</v>
+        <v>447</v>
       </c>
       <c r="E121" s="53"/>
       <c r="F121" s="53"/>
@@ -9882,16 +10103,16 @@
     </row>
     <row r="122">
       <c r="A122" s="56" t="s">
-        <v>560</v>
+        <v>599</v>
       </c>
       <c r="B122" s="52" t="s">
-        <v>561</v>
+        <v>600</v>
       </c>
       <c r="C122" s="52" t="s">
-        <v>562</v>
+        <v>601</v>
       </c>
       <c r="D122" s="52" t="s">
-        <v>563</v>
+        <v>602</v>
       </c>
       <c r="E122" s="53"/>
       <c r="F122" s="53"/>
@@ -9912,16 +10133,16 @@
     </row>
     <row r="123">
       <c r="A123" s="56" t="s">
-        <v>564</v>
+        <v>603</v>
       </c>
       <c r="B123" s="52" t="s">
-        <v>565</v>
+        <v>604</v>
       </c>
       <c r="C123" s="52" t="s">
-        <v>566</v>
+        <v>605</v>
       </c>
       <c r="D123" s="52" t="s">
-        <v>567</v>
+        <v>606</v>
       </c>
       <c r="E123" s="53"/>
       <c r="F123" s="53"/>
@@ -9942,16 +10163,16 @@
     </row>
     <row r="124">
       <c r="A124" s="56" t="s">
-        <v>568</v>
+        <v>607</v>
       </c>
       <c r="B124" s="52" t="s">
-        <v>569</v>
+        <v>608</v>
       </c>
       <c r="C124" s="52" t="s">
-        <v>570</v>
+        <v>609</v>
       </c>
       <c r="D124" s="52" t="s">
-        <v>571</v>
+        <v>610</v>
       </c>
       <c r="E124" s="53"/>
       <c r="F124" s="53"/>
@@ -9972,16 +10193,16 @@
     </row>
     <row r="125">
       <c r="A125" s="56" t="s">
-        <v>572</v>
+        <v>611</v>
       </c>
       <c r="B125" s="52" t="s">
-        <v>573</v>
+        <v>612</v>
       </c>
       <c r="C125" s="52" t="s">
-        <v>574</v>
+        <v>613</v>
       </c>
       <c r="D125" s="52" t="s">
-        <v>575</v>
+        <v>614</v>
       </c>
       <c r="E125" s="53"/>
       <c r="F125" s="53"/>
@@ -10001,47 +10222,47 @@
       <c r="T125" s="54"/>
     </row>
     <row r="126">
-      <c r="A126" s="70" t="s">
-        <v>576</v>
-      </c>
-      <c r="B126" s="71" t="s">
-        <v>577</v>
-      </c>
-      <c r="C126" s="71" t="s">
-        <v>578</v>
-      </c>
-      <c r="D126" s="71" t="s">
-        <v>579</v>
-      </c>
-      <c r="E126" s="72"/>
-      <c r="F126" s="72"/>
-      <c r="G126" s="72"/>
-      <c r="H126" s="72"/>
-      <c r="I126" s="72"/>
-      <c r="J126" s="72"/>
-      <c r="K126" s="72"/>
-      <c r="L126" s="72"/>
-      <c r="M126" s="73"/>
-      <c r="N126" s="73"/>
-      <c r="O126" s="73"/>
-      <c r="P126" s="73"/>
-      <c r="Q126" s="73"/>
-      <c r="R126" s="73"/>
-      <c r="S126" s="73"/>
-      <c r="T126" s="73"/>
+      <c r="A126" s="71" t="s">
+        <v>615</v>
+      </c>
+      <c r="B126" s="72" t="s">
+        <v>616</v>
+      </c>
+      <c r="C126" s="72" t="s">
+        <v>617</v>
+      </c>
+      <c r="D126" s="72" t="s">
+        <v>618</v>
+      </c>
+      <c r="E126" s="73"/>
+      <c r="F126" s="73"/>
+      <c r="G126" s="73"/>
+      <c r="H126" s="73"/>
+      <c r="I126" s="73"/>
+      <c r="J126" s="73"/>
+      <c r="K126" s="73"/>
+      <c r="L126" s="73"/>
+      <c r="M126" s="74"/>
+      <c r="N126" s="74"/>
+      <c r="O126" s="74"/>
+      <c r="P126" s="74"/>
+      <c r="Q126" s="74"/>
+      <c r="R126" s="74"/>
+      <c r="S126" s="74"/>
+      <c r="T126" s="74"/>
     </row>
     <row r="127">
       <c r="A127" s="56" t="s">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="B127" s="52" t="s">
-        <v>581</v>
+        <v>620</v>
       </c>
       <c r="C127" s="52" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="D127" s="52" t="s">
-        <v>582</v>
+        <v>621</v>
       </c>
       <c r="E127" s="53"/>
       <c r="F127" s="53"/>
@@ -10062,16 +10283,16 @@
     </row>
     <row r="128">
       <c r="A128" s="56" t="s">
-        <v>583</v>
+        <v>622</v>
       </c>
       <c r="B128" s="52" t="s">
-        <v>584</v>
+        <v>623</v>
       </c>
       <c r="C128" s="52" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D128" s="52" t="s">
-        <v>585</v>
+        <v>303</v>
       </c>
       <c r="E128" s="53"/>
       <c r="F128" s="53"/>
@@ -10092,16 +10313,16 @@
     </row>
     <row r="129">
       <c r="A129" s="56" t="s">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="B129" s="52" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C129" s="52" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D129" s="52" t="s">
-        <v>585</v>
+        <v>303</v>
       </c>
       <c r="E129" s="53"/>
       <c r="F129" s="53"/>
@@ -10122,16 +10343,16 @@
     </row>
     <row r="130">
       <c r="A130" s="56" t="s">
-        <v>587</v>
+        <v>625</v>
       </c>
       <c r="B130" s="52" t="s">
-        <v>588</v>
+        <v>626</v>
       </c>
       <c r="C130" s="52" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D130" s="52" t="s">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="E130" s="53"/>
       <c r="F130" s="53"/>
@@ -10152,16 +10373,16 @@
     </row>
     <row r="131">
       <c r="A131" s="56" t="s">
-        <v>590</v>
+        <v>628</v>
       </c>
       <c r="B131" s="52" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C131" s="52" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D131" s="52" t="s">
-        <v>591</v>
+        <v>261</v>
       </c>
       <c r="E131" s="53"/>
       <c r="F131" s="53"/>
@@ -10182,16 +10403,16 @@
     </row>
     <row r="132">
       <c r="A132" s="56" t="s">
-        <v>592</v>
+        <v>629</v>
       </c>
       <c r="B132" s="52" t="s">
-        <v>470</v>
+        <v>505</v>
       </c>
       <c r="C132" s="52" t="s">
-        <v>471</v>
+        <v>509</v>
       </c>
       <c r="D132" s="52" t="s">
-        <v>593</v>
+        <v>510</v>
       </c>
       <c r="E132" s="53"/>
       <c r="F132" s="53"/>
@@ -10211,77 +10432,77 @@
       <c r="T132" s="54"/>
     </row>
     <row r="133">
-      <c r="A133" s="70" t="s">
-        <v>594</v>
-      </c>
-      <c r="B133" s="71" t="s">
-        <v>595</v>
-      </c>
-      <c r="C133" s="71" t="s">
-        <v>596</v>
-      </c>
-      <c r="D133" s="71" t="s">
-        <v>597</v>
-      </c>
-      <c r="E133" s="72"/>
-      <c r="F133" s="72"/>
-      <c r="G133" s="72"/>
-      <c r="H133" s="72"/>
-      <c r="I133" s="72"/>
-      <c r="J133" s="72"/>
-      <c r="K133" s="72"/>
-      <c r="L133" s="72"/>
-      <c r="M133" s="73"/>
-      <c r="N133" s="73"/>
-      <c r="O133" s="73"/>
-      <c r="P133" s="73"/>
-      <c r="Q133" s="73"/>
-      <c r="R133" s="73"/>
-      <c r="S133" s="73"/>
-      <c r="T133" s="73"/>
+      <c r="A133" s="71" t="s">
+        <v>630</v>
+      </c>
+      <c r="B133" s="72" t="s">
+        <v>631</v>
+      </c>
+      <c r="C133" s="72" t="s">
+        <v>632</v>
+      </c>
+      <c r="D133" s="72" t="s">
+        <v>633</v>
+      </c>
+      <c r="E133" s="73"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="73"/>
+      <c r="H133" s="73"/>
+      <c r="I133" s="73"/>
+      <c r="J133" s="73"/>
+      <c r="K133" s="73"/>
+      <c r="L133" s="73"/>
+      <c r="M133" s="74"/>
+      <c r="N133" s="74"/>
+      <c r="O133" s="74"/>
+      <c r="P133" s="74"/>
+      <c r="Q133" s="74"/>
+      <c r="R133" s="74"/>
+      <c r="S133" s="74"/>
+      <c r="T133" s="74"/>
     </row>
     <row r="134">
-      <c r="A134" s="70" t="s">
-        <v>598</v>
-      </c>
-      <c r="B134" s="71" t="s">
-        <v>599</v>
-      </c>
-      <c r="C134" s="71" t="s">
-        <v>600</v>
-      </c>
-      <c r="D134" s="71" t="s">
-        <v>601</v>
-      </c>
-      <c r="E134" s="72"/>
-      <c r="F134" s="72"/>
-      <c r="G134" s="72"/>
-      <c r="H134" s="72"/>
-      <c r="I134" s="72"/>
-      <c r="J134" s="72"/>
-      <c r="K134" s="72"/>
-      <c r="L134" s="72"/>
-      <c r="M134" s="73"/>
-      <c r="N134" s="73"/>
-      <c r="O134" s="73"/>
-      <c r="P134" s="73"/>
-      <c r="Q134" s="73"/>
-      <c r="R134" s="73"/>
-      <c r="S134" s="73"/>
-      <c r="T134" s="73"/>
-    </row>
-    <row r="135">
+      <c r="A134" s="71" t="s">
+        <v>634</v>
+      </c>
+      <c r="B134" s="72" t="s">
+        <v>635</v>
+      </c>
+      <c r="C134" s="72" t="s">
+        <v>636</v>
+      </c>
+      <c r="D134" s="72" t="s">
+        <v>637</v>
+      </c>
+      <c r="E134" s="73"/>
+      <c r="F134" s="73"/>
+      <c r="G134" s="73"/>
+      <c r="H134" s="73"/>
+      <c r="I134" s="73"/>
+      <c r="J134" s="73"/>
+      <c r="K134" s="73"/>
+      <c r="L134" s="73"/>
+      <c r="M134" s="74"/>
+      <c r="N134" s="74"/>
+      <c r="O134" s="74"/>
+      <c r="P134" s="74"/>
+      <c r="Q134" s="74"/>
+      <c r="R134" s="74"/>
+      <c r="S134" s="74"/>
+      <c r="T134" s="74"/>
+    </row>
+    <row customHeight="true" ht="27" r="135">
       <c r="A135" s="56" t="s">
-        <v>602</v>
+        <v>638</v>
       </c>
       <c r="B135" s="52" t="s">
-        <v>603</v>
-      </c>
-      <c r="C135" s="52" t="s">
-        <v>604</v>
-      </c>
-      <c r="D135" s="52" t="s">
-        <v>605</v>
+        <v>639</v>
+      </c>
+      <c r="C135" s="55" t="s">
+        <v>640</v>
+      </c>
+      <c r="D135" s="75" t="s">
+        <v>641</v>
       </c>
       <c r="E135" s="53"/>
       <c r="F135" s="53"/>
@@ -10302,16 +10523,16 @@
     </row>
     <row r="136">
       <c r="A136" s="56" t="s">
-        <v>606</v>
+        <v>642</v>
       </c>
       <c r="B136" s="52" t="s">
-        <v>607</v>
+        <v>643</v>
       </c>
       <c r="C136" s="52" t="s">
-        <v>608</v>
+        <v>644</v>
       </c>
       <c r="D136" s="52" t="s">
-        <v>608</v>
+        <v>644</v>
       </c>
       <c r="E136" s="53"/>
       <c r="F136" s="53"/>
@@ -10332,16 +10553,16 @@
     </row>
     <row r="137">
       <c r="A137" s="56" t="s">
-        <v>609</v>
+        <v>645</v>
       </c>
       <c r="B137" s="52" t="s">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="C137" s="52" t="s">
-        <v>611</v>
+        <v>647</v>
       </c>
       <c r="D137" s="52" t="s">
-        <v>612</v>
+        <v>648</v>
       </c>
       <c r="E137" s="53"/>
       <c r="F137" s="53"/>
@@ -10362,16 +10583,16 @@
     </row>
     <row r="138">
       <c r="A138" s="56" t="s">
-        <v>613</v>
+        <v>649</v>
       </c>
       <c r="B138" s="55" t="s">
-        <v>614</v>
+        <v>650</v>
       </c>
       <c r="C138" s="55" t="s">
-        <v>615</v>
+        <v>651</v>
       </c>
       <c r="D138" s="52" t="s">
-        <v>616</v>
+        <v>652</v>
       </c>
       <c r="E138" s="53"/>
       <c r="F138" s="53"/>
@@ -10392,16 +10613,16 @@
     </row>
     <row r="139">
       <c r="A139" s="56" t="s">
-        <v>617</v>
+        <v>653</v>
       </c>
       <c r="B139" s="52" t="s">
-        <v>618</v>
+        <v>654</v>
       </c>
       <c r="C139" s="52" t="s">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="D139" s="52" t="s">
-        <v>620</v>
+        <v>656</v>
       </c>
       <c r="E139" s="53"/>
       <c r="F139" s="53"/>
@@ -10422,16 +10643,16 @@
     </row>
     <row r="140">
       <c r="A140" s="56" t="s">
-        <v>621</v>
+        <v>657</v>
       </c>
       <c r="B140" s="55" t="s">
-        <v>622</v>
+        <v>658</v>
       </c>
       <c r="C140" s="55" t="s">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="D140" s="52" t="s">
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="E140" s="53"/>
       <c r="F140" s="53"/>
@@ -10452,16 +10673,16 @@
     </row>
     <row r="141">
       <c r="A141" s="56" t="s">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="B141" s="52" t="s">
-        <v>626</v>
+        <v>662</v>
       </c>
       <c r="C141" s="52" t="s">
-        <v>626</v>
+        <v>662</v>
       </c>
       <c r="D141" s="52" t="s">
-        <v>626</v>
+        <v>662</v>
       </c>
       <c r="E141" s="53"/>
       <c r="F141" s="53"/>
@@ -10482,16 +10703,16 @@
     </row>
     <row r="142">
       <c r="A142" s="56" t="s">
-        <v>627</v>
+        <v>663</v>
       </c>
       <c r="B142" s="52" t="s">
-        <v>628</v>
+        <v>664</v>
       </c>
       <c r="C142" s="52" t="s">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="D142" s="52" t="s">
-        <v>630</v>
+        <v>666</v>
       </c>
       <c r="E142" s="53"/>
       <c r="F142" s="53"/>
@@ -10512,16 +10733,16 @@
     </row>
     <row r="143">
       <c r="A143" s="56" t="s">
-        <v>631</v>
+        <v>667</v>
       </c>
       <c r="B143" s="52" t="s">
-        <v>632</v>
+        <v>668</v>
       </c>
       <c r="C143" s="52" t="s">
-        <v>633</v>
+        <v>669</v>
       </c>
       <c r="D143" s="52" t="s">
-        <v>634</v>
+        <v>670</v>
       </c>
       <c r="E143" s="53"/>
       <c r="F143" s="53"/>
@@ -10542,16 +10763,16 @@
     </row>
     <row r="144">
       <c r="A144" s="56" t="s">
-        <v>635</v>
+        <v>671</v>
       </c>
       <c r="B144" s="52" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="C144" s="52" t="s">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="D144" s="52" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="E144" s="53"/>
       <c r="F144" s="53"/>
@@ -10572,16 +10793,16 @@
     </row>
     <row r="145">
       <c r="A145" s="56" t="s">
-        <v>639</v>
+        <v>675</v>
       </c>
       <c r="B145" s="55" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="C145" s="55" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="D145" s="52" t="s">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="E145" s="53"/>
       <c r="F145" s="53"/>
@@ -10602,16 +10823,16 @@
     </row>
     <row r="146">
       <c r="A146" s="56" t="s">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="B146" s="55" t="s">
-        <v>644</v>
+        <v>680</v>
       </c>
       <c r="C146" s="52" t="s">
-        <v>645</v>
+        <v>681</v>
       </c>
       <c r="D146" s="52" t="s">
-        <v>646</v>
+        <v>682</v>
       </c>
       <c r="E146" s="53"/>
       <c r="F146" s="53"/>
@@ -10632,16 +10853,16 @@
     </row>
     <row r="147">
       <c r="A147" s="56" t="s">
-        <v>647</v>
+        <v>683</v>
       </c>
       <c r="B147" s="52" t="s">
-        <v>648</v>
+        <v>684</v>
       </c>
       <c r="C147" s="52" t="s">
-        <v>649</v>
+        <v>685</v>
       </c>
       <c r="D147" s="52" t="s">
-        <v>650</v>
+        <v>686</v>
       </c>
       <c r="E147" s="53"/>
       <c r="F147" s="53"/>
@@ -10662,16 +10883,16 @@
     </row>
     <row r="148">
       <c r="A148" s="56" t="s">
-        <v>651</v>
+        <v>687</v>
       </c>
       <c r="B148" s="52" t="s">
-        <v>652</v>
+        <v>688</v>
       </c>
       <c r="C148" s="52" t="s">
-        <v>653</v>
+        <v>689</v>
       </c>
       <c r="D148" s="52" t="s">
-        <v>654</v>
+        <v>690</v>
       </c>
       <c r="E148" s="53"/>
       <c r="F148" s="53"/>
@@ -10691,47 +10912,47 @@
       <c r="T148" s="54"/>
     </row>
     <row r="149">
-      <c r="A149" s="70" t="s">
-        <v>655</v>
-      </c>
-      <c r="B149" s="71" t="s">
-        <v>656</v>
-      </c>
-      <c r="C149" s="71" t="s">
-        <v>657</v>
-      </c>
-      <c r="D149" s="71" t="s">
-        <v>658</v>
-      </c>
-      <c r="E149" s="72"/>
-      <c r="F149" s="72"/>
-      <c r="G149" s="72"/>
-      <c r="H149" s="72"/>
-      <c r="I149" s="72"/>
-      <c r="J149" s="72"/>
-      <c r="K149" s="72"/>
-      <c r="L149" s="72"/>
-      <c r="M149" s="73"/>
-      <c r="N149" s="73"/>
-      <c r="O149" s="73"/>
-      <c r="P149" s="73"/>
-      <c r="Q149" s="73"/>
-      <c r="R149" s="73"/>
-      <c r="S149" s="73"/>
-      <c r="T149" s="73"/>
+      <c r="A149" s="71" t="s">
+        <v>691</v>
+      </c>
+      <c r="B149" s="72" t="s">
+        <v>692</v>
+      </c>
+      <c r="C149" s="72" t="s">
+        <v>693</v>
+      </c>
+      <c r="D149" s="72" t="s">
+        <v>694</v>
+      </c>
+      <c r="E149" s="73"/>
+      <c r="F149" s="73"/>
+      <c r="G149" s="73"/>
+      <c r="H149" s="73"/>
+      <c r="I149" s="73"/>
+      <c r="J149" s="73"/>
+      <c r="K149" s="73"/>
+      <c r="L149" s="73"/>
+      <c r="M149" s="74"/>
+      <c r="N149" s="74"/>
+      <c r="O149" s="74"/>
+      <c r="P149" s="74"/>
+      <c r="Q149" s="74"/>
+      <c r="R149" s="74"/>
+      <c r="S149" s="74"/>
+      <c r="T149" s="74"/>
     </row>
     <row r="150">
       <c r="A150" s="56" t="s">
-        <v>659</v>
+        <v>695</v>
       </c>
       <c r="B150" s="52" t="s">
-        <v>660</v>
+        <v>696</v>
       </c>
       <c r="C150" s="52" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D150" s="52" t="s">
-        <v>661</v>
+        <v>697</v>
       </c>
       <c r="E150" s="53"/>
       <c r="F150" s="53"/>
@@ -10752,16 +10973,16 @@
     </row>
     <row r="151">
       <c r="A151" s="56" t="s">
-        <v>662</v>
+        <v>698</v>
       </c>
       <c r="B151" s="52" t="s">
-        <v>663</v>
+        <v>699</v>
       </c>
       <c r="C151" s="52" t="s">
-        <v>664</v>
+        <v>700</v>
       </c>
       <c r="D151" s="52" t="s">
-        <v>665</v>
+        <v>701</v>
       </c>
       <c r="E151" s="53"/>
       <c r="F151" s="53"/>
@@ -10782,16 +11003,16 @@
     </row>
     <row r="152">
       <c r="A152" s="56" t="s">
-        <v>666</v>
+        <v>702</v>
       </c>
       <c r="B152" s="52" t="s">
-        <v>667</v>
+        <v>703</v>
       </c>
       <c r="C152" s="52" t="s">
-        <v>668</v>
+        <v>704</v>
       </c>
       <c r="D152" s="52" t="s">
-        <v>669</v>
+        <v>705</v>
       </c>
       <c r="E152" s="53"/>
       <c r="F152" s="53"/>
@@ -10812,16 +11033,16 @@
     </row>
     <row r="153">
       <c r="A153" s="56" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="B153" s="52" t="s">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="C153" s="52" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="D153" s="52" t="s">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="E153" s="53"/>
       <c r="F153" s="53"/>
@@ -10842,16 +11063,16 @@
     </row>
     <row r="154">
       <c r="A154" s="56" t="s">
-        <v>674</v>
+        <v>710</v>
       </c>
       <c r="B154" s="52" t="s">
-        <v>675</v>
+        <v>711</v>
       </c>
       <c r="C154" s="52" t="s">
-        <v>676</v>
+        <v>712</v>
       </c>
       <c r="D154" s="52" t="s">
-        <v>677</v>
+        <v>713</v>
       </c>
       <c r="E154" s="53"/>
       <c r="F154" s="53"/>
@@ -10872,16 +11093,16 @@
     </row>
     <row r="155">
       <c r="A155" s="56" t="s">
-        <v>678</v>
+        <v>714</v>
       </c>
       <c r="B155" s="52" t="s">
-        <v>679</v>
+        <v>715</v>
       </c>
       <c r="C155" s="55" t="s">
-        <v>680</v>
+        <v>716</v>
       </c>
       <c r="D155" s="52" t="s">
-        <v>681</v>
+        <v>717</v>
       </c>
       <c r="E155" s="53"/>
       <c r="F155" s="53"/>
@@ -10902,16 +11123,16 @@
     </row>
     <row r="156">
       <c r="A156" s="56" t="s">
-        <v>682</v>
+        <v>718</v>
       </c>
       <c r="B156" s="52" t="s">
-        <v>683</v>
+        <v>719</v>
       </c>
       <c r="C156" s="52" t="s">
-        <v>684</v>
+        <v>720</v>
       </c>
       <c r="D156" s="52" t="s">
-        <v>685</v>
+        <v>721</v>
       </c>
       <c r="E156" s="53"/>
       <c r="F156" s="53"/>
@@ -10932,16 +11153,16 @@
     </row>
     <row r="157">
       <c r="A157" s="56" t="s">
-        <v>686</v>
+        <v>722</v>
       </c>
       <c r="B157" s="52" t="s">
-        <v>687</v>
+        <v>723</v>
       </c>
       <c r="C157" s="52" t="s">
-        <v>688</v>
+        <v>724</v>
       </c>
       <c r="D157" s="52" t="s">
-        <v>689</v>
+        <v>725</v>
       </c>
       <c r="E157" s="53"/>
       <c r="F157" s="53"/>
@@ -10962,16 +11183,16 @@
     </row>
     <row r="158">
       <c r="A158" s="56" t="s">
-        <v>690</v>
+        <v>726</v>
       </c>
       <c r="B158" s="52" t="s">
-        <v>691</v>
+        <v>727</v>
       </c>
       <c r="C158" s="52" t="s">
-        <v>692</v>
+        <v>728</v>
       </c>
       <c r="D158" s="52" t="s">
-        <v>693</v>
+        <v>729</v>
       </c>
       <c r="E158" s="53"/>
       <c r="F158" s="53"/>
@@ -10992,16 +11213,16 @@
     </row>
     <row r="159">
       <c r="A159" s="56" t="s">
-        <v>694</v>
+        <v>730</v>
       </c>
       <c r="B159" s="52" t="s">
-        <v>695</v>
+        <v>731</v>
       </c>
       <c r="C159" s="52" t="s">
-        <v>696</v>
+        <v>732</v>
       </c>
       <c r="D159" s="52" t="s">
-        <v>697</v>
+        <v>733</v>
       </c>
       <c r="E159" s="53"/>
       <c r="F159" s="53"/>
@@ -11022,16 +11243,16 @@
     </row>
     <row r="160">
       <c r="A160" s="56" t="s">
-        <v>698</v>
+        <v>734</v>
       </c>
       <c r="B160" s="52" t="s">
-        <v>699</v>
+        <v>735</v>
       </c>
       <c r="C160" s="52" t="s">
-        <v>700</v>
+        <v>736</v>
       </c>
       <c r="D160" s="52" t="s">
-        <v>701</v>
+        <v>737</v>
       </c>
       <c r="E160" s="53"/>
       <c r="F160" s="53"/>
@@ -11052,16 +11273,16 @@
     </row>
     <row r="161">
       <c r="A161" s="56" t="s">
-        <v>702</v>
+        <v>738</v>
       </c>
       <c r="B161" s="52" t="s">
-        <v>703</v>
+        <v>739</v>
       </c>
       <c r="C161" s="52" t="s">
-        <v>704</v>
+        <v>740</v>
       </c>
       <c r="D161" s="52" t="s">
-        <v>705</v>
+        <v>741</v>
       </c>
       <c r="E161" s="53"/>
       <c r="F161" s="53"/>
@@ -11082,16 +11303,16 @@
     </row>
     <row r="162">
       <c r="A162" s="56" t="s">
-        <v>706</v>
+        <v>742</v>
       </c>
       <c r="B162" s="52" t="s">
-        <v>707</v>
+        <v>743</v>
       </c>
       <c r="C162" s="52" t="s">
-        <v>708</v>
+        <v>744</v>
       </c>
       <c r="D162" s="52" t="s">
-        <v>709</v>
+        <v>745</v>
       </c>
       <c r="E162" s="53"/>
       <c r="F162" s="53"/>
@@ -11112,16 +11333,16 @@
     </row>
     <row r="163">
       <c r="A163" s="56" t="s">
-        <v>710</v>
+        <v>746</v>
       </c>
       <c r="B163" s="52" t="s">
-        <v>711</v>
+        <v>747</v>
       </c>
       <c r="C163" s="52" t="s">
-        <v>712</v>
+        <v>748</v>
       </c>
       <c r="D163" s="52" t="s">
-        <v>713</v>
+        <v>749</v>
       </c>
       <c r="E163" s="53"/>
       <c r="F163" s="53"/>
@@ -11142,16 +11363,16 @@
     </row>
     <row r="164">
       <c r="A164" s="56" t="s">
-        <v>714</v>
+        <v>750</v>
       </c>
       <c r="B164" s="52" t="s">
-        <v>715</v>
+        <v>751</v>
       </c>
       <c r="C164" s="52" t="s">
-        <v>716</v>
+        <v>752</v>
       </c>
       <c r="D164" s="52" t="s">
-        <v>717</v>
+        <v>753</v>
       </c>
       <c r="E164" s="53"/>
       <c r="F164" s="53"/>
@@ -11172,16 +11393,16 @@
     </row>
     <row r="165">
       <c r="A165" s="56" t="s">
-        <v>718</v>
+        <v>754</v>
       </c>
       <c r="B165" s="52" t="s">
-        <v>719</v>
+        <v>755</v>
       </c>
       <c r="C165" s="52" t="s">
-        <v>720</v>
+        <v>756</v>
       </c>
       <c r="D165" s="52" t="s">
-        <v>721</v>
+        <v>757</v>
       </c>
       <c r="E165" s="53"/>
       <c r="F165" s="53"/>
@@ -11202,16 +11423,16 @@
     </row>
     <row r="166">
       <c r="A166" s="56" t="s">
-        <v>722</v>
+        <v>758</v>
       </c>
       <c r="B166" s="52" t="s">
-        <v>723</v>
+        <v>759</v>
       </c>
       <c r="C166" s="52" t="s">
-        <v>724</v>
+        <v>760</v>
       </c>
       <c r="D166" s="52" t="s">
-        <v>725</v>
+        <v>761</v>
       </c>
       <c r="E166" s="53"/>
       <c r="F166" s="53"/>
@@ -11230,78 +11451,78 @@
       <c r="S166" s="54"/>
       <c r="T166" s="54"/>
     </row>
-    <row r="167">
-      <c r="A167" s="56" t="s">
-        <v>726</v>
-      </c>
-      <c r="B167" s="52" t="s">
-        <v>727</v>
-      </c>
-      <c r="C167" s="52" t="s">
-        <v>391</v>
-      </c>
-      <c r="D167" s="52" t="s">
-        <v>728</v>
-      </c>
-      <c r="E167" s="53"/>
-      <c r="F167" s="53"/>
-      <c r="G167" s="53"/>
-      <c r="H167" s="53"/>
-      <c r="I167" s="53"/>
-      <c r="J167" s="53"/>
-      <c r="K167" s="53"/>
-      <c r="L167" s="53"/>
-      <c r="M167" s="54"/>
-      <c r="N167" s="54"/>
-      <c r="O167" s="54"/>
-      <c r="P167" s="54"/>
-      <c r="Q167" s="54"/>
-      <c r="R167" s="54"/>
-      <c r="S167" s="54"/>
-      <c r="T167" s="54"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="56" t="s">
-        <v>729</v>
-      </c>
-      <c r="B168" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="C168" s="52" t="s">
-        <v>385</v>
-      </c>
-      <c r="D168" s="52" t="s">
-        <v>730</v>
-      </c>
-      <c r="E168" s="53"/>
-      <c r="F168" s="53"/>
-      <c r="G168" s="53"/>
-      <c r="H168" s="53"/>
-      <c r="I168" s="53"/>
-      <c r="J168" s="53"/>
-      <c r="K168" s="53"/>
-      <c r="L168" s="53"/>
-      <c r="M168" s="54"/>
-      <c r="N168" s="54"/>
-      <c r="O168" s="54"/>
-      <c r="P168" s="54"/>
-      <c r="Q168" s="54"/>
-      <c r="R168" s="54"/>
-      <c r="S168" s="54"/>
-      <c r="T168" s="54"/>
+    <row customHeight="true" ht="16" r="167">
+      <c r="A167" s="76" t="s">
+        <v>762</v>
+      </c>
+      <c r="B167" s="77" t="s">
+        <v>763</v>
+      </c>
+      <c r="C167" s="77" t="s">
+        <v>764</v>
+      </c>
+      <c r="D167" s="78" t="s">
+        <v>765</v>
+      </c>
+      <c r="E167" s="79"/>
+      <c r="F167" s="79"/>
+      <c r="G167" s="79"/>
+      <c r="H167" s="79"/>
+      <c r="I167" s="79"/>
+      <c r="J167" s="79"/>
+      <c r="K167" s="79"/>
+      <c r="L167" s="79"/>
+      <c r="M167" s="80"/>
+      <c r="N167" s="80"/>
+      <c r="O167" s="80"/>
+      <c r="P167" s="80"/>
+      <c r="Q167" s="80"/>
+      <c r="R167" s="80"/>
+      <c r="S167" s="80"/>
+      <c r="T167" s="80"/>
+    </row>
+    <row customHeight="true" ht="16" r="168">
+      <c r="A168" s="76" t="s">
+        <v>766</v>
+      </c>
+      <c r="B168" s="78" t="s">
+        <v>767</v>
+      </c>
+      <c r="C168" s="78" t="s">
+        <v>768</v>
+      </c>
+      <c r="D168" s="78" t="s">
+        <v>769</v>
+      </c>
+      <c r="E168" s="81"/>
+      <c r="F168" s="81"/>
+      <c r="G168" s="81"/>
+      <c r="H168" s="81"/>
+      <c r="I168" s="81"/>
+      <c r="J168" s="81"/>
+      <c r="K168" s="81"/>
+      <c r="L168" s="81"/>
+      <c r="M168" s="82"/>
+      <c r="N168" s="82"/>
+      <c r="O168" s="82"/>
+      <c r="P168" s="82"/>
+      <c r="Q168" s="82"/>
+      <c r="R168" s="82"/>
+      <c r="S168" s="82"/>
+      <c r="T168" s="82"/>
     </row>
     <row r="169">
-      <c r="A169" s="56" t="s">
-        <v>731</v>
+      <c r="A169" s="83" t="s">
+        <v>770</v>
       </c>
       <c r="B169" s="52" t="s">
-        <v>732</v>
+        <v>771</v>
       </c>
       <c r="C169" s="52" t="s">
-        <v>733</v>
+        <v>407</v>
       </c>
       <c r="D169" s="52" t="s">
-        <v>734</v>
+        <v>772</v>
       </c>
       <c r="E169" s="53"/>
       <c r="F169" s="53"/>
@@ -11321,17 +11542,17 @@
       <c r="T169" s="54"/>
     </row>
     <row r="170">
-      <c r="A170" s="56" t="s">
-        <v>735</v>
-      </c>
-      <c r="B170" s="52" t="s">
-        <v>736</v>
+      <c r="A170" s="83" t="s">
+        <v>773</v>
+      </c>
+      <c r="B170" s="55" t="s">
+        <v>398</v>
       </c>
       <c r="C170" s="52" t="s">
-        <v>737</v>
+        <v>399</v>
       </c>
       <c r="D170" s="52" t="s">
-        <v>738</v>
+        <v>400</v>
       </c>
       <c r="E170" s="53"/>
       <c r="F170" s="53"/>
@@ -11351,17 +11572,17 @@
       <c r="T170" s="54"/>
     </row>
     <row r="171">
-      <c r="A171" s="56" t="s">
-        <v>739</v>
+      <c r="A171" s="83" t="s">
+        <v>774</v>
       </c>
       <c r="B171" s="52" t="s">
-        <v>740</v>
+        <v>775</v>
       </c>
       <c r="C171" s="52" t="s">
-        <v>741</v>
+        <v>776</v>
       </c>
       <c r="D171" s="52" t="s">
-        <v>742</v>
+        <v>777</v>
       </c>
       <c r="E171" s="53"/>
       <c r="F171" s="53"/>
@@ -11382,16 +11603,16 @@
     </row>
     <row r="172">
       <c r="A172" s="56" t="s">
-        <v>743</v>
+        <v>778</v>
       </c>
       <c r="B172" s="52" t="s">
-        <v>744</v>
+        <v>779</v>
       </c>
       <c r="C172" s="52" t="s">
-        <v>745</v>
+        <v>780</v>
       </c>
       <c r="D172" s="52" t="s">
-        <v>746</v>
+        <v>781</v>
       </c>
       <c r="E172" s="53"/>
       <c r="F172" s="53"/>
@@ -11412,16 +11633,16 @@
     </row>
     <row r="173">
       <c r="A173" s="56" t="s">
-        <v>747</v>
+        <v>782</v>
       </c>
       <c r="B173" s="52" t="s">
-        <v>748</v>
+        <v>783</v>
       </c>
       <c r="C173" s="52" t="s">
-        <v>749</v>
+        <v>784</v>
       </c>
       <c r="D173" s="52" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="E173" s="53"/>
       <c r="F173" s="53"/>
@@ -11442,16 +11663,16 @@
     </row>
     <row r="174">
       <c r="A174" s="56" t="s">
-        <v>751</v>
+        <v>786</v>
       </c>
       <c r="B174" s="52" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="C174" s="52" t="s">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="D174" s="52" t="s">
-        <v>754</v>
+        <v>789</v>
       </c>
       <c r="E174" s="53"/>
       <c r="F174" s="53"/>
@@ -11472,16 +11693,16 @@
     </row>
     <row r="175">
       <c r="A175" s="56" t="s">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="B175" s="52" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="C175" s="52" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="D175" s="52" t="s">
-        <v>758</v>
+        <v>793</v>
       </c>
       <c r="E175" s="53"/>
       <c r="F175" s="53"/>
@@ -11502,16 +11723,16 @@
     </row>
     <row r="176">
       <c r="A176" s="56" t="s">
-        <v>759</v>
+        <v>794</v>
       </c>
       <c r="B176" s="52" t="s">
-        <v>760</v>
+        <v>795</v>
       </c>
       <c r="C176" s="52" t="s">
-        <v>761</v>
+        <v>796</v>
       </c>
       <c r="D176" s="52" t="s">
-        <v>762</v>
+        <v>797</v>
       </c>
       <c r="E176" s="53"/>
       <c r="F176" s="53"/>
@@ -11532,16 +11753,16 @@
     </row>
     <row r="177">
       <c r="A177" s="56" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="B177" s="52" t="s">
-        <v>764</v>
+        <v>799</v>
       </c>
       <c r="C177" s="52" t="s">
-        <v>765</v>
+        <v>800</v>
       </c>
       <c r="D177" s="52" t="s">
-        <v>766</v>
+        <v>801</v>
       </c>
       <c r="E177" s="53"/>
       <c r="F177" s="53"/>
@@ -11562,16 +11783,16 @@
     </row>
     <row r="178">
       <c r="A178" s="56" t="s">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="B178" s="52" t="s">
-        <v>768</v>
+        <v>803</v>
       </c>
       <c r="C178" s="52" t="s">
-        <v>769</v>
+        <v>804</v>
       </c>
       <c r="D178" s="52" t="s">
-        <v>770</v>
+        <v>805</v>
       </c>
       <c r="E178" s="53"/>
       <c r="F178" s="53"/>
@@ -11592,16 +11813,16 @@
     </row>
     <row r="179">
       <c r="A179" s="56" t="s">
-        <v>771</v>
+        <v>806</v>
       </c>
       <c r="B179" s="52" t="s">
-        <v>772</v>
+        <v>807</v>
       </c>
       <c r="C179" s="52" t="s">
-        <v>773</v>
+        <v>808</v>
       </c>
       <c r="D179" s="52" t="s">
-        <v>774</v>
+        <v>809</v>
       </c>
       <c r="E179" s="53"/>
       <c r="F179" s="53"/>
@@ -11622,16 +11843,16 @@
     </row>
     <row r="180">
       <c r="A180" s="56" t="s">
-        <v>775</v>
+        <v>810</v>
       </c>
       <c r="B180" s="52" t="s">
-        <v>776</v>
+        <v>811</v>
       </c>
       <c r="C180" s="52" t="s">
-        <v>403</v>
+        <v>812</v>
       </c>
       <c r="D180" s="52" t="s">
-        <v>777</v>
+        <v>813</v>
       </c>
       <c r="E180" s="53"/>
       <c r="F180" s="53"/>
@@ -11652,16 +11873,16 @@
     </row>
     <row r="181">
       <c r="A181" s="56" t="s">
-        <v>778</v>
+        <v>814</v>
       </c>
       <c r="B181" s="52" t="s">
-        <v>779</v>
+        <v>815</v>
       </c>
       <c r="C181" s="52" t="s">
-        <v>780</v>
+        <v>816</v>
       </c>
       <c r="D181" s="52" t="s">
-        <v>781</v>
+        <v>817</v>
       </c>
       <c r="E181" s="53"/>
       <c r="F181" s="53"/>
@@ -11682,16 +11903,16 @@
     </row>
     <row r="182">
       <c r="A182" s="56" t="s">
-        <v>782</v>
+        <v>818</v>
       </c>
       <c r="B182" s="52" t="s">
-        <v>783</v>
+        <v>819</v>
       </c>
       <c r="C182" s="52" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D182" s="52" t="s">
-        <v>784</v>
+        <v>820</v>
       </c>
       <c r="E182" s="53"/>
       <c r="F182" s="53"/>
@@ -11712,16 +11933,16 @@
     </row>
     <row r="183">
       <c r="A183" s="56" t="s">
-        <v>785</v>
+        <v>821</v>
       </c>
       <c r="B183" s="52" t="s">
-        <v>786</v>
+        <v>822</v>
       </c>
       <c r="C183" s="52" t="s">
-        <v>787</v>
+        <v>823</v>
       </c>
       <c r="D183" s="52" t="s">
-        <v>788</v>
+        <v>824</v>
       </c>
       <c r="E183" s="53"/>
       <c r="F183" s="53"/>
@@ -11742,16 +11963,16 @@
     </row>
     <row r="184">
       <c r="A184" s="56" t="s">
-        <v>789</v>
+        <v>825</v>
       </c>
       <c r="B184" s="52" t="s">
-        <v>790</v>
+        <v>826</v>
       </c>
       <c r="C184" s="52" t="s">
-        <v>791</v>
+        <v>427</v>
       </c>
       <c r="D184" s="52" t="s">
-        <v>792</v>
+        <v>827</v>
       </c>
       <c r="E184" s="53"/>
       <c r="F184" s="53"/>
@@ -11772,16 +11993,16 @@
     </row>
     <row r="185">
       <c r="A185" s="56" t="s">
-        <v>793</v>
+        <v>828</v>
       </c>
       <c r="B185" s="52" t="s">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="C185" s="52" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
       <c r="D185" s="52" t="s">
-        <v>796</v>
+        <v>831</v>
       </c>
       <c r="E185" s="53"/>
       <c r="F185" s="53"/>
@@ -11802,16 +12023,16 @@
     </row>
     <row r="186">
       <c r="A186" s="56" t="s">
-        <v>797</v>
+        <v>832</v>
       </c>
       <c r="B186" s="52" t="s">
-        <v>798</v>
+        <v>833</v>
       </c>
       <c r="C186" s="52" t="s">
-        <v>799</v>
+        <v>834</v>
       </c>
       <c r="D186" s="52" t="s">
-        <v>800</v>
+        <v>835</v>
       </c>
       <c r="E186" s="53"/>
       <c r="F186" s="53"/>
@@ -11832,16 +12053,16 @@
     </row>
     <row r="187">
       <c r="A187" s="56" t="s">
-        <v>801</v>
+        <v>836</v>
       </c>
       <c r="B187" s="52" t="s">
-        <v>802</v>
+        <v>837</v>
       </c>
       <c r="C187" s="52" t="s">
-        <v>803</v>
+        <v>838</v>
       </c>
       <c r="D187" s="52" t="s">
-        <v>804</v>
+        <v>839</v>
       </c>
       <c r="E187" s="53"/>
       <c r="F187" s="53"/>
@@ -11862,16 +12083,16 @@
     </row>
     <row r="188">
       <c r="A188" s="56" t="s">
-        <v>805</v>
+        <v>840</v>
       </c>
       <c r="B188" s="52" t="s">
-        <v>561</v>
+        <v>841</v>
       </c>
       <c r="C188" s="52" t="s">
-        <v>457</v>
+        <v>842</v>
       </c>
       <c r="D188" s="52" t="s">
-        <v>562</v>
+        <v>843</v>
       </c>
       <c r="E188" s="53"/>
       <c r="F188" s="53"/>
@@ -11892,16 +12113,16 @@
     </row>
     <row r="189">
       <c r="A189" s="56" t="s">
-        <v>806</v>
-      </c>
-      <c r="B189" s="55" t="s">
-        <v>807</v>
-      </c>
-      <c r="C189" s="74" t="s">
-        <v>808</v>
-      </c>
-      <c r="D189" s="55" t="s">
-        <v>809</v>
+        <v>844</v>
+      </c>
+      <c r="B189" s="52" t="s">
+        <v>845</v>
+      </c>
+      <c r="C189" s="52" t="s">
+        <v>846</v>
+      </c>
+      <c r="D189" s="52" t="s">
+        <v>847</v>
       </c>
       <c r="E189" s="53"/>
       <c r="F189" s="53"/>
@@ -11922,16 +12143,16 @@
     </row>
     <row r="190">
       <c r="A190" s="56" t="s">
-        <v>810</v>
+        <v>848</v>
       </c>
       <c r="B190" s="52" t="s">
-        <v>811</v>
+        <v>600</v>
       </c>
       <c r="C190" s="52" t="s">
-        <v>812</v>
+        <v>489</v>
       </c>
       <c r="D190" s="52" t="s">
-        <v>813</v>
+        <v>601</v>
       </c>
       <c r="E190" s="53"/>
       <c r="F190" s="53"/>
@@ -11952,16 +12173,16 @@
     </row>
     <row r="191">
       <c r="A191" s="56" t="s">
-        <v>814</v>
-      </c>
-      <c r="B191" s="52" t="s">
-        <v>815</v>
-      </c>
-      <c r="C191" s="52" t="s">
-        <v>816</v>
-      </c>
-      <c r="D191" s="52" t="s">
-        <v>817</v>
+        <v>849</v>
+      </c>
+      <c r="B191" s="55" t="s">
+        <v>850</v>
+      </c>
+      <c r="C191" s="84" t="s">
+        <v>851</v>
+      </c>
+      <c r="D191" s="55" t="s">
+        <v>852</v>
       </c>
       <c r="E191" s="53"/>
       <c r="F191" s="53"/>
@@ -11982,16 +12203,16 @@
     </row>
     <row r="192">
       <c r="A192" s="56" t="s">
-        <v>818</v>
+        <v>853</v>
       </c>
       <c r="B192" s="52" t="s">
-        <v>819</v>
+        <v>854</v>
       </c>
       <c r="C192" s="52" t="s">
-        <v>820</v>
+        <v>855</v>
       </c>
       <c r="D192" s="52" t="s">
-        <v>821</v>
+        <v>856</v>
       </c>
       <c r="E192" s="53"/>
       <c r="F192" s="53"/>
@@ -12012,16 +12233,16 @@
     </row>
     <row r="193">
       <c r="A193" s="56" t="s">
-        <v>822</v>
+        <v>857</v>
       </c>
       <c r="B193" s="52" t="s">
-        <v>823</v>
+        <v>858</v>
       </c>
       <c r="C193" s="52" t="s">
-        <v>824</v>
+        <v>859</v>
       </c>
       <c r="D193" s="52" t="s">
-        <v>825</v>
+        <v>860</v>
       </c>
       <c r="E193" s="53"/>
       <c r="F193" s="53"/>
@@ -12042,16 +12263,16 @@
     </row>
     <row r="194">
       <c r="A194" s="56" t="s">
-        <v>826</v>
+        <v>861</v>
       </c>
       <c r="B194" s="52" t="s">
-        <v>827</v>
+        <v>862</v>
       </c>
       <c r="C194" s="52" t="s">
-        <v>828</v>
+        <v>863</v>
       </c>
       <c r="D194" s="52" t="s">
-        <v>829</v>
+        <v>864</v>
       </c>
       <c r="E194" s="53"/>
       <c r="F194" s="53"/>
@@ -12072,16 +12293,16 @@
     </row>
     <row r="195">
       <c r="A195" s="56" t="s">
-        <v>830</v>
+        <v>865</v>
       </c>
       <c r="B195" s="52" t="s">
-        <v>831</v>
+        <v>866</v>
       </c>
       <c r="C195" s="52" t="s">
-        <v>832</v>
+        <v>867</v>
       </c>
       <c r="D195" s="52" t="s">
-        <v>833</v>
+        <v>868</v>
       </c>
       <c r="E195" s="53"/>
       <c r="F195" s="53"/>
@@ -12102,16 +12323,16 @@
     </row>
     <row r="196">
       <c r="A196" s="56" t="s">
-        <v>834</v>
+        <v>869</v>
       </c>
       <c r="B196" s="52" t="s">
-        <v>835</v>
+        <v>870</v>
       </c>
       <c r="C196" s="52" t="s">
-        <v>836</v>
+        <v>871</v>
       </c>
       <c r="D196" s="52" t="s">
-        <v>837</v>
+        <v>872</v>
       </c>
       <c r="E196" s="53"/>
       <c r="F196" s="53"/>
@@ -12132,16 +12353,16 @@
     </row>
     <row r="197">
       <c r="A197" s="56" t="s">
-        <v>838</v>
+        <v>873</v>
       </c>
       <c r="B197" s="52" t="s">
-        <v>839</v>
+        <v>874</v>
       </c>
       <c r="C197" s="52" t="s">
-        <v>840</v>
+        <v>875</v>
       </c>
       <c r="D197" s="52" t="s">
-        <v>841</v>
+        <v>876</v>
       </c>
       <c r="E197" s="53"/>
       <c r="F197" s="53"/>
@@ -12162,16 +12383,16 @@
     </row>
     <row r="198">
       <c r="A198" s="56" t="s">
-        <v>842</v>
+        <v>877</v>
       </c>
       <c r="B198" s="52" t="s">
-        <v>843</v>
+        <v>878</v>
       </c>
       <c r="C198" s="52" t="s">
-        <v>844</v>
+        <v>879</v>
       </c>
       <c r="D198" s="52" t="s">
-        <v>845</v>
+        <v>880</v>
       </c>
       <c r="E198" s="53"/>
       <c r="F198" s="53"/>
@@ -12192,16 +12413,16 @@
     </row>
     <row r="199">
       <c r="A199" s="56" t="s">
-        <v>846</v>
+        <v>881</v>
       </c>
       <c r="B199" s="52" t="s">
-        <v>847</v>
+        <v>882</v>
       </c>
       <c r="C199" s="52" t="s">
-        <v>848</v>
+        <v>883</v>
       </c>
       <c r="D199" s="52" t="s">
-        <v>849</v>
+        <v>884</v>
       </c>
       <c r="E199" s="53"/>
       <c r="F199" s="53"/>
@@ -12222,16 +12443,16 @@
     </row>
     <row r="200">
       <c r="A200" s="56" t="s">
-        <v>850</v>
+        <v>885</v>
       </c>
       <c r="B200" s="52" t="s">
-        <v>851</v>
+        <v>886</v>
       </c>
       <c r="C200" s="52" t="s">
-        <v>852</v>
+        <v>887</v>
       </c>
       <c r="D200" s="52" t="s">
-        <v>853</v>
+        <v>888</v>
       </c>
       <c r="E200" s="53"/>
       <c r="F200" s="53"/>
@@ -12252,16 +12473,16 @@
     </row>
     <row r="201">
       <c r="A201" s="56" t="s">
-        <v>854</v>
+        <v>889</v>
       </c>
       <c r="B201" s="52" t="s">
-        <v>855</v>
+        <v>890</v>
       </c>
       <c r="C201" s="52" t="s">
-        <v>856</v>
+        <v>891</v>
       </c>
       <c r="D201" s="52" t="s">
-        <v>857</v>
+        <v>892</v>
       </c>
       <c r="E201" s="53"/>
       <c r="F201" s="53"/>
@@ -12282,16 +12503,16 @@
     </row>
     <row r="202">
       <c r="A202" s="56" t="s">
-        <v>858</v>
+        <v>893</v>
       </c>
       <c r="B202" s="52" t="s">
-        <v>859</v>
+        <v>894</v>
       </c>
       <c r="C202" s="52" t="s">
-        <v>860</v>
+        <v>895</v>
       </c>
       <c r="D202" s="52" t="s">
-        <v>861</v>
+        <v>896</v>
       </c>
       <c r="E202" s="53"/>
       <c r="F202" s="53"/>
@@ -12312,16 +12533,16 @@
     </row>
     <row r="203">
       <c r="A203" s="56" t="s">
-        <v>862</v>
+        <v>897</v>
       </c>
       <c r="B203" s="52" t="s">
-        <v>863</v>
+        <v>898</v>
       </c>
       <c r="C203" s="52" t="s">
-        <v>864</v>
+        <v>899</v>
       </c>
       <c r="D203" s="52" t="s">
-        <v>865</v>
+        <v>900</v>
       </c>
       <c r="E203" s="53"/>
       <c r="F203" s="53"/>
@@ -12342,16 +12563,16 @@
     </row>
     <row r="204">
       <c r="A204" s="56" t="s">
-        <v>866</v>
+        <v>901</v>
       </c>
       <c r="B204" s="52" t="s">
-        <v>867</v>
+        <v>902</v>
       </c>
       <c r="C204" s="52" t="s">
-        <v>479</v>
+        <v>903</v>
       </c>
       <c r="D204" s="52" t="s">
-        <v>868</v>
+        <v>904</v>
       </c>
       <c r="E204" s="53"/>
       <c r="F204" s="53"/>
@@ -12372,16 +12593,16 @@
     </row>
     <row r="205">
       <c r="A205" s="56" t="s">
-        <v>869</v>
+        <v>905</v>
       </c>
       <c r="B205" s="52" t="s">
-        <v>870</v>
+        <v>906</v>
       </c>
       <c r="C205" s="52" t="s">
-        <v>871</v>
+        <v>907</v>
       </c>
       <c r="D205" s="52" t="s">
-        <v>872</v>
+        <v>908</v>
       </c>
       <c r="E205" s="53"/>
       <c r="F205" s="53"/>
@@ -12402,16 +12623,16 @@
     </row>
     <row r="206">
       <c r="A206" s="56" t="s">
-        <v>873</v>
+        <v>909</v>
       </c>
       <c r="B206" s="52" t="s">
-        <v>874</v>
+        <v>910</v>
       </c>
       <c r="C206" s="52" t="s">
-        <v>875</v>
+        <v>517</v>
       </c>
       <c r="D206" s="52" t="s">
-        <v>876</v>
+        <v>518</v>
       </c>
       <c r="E206" s="53"/>
       <c r="F206" s="53"/>
@@ -12432,16 +12653,16 @@
     </row>
     <row r="207">
       <c r="A207" s="56" t="s">
-        <v>877</v>
+        <v>911</v>
       </c>
       <c r="B207" s="52" t="s">
-        <v>878</v>
+        <v>912</v>
       </c>
       <c r="C207" s="52" t="s">
-        <v>879</v>
+        <v>913</v>
       </c>
       <c r="D207" s="52" t="s">
-        <v>880</v>
+        <v>914</v>
       </c>
       <c r="E207" s="53"/>
       <c r="F207" s="53"/>
@@ -12462,16 +12683,16 @@
     </row>
     <row r="208">
       <c r="A208" s="56" t="s">
-        <v>881</v>
+        <v>915</v>
       </c>
       <c r="B208" s="52" t="s">
-        <v>882</v>
+        <v>916</v>
       </c>
       <c r="C208" s="52" t="s">
-        <v>883</v>
+        <v>917</v>
       </c>
       <c r="D208" s="52" t="s">
-        <v>884</v>
+        <v>918</v>
       </c>
       <c r="E208" s="53"/>
       <c r="F208" s="53"/>
@@ -12492,16 +12713,16 @@
     </row>
     <row r="209">
       <c r="A209" s="56" t="s">
-        <v>885</v>
+        <v>919</v>
       </c>
       <c r="B209" s="52" t="s">
-        <v>886</v>
+        <v>920</v>
       </c>
       <c r="C209" s="52" t="s">
-        <v>482</v>
+        <v>921</v>
       </c>
       <c r="D209" s="52" t="s">
-        <v>887</v>
+        <v>922</v>
       </c>
       <c r="E209" s="53"/>
       <c r="F209" s="53"/>
@@ -12522,16 +12743,16 @@
     </row>
     <row r="210">
       <c r="A210" s="56" t="s">
-        <v>888</v>
+        <v>923</v>
       </c>
       <c r="B210" s="52" t="s">
-        <v>889</v>
+        <v>924</v>
       </c>
       <c r="C210" s="52" t="s">
-        <v>890</v>
+        <v>925</v>
       </c>
       <c r="D210" s="52" t="s">
-        <v>891</v>
+        <v>926</v>
       </c>
       <c r="E210" s="53"/>
       <c r="F210" s="53"/>
@@ -12552,16 +12773,16 @@
     </row>
     <row r="211">
       <c r="A211" s="56" t="s">
-        <v>892</v>
+        <v>927</v>
       </c>
       <c r="B211" s="52" t="s">
-        <v>893</v>
+        <v>928</v>
       </c>
       <c r="C211" s="52" t="s">
-        <v>894</v>
+        <v>521</v>
       </c>
       <c r="D211" s="52" t="s">
-        <v>894</v>
+        <v>929</v>
       </c>
       <c r="E211" s="53"/>
       <c r="F211" s="53"/>
@@ -12582,16 +12803,16 @@
     </row>
     <row r="212">
       <c r="A212" s="56" t="s">
-        <v>895</v>
+        <v>930</v>
       </c>
       <c r="B212" s="52" t="s">
-        <v>896</v>
+        <v>931</v>
       </c>
       <c r="C212" s="52" t="s">
-        <v>897</v>
+        <v>932</v>
       </c>
       <c r="D212" s="52" t="s">
-        <v>898</v>
+        <v>933</v>
       </c>
       <c r="E212" s="53"/>
       <c r="F212" s="53"/>
@@ -12612,16 +12833,16 @@
     </row>
     <row r="213">
       <c r="A213" s="56" t="s">
-        <v>899</v>
-      </c>
-      <c r="B213" s="55" t="s">
-        <v>417</v>
+        <v>934</v>
+      </c>
+      <c r="B213" s="52" t="s">
+        <v>935</v>
       </c>
       <c r="C213" s="52" t="s">
-        <v>418</v>
+        <v>936</v>
       </c>
       <c r="D213" s="52" t="s">
-        <v>900</v>
+        <v>936</v>
       </c>
       <c r="E213" s="53"/>
       <c r="F213" s="53"/>
@@ -12642,16 +12863,16 @@
     </row>
     <row r="214">
       <c r="A214" s="56" t="s">
-        <v>901</v>
+        <v>937</v>
       </c>
       <c r="B214" s="52" t="s">
-        <v>902</v>
+        <v>938</v>
       </c>
       <c r="C214" s="52" t="s">
-        <v>903</v>
+        <v>939</v>
       </c>
       <c r="D214" s="52" t="s">
-        <v>904</v>
+        <v>940</v>
       </c>
       <c r="E214" s="53"/>
       <c r="F214" s="53"/>
@@ -12672,16 +12893,16 @@
     </row>
     <row r="215">
       <c r="A215" s="56" t="s">
-        <v>905</v>
+        <v>941</v>
       </c>
       <c r="B215" s="55" t="s">
-        <v>906</v>
+        <v>441</v>
       </c>
       <c r="C215" s="52" t="s">
-        <v>907</v>
+        <v>442</v>
       </c>
       <c r="D215" s="52" t="s">
-        <v>908</v>
+        <v>443</v>
       </c>
       <c r="E215" s="53"/>
       <c r="F215" s="53"/>
@@ -12702,16 +12923,16 @@
     </row>
     <row r="216">
       <c r="A216" s="56" t="s">
-        <v>909</v>
-      </c>
-      <c r="B216" s="55" t="s">
-        <v>910</v>
-      </c>
-      <c r="C216" s="55" t="s">
-        <v>911</v>
+        <v>942</v>
+      </c>
+      <c r="B216" s="52" t="s">
+        <v>943</v>
+      </c>
+      <c r="C216" s="52" t="s">
+        <v>944</v>
       </c>
       <c r="D216" s="52" t="s">
-        <v>912</v>
+        <v>945</v>
       </c>
       <c r="E216" s="53"/>
       <c r="F216" s="53"/>
@@ -12732,16 +12953,16 @@
     </row>
     <row r="217">
       <c r="A217" s="56" t="s">
-        <v>913</v>
-      </c>
-      <c r="B217" s="52" t="s">
-        <v>914</v>
+        <v>946</v>
+      </c>
+      <c r="B217" s="55" t="s">
+        <v>947</v>
       </c>
       <c r="C217" s="52" t="s">
-        <v>915</v>
+        <v>948</v>
       </c>
       <c r="D217" s="52" t="s">
-        <v>916</v>
+        <v>949</v>
       </c>
       <c r="E217" s="53"/>
       <c r="F217" s="53"/>
@@ -12762,16 +12983,16 @@
     </row>
     <row r="218">
       <c r="A218" s="56" t="s">
-        <v>917</v>
+        <v>950</v>
       </c>
       <c r="B218" s="55" t="s">
-        <v>918</v>
-      </c>
-      <c r="C218" s="52" t="s">
-        <v>919</v>
+        <v>951</v>
+      </c>
+      <c r="C218" s="55" t="s">
+        <v>952</v>
       </c>
       <c r="D218" s="52" t="s">
-        <v>920</v>
+        <v>953</v>
       </c>
       <c r="E218" s="53"/>
       <c r="F218" s="53"/>
@@ -12792,16 +13013,16 @@
     </row>
     <row r="219">
       <c r="A219" s="56" t="s">
-        <v>921</v>
-      </c>
-      <c r="B219" s="55" t="s">
-        <v>922</v>
+        <v>954</v>
+      </c>
+      <c r="B219" s="52" t="s">
+        <v>955</v>
       </c>
       <c r="C219" s="52" t="s">
-        <v>923</v>
+        <v>956</v>
       </c>
       <c r="D219" s="52" t="s">
-        <v>924</v>
+        <v>957</v>
       </c>
       <c r="E219" s="53"/>
       <c r="F219" s="53"/>
@@ -12822,16 +13043,16 @@
     </row>
     <row r="220">
       <c r="A220" s="56" t="s">
-        <v>925</v>
-      </c>
-      <c r="B220" s="52" t="s">
-        <v>438</v>
+        <v>958</v>
+      </c>
+      <c r="B220" s="55" t="s">
+        <v>959</v>
       </c>
       <c r="C220" s="52" t="s">
-        <v>926</v>
+        <v>960</v>
       </c>
       <c r="D220" s="52" t="s">
-        <v>439</v>
+        <v>961</v>
       </c>
       <c r="E220" s="53"/>
       <c r="F220" s="53"/>
@@ -12852,16 +13073,16 @@
     </row>
     <row r="221">
       <c r="A221" s="56" t="s">
-        <v>927</v>
+        <v>962</v>
       </c>
       <c r="B221" s="55" t="s">
-        <v>928</v>
+        <v>963</v>
       </c>
       <c r="C221" s="52" t="s">
-        <v>929</v>
+        <v>964</v>
       </c>
       <c r="D221" s="52" t="s">
-        <v>930</v>
+        <v>965</v>
       </c>
       <c r="E221" s="53"/>
       <c r="F221" s="53"/>
@@ -12882,16 +13103,16 @@
     </row>
     <row r="222">
       <c r="A222" s="56" t="s">
-        <v>931</v>
+        <v>966</v>
       </c>
       <c r="B222" s="52" t="s">
-        <v>932</v>
+        <v>466</v>
       </c>
       <c r="C222" s="52" t="s">
-        <v>933</v>
+        <v>967</v>
       </c>
       <c r="D222" s="52" t="s">
-        <v>934</v>
+        <v>467</v>
       </c>
       <c r="E222" s="53"/>
       <c r="F222" s="53"/>
@@ -12912,16 +13133,16 @@
     </row>
     <row r="223">
       <c r="A223" s="56" t="s">
-        <v>935</v>
+        <v>968</v>
       </c>
       <c r="B223" s="55" t="s">
-        <v>936</v>
+        <v>969</v>
       </c>
       <c r="C223" s="52" t="s">
-        <v>937</v>
+        <v>970</v>
       </c>
       <c r="D223" s="52" t="s">
-        <v>938</v>
+        <v>971</v>
       </c>
       <c r="E223" s="53"/>
       <c r="F223" s="53"/>
@@ -12942,16 +13163,16 @@
     </row>
     <row r="224">
       <c r="A224" s="56" t="s">
-        <v>939</v>
-      </c>
-      <c r="B224" s="55" t="s">
-        <v>940</v>
+        <v>972</v>
+      </c>
+      <c r="B224" s="52" t="s">
+        <v>973</v>
       </c>
       <c r="C224" s="52" t="s">
-        <v>941</v>
+        <v>974</v>
       </c>
       <c r="D224" s="52" t="s">
-        <v>942</v>
+        <v>975</v>
       </c>
       <c r="E224" s="53"/>
       <c r="F224" s="53"/>
@@ -12972,16 +13193,16 @@
     </row>
     <row r="225">
       <c r="A225" s="56" t="s">
-        <v>943</v>
-      </c>
-      <c r="B225" s="52" t="s">
-        <v>944</v>
+        <v>976</v>
+      </c>
+      <c r="B225" s="55" t="s">
+        <v>977</v>
       </c>
       <c r="C225" s="52" t="s">
-        <v>945</v>
+        <v>978</v>
       </c>
       <c r="D225" s="52" t="s">
-        <v>946</v>
+        <v>979</v>
       </c>
       <c r="E225" s="53"/>
       <c r="F225" s="53"/>
@@ -13002,16 +13223,16 @@
     </row>
     <row r="226">
       <c r="A226" s="56" t="s">
-        <v>947</v>
-      </c>
-      <c r="B226" s="52" t="s">
-        <v>948</v>
+        <v>980</v>
+      </c>
+      <c r="B226" s="55" t="s">
+        <v>981</v>
       </c>
       <c r="C226" s="52" t="s">
-        <v>949</v>
+        <v>982</v>
       </c>
       <c r="D226" s="52" t="s">
-        <v>950</v>
+        <v>983</v>
       </c>
       <c r="E226" s="53"/>
       <c r="F226" s="53"/>
@@ -13032,16 +13253,16 @@
     </row>
     <row r="227">
       <c r="A227" s="56" t="s">
-        <v>951</v>
+        <v>984</v>
       </c>
       <c r="B227" s="52" t="s">
-        <v>952</v>
+        <v>985</v>
       </c>
       <c r="C227" s="52" t="s">
-        <v>953</v>
+        <v>986</v>
       </c>
       <c r="D227" s="52" t="s">
-        <v>954</v>
+        <v>987</v>
       </c>
       <c r="E227" s="53"/>
       <c r="F227" s="53"/>
@@ -13062,16 +13283,16 @@
     </row>
     <row r="228">
       <c r="A228" s="56" t="s">
-        <v>955</v>
+        <v>988</v>
       </c>
       <c r="B228" s="52" t="s">
-        <v>956</v>
+        <v>989</v>
       </c>
       <c r="C228" s="52" t="s">
-        <v>957</v>
+        <v>990</v>
       </c>
       <c r="D228" s="52" t="s">
-        <v>958</v>
+        <v>991</v>
       </c>
       <c r="E228" s="53"/>
       <c r="F228" s="53"/>
@@ -13092,16 +13313,16 @@
     </row>
     <row r="229">
       <c r="A229" s="56" t="s">
-        <v>959</v>
+        <v>992</v>
       </c>
       <c r="B229" s="52" t="s">
-        <v>960</v>
+        <v>993</v>
       </c>
       <c r="C229" s="52" t="s">
-        <v>961</v>
+        <v>994</v>
       </c>
       <c r="D229" s="52" t="s">
-        <v>962</v>
+        <v>995</v>
       </c>
       <c r="E229" s="53"/>
       <c r="F229" s="53"/>
@@ -13122,16 +13343,16 @@
     </row>
     <row r="230">
       <c r="A230" s="56" t="s">
-        <v>963</v>
+        <v>996</v>
       </c>
       <c r="B230" s="52" t="s">
-        <v>964</v>
+        <v>997</v>
       </c>
       <c r="C230" s="52" t="s">
-        <v>965</v>
+        <v>998</v>
       </c>
       <c r="D230" s="52" t="s">
-        <v>966</v>
+        <v>999</v>
       </c>
       <c r="E230" s="53"/>
       <c r="F230" s="53"/>
@@ -13152,16 +13373,16 @@
     </row>
     <row r="231">
       <c r="A231" s="56" t="s">
-        <v>967</v>
-      </c>
-      <c r="B231" s="55" t="s">
-        <v>968</v>
+        <v>1000</v>
+      </c>
+      <c r="B231" s="52" t="s">
+        <v>1001</v>
       </c>
       <c r="C231" s="52" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="D231" s="52" t="s">
-        <v>970</v>
+        <v>1003</v>
       </c>
       <c r="E231" s="53"/>
       <c r="F231" s="53"/>
@@ -13182,16 +13403,16 @@
     </row>
     <row r="232">
       <c r="A232" s="56" t="s">
-        <v>971</v>
+        <v>1004</v>
       </c>
       <c r="B232" s="52" t="s">
-        <v>972</v>
+        <v>1005</v>
       </c>
       <c r="C232" s="52" t="s">
-        <v>973</v>
+        <v>1006</v>
       </c>
       <c r="D232" s="52" t="s">
-        <v>974</v>
+        <v>1007</v>
       </c>
       <c r="E232" s="53"/>
       <c r="F232" s="53"/>
@@ -13212,16 +13433,16 @@
     </row>
     <row r="233">
       <c r="A233" s="56" t="s">
-        <v>975</v>
-      </c>
-      <c r="B233" s="52" t="s">
-        <v>976</v>
+        <v>1008</v>
+      </c>
+      <c r="B233" s="55" t="s">
+        <v>1009</v>
       </c>
       <c r="C233" s="52" t="s">
-        <v>977</v>
+        <v>1010</v>
       </c>
       <c r="D233" s="52" t="s">
-        <v>978</v>
+        <v>1011</v>
       </c>
       <c r="E233" s="53"/>
       <c r="F233" s="53"/>
@@ -13242,16 +13463,16 @@
     </row>
     <row r="234">
       <c r="A234" s="56" t="s">
-        <v>979</v>
+        <v>1012</v>
       </c>
       <c r="B234" s="52" t="s">
-        <v>980</v>
+        <v>1013</v>
       </c>
       <c r="C234" s="52" t="s">
-        <v>981</v>
+        <v>1014</v>
       </c>
       <c r="D234" s="52" t="s">
-        <v>982</v>
+        <v>1015</v>
       </c>
       <c r="E234" s="53"/>
       <c r="F234" s="53"/>
@@ -13272,16 +13493,16 @@
     </row>
     <row r="235">
       <c r="A235" s="56" t="s">
-        <v>983</v>
+        <v>1016</v>
       </c>
       <c r="B235" s="52" t="s">
-        <v>984</v>
+        <v>1017</v>
       </c>
       <c r="C235" s="52" t="s">
-        <v>985</v>
+        <v>1018</v>
       </c>
       <c r="D235" s="52" t="s">
-        <v>986</v>
+        <v>1019</v>
       </c>
       <c r="E235" s="53"/>
       <c r="F235" s="53"/>
@@ -13301,47 +13522,47 @@
       <c r="T235" s="54"/>
     </row>
     <row r="236">
-      <c r="A236" s="75" t="s">
-        <v>987</v>
-      </c>
-      <c r="B236" s="76" t="s">
-        <v>988</v>
-      </c>
-      <c r="C236" s="76" t="s">
-        <v>486</v>
-      </c>
-      <c r="D236" s="76" t="s">
-        <v>989</v>
-      </c>
-      <c r="E236" s="77"/>
-      <c r="F236" s="77"/>
-      <c r="G236" s="77"/>
-      <c r="H236" s="77"/>
-      <c r="I236" s="77"/>
-      <c r="J236" s="77"/>
-      <c r="K236" s="77"/>
-      <c r="L236" s="77"/>
-      <c r="M236" s="78"/>
-      <c r="N236" s="78"/>
-      <c r="O236" s="78"/>
-      <c r="P236" s="78"/>
-      <c r="Q236" s="78"/>
-      <c r="R236" s="78"/>
-      <c r="S236" s="78"/>
-      <c r="T236" s="78"/>
+      <c r="A236" s="56" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B236" s="52" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C236" s="52" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D236" s="52" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E236" s="53"/>
+      <c r="F236" s="53"/>
+      <c r="G236" s="53"/>
+      <c r="H236" s="53"/>
+      <c r="I236" s="53"/>
+      <c r="J236" s="53"/>
+      <c r="K236" s="53"/>
+      <c r="L236" s="53"/>
+      <c r="M236" s="54"/>
+      <c r="N236" s="54"/>
+      <c r="O236" s="54"/>
+      <c r="P236" s="54"/>
+      <c r="Q236" s="54"/>
+      <c r="R236" s="54"/>
+      <c r="S236" s="54"/>
+      <c r="T236" s="54"/>
     </row>
     <row r="237">
       <c r="A237" s="56" t="s">
-        <v>990</v>
+        <v>1024</v>
       </c>
       <c r="B237" s="52" t="s">
-        <v>991</v>
+        <v>1025</v>
       </c>
       <c r="C237" s="52" t="s">
-        <v>992</v>
+        <v>1026</v>
       </c>
       <c r="D237" s="52" t="s">
-        <v>993</v>
+        <v>1027</v>
       </c>
       <c r="E237" s="53"/>
       <c r="F237" s="53"/>
@@ -13361,47 +13582,47 @@
       <c r="T237" s="54"/>
     </row>
     <row r="238">
-      <c r="A238" s="56" t="s">
-        <v>994</v>
-      </c>
-      <c r="B238" s="52" t="s">
-        <v>497</v>
-      </c>
-      <c r="C238" s="52" t="s">
-        <v>498</v>
-      </c>
-      <c r="D238" s="52" t="s">
-        <v>499</v>
-      </c>
-      <c r="E238" s="53"/>
-      <c r="F238" s="53"/>
-      <c r="G238" s="53"/>
-      <c r="H238" s="53"/>
-      <c r="I238" s="53"/>
-      <c r="J238" s="53"/>
-      <c r="K238" s="53"/>
-      <c r="L238" s="53"/>
-      <c r="M238" s="54"/>
-      <c r="N238" s="54"/>
-      <c r="O238" s="54"/>
-      <c r="P238" s="54"/>
-      <c r="Q238" s="54"/>
-      <c r="R238" s="54"/>
-      <c r="S238" s="54"/>
-      <c r="T238" s="54"/>
+      <c r="A238" s="85" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B238" s="86" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C238" s="86" t="s">
+        <v>527</v>
+      </c>
+      <c r="D238" s="86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E238" s="79"/>
+      <c r="F238" s="79"/>
+      <c r="G238" s="79"/>
+      <c r="H238" s="79"/>
+      <c r="I238" s="79"/>
+      <c r="J238" s="79"/>
+      <c r="K238" s="79"/>
+      <c r="L238" s="79"/>
+      <c r="M238" s="80"/>
+      <c r="N238" s="80"/>
+      <c r="O238" s="80"/>
+      <c r="P238" s="80"/>
+      <c r="Q238" s="80"/>
+      <c r="R238" s="80"/>
+      <c r="S238" s="80"/>
+      <c r="T238" s="80"/>
     </row>
     <row r="239">
       <c r="A239" s="56" t="s">
-        <v>995</v>
+        <v>1031</v>
       </c>
       <c r="B239" s="52" t="s">
-        <v>497</v>
+        <v>1032</v>
       </c>
       <c r="C239" s="52" t="s">
-        <v>498</v>
+        <v>1033</v>
       </c>
       <c r="D239" s="52" t="s">
-        <v>499</v>
+        <v>1034</v>
       </c>
       <c r="E239" s="53"/>
       <c r="F239" s="53"/>
@@ -13422,16 +13643,16 @@
     </row>
     <row r="240">
       <c r="A240" s="56" t="s">
-        <v>996</v>
-      </c>
-      <c r="B240" s="55" t="s">
-        <v>997</v>
-      </c>
-      <c r="C240" s="55" t="s">
-        <v>998</v>
+        <v>1035</v>
+      </c>
+      <c r="B240" s="52" t="s">
+        <v>538</v>
+      </c>
+      <c r="C240" s="52" t="s">
+        <v>539</v>
       </c>
       <c r="D240" s="52" t="s">
-        <v>999</v>
+        <v>540</v>
       </c>
       <c r="E240" s="53"/>
       <c r="F240" s="53"/>
@@ -13452,16 +13673,16 @@
     </row>
     <row r="241">
       <c r="A241" s="56" t="s">
-        <v>1000</v>
+        <v>1036</v>
       </c>
       <c r="B241" s="52" t="s">
-        <v>1001</v>
+        <v>538</v>
       </c>
       <c r="C241" s="52" t="s">
-        <v>1001</v>
+        <v>539</v>
       </c>
       <c r="D241" s="52" t="s">
-        <v>1001</v>
+        <v>540</v>
       </c>
       <c r="E241" s="53"/>
       <c r="F241" s="53"/>
@@ -13481,45 +13702,47 @@
       <c r="T241" s="54"/>
     </row>
     <row r="242">
-      <c r="A242" s="79" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B242" s="80" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C242" s="74"/>
-      <c r="D242" s="80" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E242" s="81"/>
-      <c r="F242" s="81"/>
-      <c r="G242" s="81"/>
-      <c r="H242" s="81"/>
-      <c r="I242" s="81"/>
-      <c r="J242" s="81"/>
-      <c r="K242" s="81"/>
-      <c r="L242" s="81"/>
-      <c r="M242" s="82"/>
-      <c r="N242" s="82"/>
-      <c r="O242" s="82"/>
-      <c r="P242" s="82"/>
-      <c r="Q242" s="82"/>
-      <c r="R242" s="82"/>
-      <c r="S242" s="82"/>
-      <c r="T242" s="82"/>
+      <c r="A242" s="56" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B242" s="55" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C242" s="55" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D242" s="52" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E242" s="53"/>
+      <c r="F242" s="53"/>
+      <c r="G242" s="53"/>
+      <c r="H242" s="53"/>
+      <c r="I242" s="53"/>
+      <c r="J242" s="53"/>
+      <c r="K242" s="53"/>
+      <c r="L242" s="53"/>
+      <c r="M242" s="54"/>
+      <c r="N242" s="54"/>
+      <c r="O242" s="54"/>
+      <c r="P242" s="54"/>
+      <c r="Q242" s="54"/>
+      <c r="R242" s="54"/>
+      <c r="S242" s="54"/>
+      <c r="T242" s="54"/>
     </row>
     <row r="243">
       <c r="A243" s="56" t="s">
-        <v>1005</v>
+        <v>1041</v>
       </c>
       <c r="B243" s="52" t="s">
-        <v>1006</v>
+        <v>1042</v>
       </c>
       <c r="C243" s="52" t="s">
-        <v>1007</v>
+        <v>1042</v>
       </c>
       <c r="D243" s="52" t="s">
-        <v>1008</v>
+        <v>1042</v>
       </c>
       <c r="E243" s="53"/>
       <c r="F243" s="53"/>
@@ -13539,47 +13762,45 @@
       <c r="T243" s="54"/>
     </row>
     <row r="244">
-      <c r="A244" s="56" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B244" s="52" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C244" s="52" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D244" s="52" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E244" s="53"/>
-      <c r="F244" s="53"/>
-      <c r="G244" s="53"/>
-      <c r="H244" s="53"/>
-      <c r="I244" s="53"/>
-      <c r="J244" s="53"/>
-      <c r="K244" s="53"/>
-      <c r="L244" s="53"/>
-      <c r="M244" s="54"/>
-      <c r="N244" s="54"/>
-      <c r="O244" s="54"/>
-      <c r="P244" s="54"/>
-      <c r="Q244" s="54"/>
-      <c r="R244" s="54"/>
-      <c r="S244" s="54"/>
-      <c r="T244" s="54"/>
+      <c r="A244" s="87" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B244" s="88" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C244" s="84"/>
+      <c r="D244" s="88" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E244" s="89"/>
+      <c r="F244" s="89"/>
+      <c r="G244" s="89"/>
+      <c r="H244" s="89"/>
+      <c r="I244" s="89"/>
+      <c r="J244" s="89"/>
+      <c r="K244" s="89"/>
+      <c r="L244" s="89"/>
+      <c r="M244" s="90"/>
+      <c r="N244" s="90"/>
+      <c r="O244" s="90"/>
+      <c r="P244" s="90"/>
+      <c r="Q244" s="90"/>
+      <c r="R244" s="90"/>
+      <c r="S244" s="90"/>
+      <c r="T244" s="90"/>
     </row>
     <row r="245">
       <c r="A245" s="56" t="s">
-        <v>1013</v>
+        <v>1046</v>
       </c>
       <c r="B245" s="52" t="s">
-        <v>1014</v>
+        <v>1047</v>
       </c>
       <c r="C245" s="52" t="s">
-        <v>1015</v>
+        <v>1048</v>
       </c>
       <c r="D245" s="52" t="s">
-        <v>1016</v>
+        <v>1049</v>
       </c>
       <c r="E245" s="53"/>
       <c r="F245" s="53"/>
@@ -13600,16 +13821,16 @@
     </row>
     <row r="246">
       <c r="A246" s="56" t="s">
-        <v>1017</v>
+        <v>1050</v>
       </c>
       <c r="B246" s="52" t="s">
-        <v>1018</v>
+        <v>1051</v>
       </c>
       <c r="C246" s="52" t="s">
-        <v>1019</v>
+        <v>1052</v>
       </c>
       <c r="D246" s="52" t="s">
-        <v>1020</v>
+        <v>1053</v>
       </c>
       <c r="E246" s="53"/>
       <c r="F246" s="53"/>
@@ -13629,47 +13850,47 @@
       <c r="T246" s="54"/>
     </row>
     <row r="247">
-      <c r="A247" s="79" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B247" s="74" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C247" s="74" t="s">
-        <v>1023</v>
-      </c>
-      <c r="D247" s="80" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E247" s="81"/>
-      <c r="F247" s="81"/>
-      <c r="G247" s="81"/>
-      <c r="H247" s="81"/>
-      <c r="I247" s="81"/>
-      <c r="J247" s="81"/>
-      <c r="K247" s="81"/>
-      <c r="L247" s="81"/>
-      <c r="M247" s="82"/>
-      <c r="N247" s="82"/>
-      <c r="O247" s="82"/>
-      <c r="P247" s="82"/>
-      <c r="Q247" s="82"/>
-      <c r="R247" s="82"/>
-      <c r="S247" s="82"/>
-      <c r="T247" s="82"/>
+      <c r="A247" s="56" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B247" s="52" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C247" s="52" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D247" s="52" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E247" s="53"/>
+      <c r="F247" s="53"/>
+      <c r="G247" s="53"/>
+      <c r="H247" s="53"/>
+      <c r="I247" s="53"/>
+      <c r="J247" s="53"/>
+      <c r="K247" s="53"/>
+      <c r="L247" s="53"/>
+      <c r="M247" s="54"/>
+      <c r="N247" s="54"/>
+      <c r="O247" s="54"/>
+      <c r="P247" s="54"/>
+      <c r="Q247" s="54"/>
+      <c r="R247" s="54"/>
+      <c r="S247" s="54"/>
+      <c r="T247" s="54"/>
     </row>
     <row r="248">
       <c r="A248" s="56" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B248" s="83" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C248" s="74" t="s">
-        <v>1027</v>
+        <v>1058</v>
+      </c>
+      <c r="B248" s="52" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C248" s="52" t="s">
+        <v>1060</v>
       </c>
       <c r="D248" s="52" t="s">
-        <v>1028</v>
+        <v>1061</v>
       </c>
       <c r="E248" s="53"/>
       <c r="F248" s="53"/>
@@ -13689,171 +13910,171 @@
       <c r="T248" s="54"/>
     </row>
     <row r="249">
-      <c r="A249" s="56" t="s">
-        <v>1029</v>
+      <c r="A249" s="87" t="s">
+        <v>1062</v>
       </c>
       <c r="B249" s="84" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C249" s="85" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D249" s="86" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E249" s="87" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F249" s="53"/>
-      <c r="G249" s="53"/>
-      <c r="H249" s="53"/>
-      <c r="I249" s="53"/>
-      <c r="J249" s="53"/>
-      <c r="K249" s="53"/>
-      <c r="L249" s="53"/>
-      <c r="M249" s="54"/>
-      <c r="N249" s="54"/>
-      <c r="O249" s="54"/>
-      <c r="P249" s="54"/>
-      <c r="Q249" s="54"/>
-      <c r="R249" s="54"/>
-      <c r="S249" s="54"/>
-      <c r="T249" s="54"/>
-    </row>
-    <row customHeight="true" ht="16" r="250">
-      <c r="A250" s="88" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B250" s="84" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C250" s="85" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D250" s="86" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E250" s="87" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F250" s="89"/>
-      <c r="G250" s="89"/>
-      <c r="H250" s="89"/>
-      <c r="I250" s="89"/>
-      <c r="J250" s="89"/>
-      <c r="K250" s="89"/>
-      <c r="L250" s="89"/>
-      <c r="M250" s="90"/>
-      <c r="N250" s="90"/>
-      <c r="O250" s="90"/>
-      <c r="P250" s="90"/>
-      <c r="Q250" s="90"/>
-      <c r="R250" s="90"/>
-      <c r="S250" s="90"/>
-      <c r="T250" s="90"/>
-    </row>
-    <row customHeight="true" ht="16" r="251">
-      <c r="A251" s="88" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B251" s="91" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C251" s="85" t="s">
-        <v>1038</v>
+        <v>1063</v>
+      </c>
+      <c r="C249" s="84" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D249" s="88" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E249" s="89"/>
+      <c r="F249" s="89"/>
+      <c r="G249" s="89"/>
+      <c r="H249" s="89"/>
+      <c r="I249" s="89"/>
+      <c r="J249" s="89"/>
+      <c r="K249" s="89"/>
+      <c r="L249" s="89"/>
+      <c r="M249" s="90"/>
+      <c r="N249" s="90"/>
+      <c r="O249" s="90"/>
+      <c r="P249" s="90"/>
+      <c r="Q249" s="90"/>
+      <c r="R249" s="90"/>
+      <c r="S249" s="90"/>
+      <c r="T249" s="90"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="56" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B250" s="91" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C250" s="84" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D250" s="52" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E250" s="53"/>
+      <c r="F250" s="53"/>
+      <c r="G250" s="53"/>
+      <c r="H250" s="53"/>
+      <c r="I250" s="53"/>
+      <c r="J250" s="53"/>
+      <c r="K250" s="53"/>
+      <c r="L250" s="53"/>
+      <c r="M250" s="54"/>
+      <c r="N250" s="54"/>
+      <c r="O250" s="54"/>
+      <c r="P250" s="54"/>
+      <c r="Q250" s="54"/>
+      <c r="R250" s="54"/>
+      <c r="S250" s="54"/>
+      <c r="T250" s="54"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="85" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B251" s="92" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C251" s="93" t="s">
+        <v>1072</v>
       </c>
       <c r="D251" s="86" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E251" s="87"/>
-      <c r="F251" s="89"/>
-      <c r="G251" s="89"/>
-      <c r="H251" s="89"/>
-      <c r="I251" s="89"/>
-      <c r="J251" s="89"/>
-      <c r="K251" s="89"/>
-      <c r="L251" s="89"/>
-      <c r="M251" s="90"/>
-      <c r="N251" s="90"/>
-      <c r="O251" s="90"/>
-      <c r="P251" s="90"/>
-      <c r="Q251" s="90"/>
-      <c r="R251" s="90"/>
-      <c r="S251" s="90"/>
-      <c r="T251" s="90"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="56" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B252" s="83" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C252" s="85" t="s">
-        <v>1042</v>
-      </c>
-      <c r="D252" s="66" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E252" s="53"/>
-      <c r="F252" s="53"/>
-      <c r="G252" s="53"/>
-      <c r="H252" s="53"/>
-      <c r="I252" s="53"/>
-      <c r="J252" s="53"/>
-      <c r="K252" s="53"/>
-      <c r="L252" s="53"/>
-      <c r="M252" s="54"/>
-      <c r="N252" s="54"/>
-      <c r="O252" s="54"/>
-      <c r="P252" s="54"/>
-      <c r="Q252" s="54"/>
-      <c r="R252" s="54"/>
-      <c r="S252" s="54"/>
-      <c r="T252" s="54"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="56" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B253" s="83" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C253" s="74" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D253" s="52" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E253" s="53"/>
-      <c r="F253" s="53"/>
-      <c r="G253" s="53"/>
-      <c r="H253" s="53"/>
-      <c r="I253" s="53"/>
-      <c r="J253" s="53"/>
-      <c r="K253" s="53"/>
-      <c r="L253" s="53"/>
-      <c r="M253" s="54"/>
-      <c r="N253" s="54"/>
-      <c r="O253" s="54"/>
-      <c r="P253" s="54"/>
-      <c r="Q253" s="54"/>
-      <c r="R253" s="54"/>
-      <c r="S253" s="54"/>
-      <c r="T253" s="54"/>
+        <v>1073</v>
+      </c>
+      <c r="E251" s="94" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F251" s="79"/>
+      <c r="G251" s="79"/>
+      <c r="H251" s="79"/>
+      <c r="I251" s="79"/>
+      <c r="J251" s="79"/>
+      <c r="K251" s="79"/>
+      <c r="L251" s="79"/>
+      <c r="M251" s="80"/>
+      <c r="N251" s="80"/>
+      <c r="O251" s="80"/>
+      <c r="P251" s="80"/>
+      <c r="Q251" s="80"/>
+      <c r="R251" s="80"/>
+      <c r="S251" s="80"/>
+      <c r="T251" s="80"/>
+    </row>
+    <row customHeight="true" ht="16" r="252">
+      <c r="A252" s="95" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B252" s="92" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C252" s="93" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D252" s="86" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E252" s="94" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F252" s="79"/>
+      <c r="G252" s="79"/>
+      <c r="H252" s="79"/>
+      <c r="I252" s="79"/>
+      <c r="J252" s="79"/>
+      <c r="K252" s="79"/>
+      <c r="L252" s="79"/>
+      <c r="M252" s="80"/>
+      <c r="N252" s="80"/>
+      <c r="O252" s="80"/>
+      <c r="P252" s="80"/>
+      <c r="Q252" s="80"/>
+      <c r="R252" s="80"/>
+      <c r="S252" s="80"/>
+      <c r="T252" s="80"/>
+    </row>
+    <row customHeight="true" ht="16" r="253">
+      <c r="A253" s="95" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B253" s="96" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C253" s="93" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D253" s="86" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E253" s="94"/>
+      <c r="F253" s="79"/>
+      <c r="G253" s="79"/>
+      <c r="H253" s="79"/>
+      <c r="I253" s="79"/>
+      <c r="J253" s="79"/>
+      <c r="K253" s="79"/>
+      <c r="L253" s="79"/>
+      <c r="M253" s="80"/>
+      <c r="N253" s="80"/>
+      <c r="O253" s="80"/>
+      <c r="P253" s="80"/>
+      <c r="Q253" s="80"/>
+      <c r="R253" s="80"/>
+      <c r="S253" s="80"/>
+      <c r="T253" s="80"/>
     </row>
     <row r="254">
       <c r="A254" s="56" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B254" s="83" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C254" s="74" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D254" s="66" t="s">
-        <v>1051</v>
+        <v>1081</v>
+      </c>
+      <c r="B254" s="91" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C254" s="84" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D254" s="55" t="s">
+        <v>1084</v>
       </c>
       <c r="E254" s="53"/>
       <c r="F254" s="53"/>
@@ -13874,16 +14095,16 @@
     </row>
     <row r="255">
       <c r="A255" s="56" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B255" s="83" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C255" s="74" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D255" s="66" t="s">
-        <v>1055</v>
+        <v>1085</v>
+      </c>
+      <c r="B255" s="91" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C255" s="84" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D255" s="52" t="s">
+        <v>1088</v>
       </c>
       <c r="E255" s="53"/>
       <c r="F255" s="53"/>
@@ -13903,137 +14124,137 @@
       <c r="T255" s="54"/>
     </row>
     <row r="256">
-      <c r="A256" s="79" t="s">
-        <v>1056</v>
-      </c>
-      <c r="B256" s="83" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C256" s="74" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D256" s="80" t="s">
-        <v>1059</v>
-      </c>
-      <c r="E256" s="81"/>
-      <c r="F256" s="81"/>
-      <c r="G256" s="81"/>
-      <c r="H256" s="81"/>
-      <c r="I256" s="81"/>
-      <c r="J256" s="81"/>
-      <c r="K256" s="81"/>
-      <c r="L256" s="81"/>
-      <c r="M256" s="82"/>
-      <c r="N256" s="82"/>
-      <c r="O256" s="82"/>
-      <c r="P256" s="82"/>
-      <c r="Q256" s="82"/>
-      <c r="R256" s="82"/>
-      <c r="S256" s="82"/>
-      <c r="T256" s="82"/>
+      <c r="A256" s="56" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B256" s="91" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C256" s="84" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D256" s="55" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E256" s="53"/>
+      <c r="F256" s="53"/>
+      <c r="G256" s="53"/>
+      <c r="H256" s="53"/>
+      <c r="I256" s="53"/>
+      <c r="J256" s="53"/>
+      <c r="K256" s="53"/>
+      <c r="L256" s="53"/>
+      <c r="M256" s="54"/>
+      <c r="N256" s="54"/>
+      <c r="O256" s="54"/>
+      <c r="P256" s="54"/>
+      <c r="Q256" s="54"/>
+      <c r="R256" s="54"/>
+      <c r="S256" s="54"/>
+      <c r="T256" s="54"/>
     </row>
     <row r="257">
-      <c r="A257" s="79" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B257" s="83" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C257" s="74" t="s">
-        <v>1062</v>
-      </c>
-      <c r="D257" s="80" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E257" s="81"/>
-      <c r="F257" s="81"/>
-      <c r="G257" s="81"/>
-      <c r="H257" s="81"/>
-      <c r="I257" s="81"/>
-      <c r="J257" s="81"/>
-      <c r="K257" s="81"/>
-      <c r="L257" s="81"/>
-      <c r="M257" s="82"/>
-      <c r="N257" s="82"/>
-      <c r="O257" s="82"/>
-      <c r="P257" s="82"/>
-      <c r="Q257" s="82"/>
-      <c r="R257" s="82"/>
-      <c r="S257" s="82"/>
-      <c r="T257" s="82"/>
+      <c r="A257" s="56" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B257" s="91" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C257" s="84" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D257" s="55" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E257" s="53"/>
+      <c r="F257" s="53"/>
+      <c r="G257" s="53"/>
+      <c r="H257" s="53"/>
+      <c r="I257" s="53"/>
+      <c r="J257" s="53"/>
+      <c r="K257" s="53"/>
+      <c r="L257" s="53"/>
+      <c r="M257" s="54"/>
+      <c r="N257" s="54"/>
+      <c r="O257" s="54"/>
+      <c r="P257" s="54"/>
+      <c r="Q257" s="54"/>
+      <c r="R257" s="54"/>
+      <c r="S257" s="54"/>
+      <c r="T257" s="54"/>
     </row>
     <row r="258">
-      <c r="A258" s="56" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B258" s="83" t="s">
-        <v>1065</v>
-      </c>
-      <c r="C258" s="85" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D258" s="52" t="s">
-        <v>1067</v>
-      </c>
-      <c r="E258" s="53"/>
-      <c r="F258" s="53"/>
-      <c r="G258" s="53"/>
-      <c r="H258" s="53"/>
-      <c r="I258" s="53"/>
-      <c r="J258" s="53"/>
-      <c r="K258" s="53"/>
-      <c r="L258" s="53"/>
-      <c r="M258" s="54"/>
-      <c r="N258" s="54"/>
-      <c r="O258" s="54"/>
-      <c r="P258" s="54"/>
-      <c r="Q258" s="54"/>
-      <c r="R258" s="54"/>
-      <c r="S258" s="54"/>
-      <c r="T258" s="54"/>
+      <c r="A258" s="87" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B258" s="91" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C258" s="84" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D258" s="88" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E258" s="89"/>
+      <c r="F258" s="89"/>
+      <c r="G258" s="89"/>
+      <c r="H258" s="89"/>
+      <c r="I258" s="89"/>
+      <c r="J258" s="89"/>
+      <c r="K258" s="89"/>
+      <c r="L258" s="89"/>
+      <c r="M258" s="90"/>
+      <c r="N258" s="90"/>
+      <c r="O258" s="90"/>
+      <c r="P258" s="90"/>
+      <c r="Q258" s="90"/>
+      <c r="R258" s="90"/>
+      <c r="S258" s="90"/>
+      <c r="T258" s="90"/>
     </row>
     <row r="259">
-      <c r="A259" s="56" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B259" s="83" t="s">
-        <v>1069</v>
-      </c>
-      <c r="C259" s="85" t="s">
-        <v>1070</v>
-      </c>
-      <c r="D259" s="52" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E259" s="53"/>
-      <c r="F259" s="53"/>
-      <c r="G259" s="53"/>
-      <c r="H259" s="53"/>
-      <c r="I259" s="53"/>
-      <c r="J259" s="53"/>
-      <c r="K259" s="53"/>
-      <c r="L259" s="53"/>
-      <c r="M259" s="54"/>
-      <c r="N259" s="54"/>
-      <c r="O259" s="54"/>
-      <c r="P259" s="54"/>
-      <c r="Q259" s="54"/>
-      <c r="R259" s="54"/>
-      <c r="S259" s="54"/>
-      <c r="T259" s="54"/>
+      <c r="A259" s="87" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B259" s="91" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C259" s="84" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D259" s="88" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E259" s="89"/>
+      <c r="F259" s="89"/>
+      <c r="G259" s="89"/>
+      <c r="H259" s="89"/>
+      <c r="I259" s="89"/>
+      <c r="J259" s="89"/>
+      <c r="K259" s="89"/>
+      <c r="L259" s="89"/>
+      <c r="M259" s="90"/>
+      <c r="N259" s="90"/>
+      <c r="O259" s="90"/>
+      <c r="P259" s="90"/>
+      <c r="Q259" s="90"/>
+      <c r="R259" s="90"/>
+      <c r="S259" s="90"/>
+      <c r="T259" s="90"/>
     </row>
     <row r="260">
       <c r="A260" s="56" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B260" s="83" t="s">
-        <v>1073</v>
-      </c>
-      <c r="C260" s="80" t="s">
-        <v>1074</v>
+        <v>1105</v>
+      </c>
+      <c r="B260" s="91" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C260" s="84" t="s">
+        <v>1107</v>
       </c>
       <c r="D260" s="52" t="s">
-        <v>1075</v>
+        <v>1108</v>
       </c>
       <c r="E260" s="53"/>
       <c r="F260" s="53"/>
@@ -14054,16 +14275,16 @@
     </row>
     <row r="261">
       <c r="A261" s="56" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B261" s="83" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C261" s="74" t="s">
-        <v>1078</v>
+        <v>1109</v>
+      </c>
+      <c r="B261" s="91" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C261" s="84" t="s">
+        <v>1111</v>
       </c>
       <c r="D261" s="52" t="s">
-        <v>1079</v>
+        <v>1112</v>
       </c>
       <c r="E261" s="53"/>
       <c r="F261" s="53"/>
@@ -14084,16 +14305,16 @@
     </row>
     <row r="262">
       <c r="A262" s="56" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B262" s="83" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C262" s="74" t="s">
-        <v>1082</v>
+        <v>1113</v>
+      </c>
+      <c r="B262" s="91" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C262" s="88" t="s">
+        <v>1115</v>
       </c>
       <c r="D262" s="52" t="s">
-        <v>1083</v>
+        <v>1116</v>
       </c>
       <c r="E262" s="53"/>
       <c r="F262" s="53"/>
@@ -14114,16 +14335,16 @@
     </row>
     <row r="263">
       <c r="A263" s="56" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B263" s="83" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C263" s="74" t="s">
-        <v>1086</v>
+        <v>1117</v>
+      </c>
+      <c r="B263" s="91" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C263" s="84" t="s">
+        <v>1119</v>
       </c>
       <c r="D263" s="52" t="s">
-        <v>1087</v>
+        <v>1120</v>
       </c>
       <c r="E263" s="53"/>
       <c r="F263" s="53"/>
@@ -14144,16 +14365,16 @@
     </row>
     <row r="264">
       <c r="A264" s="56" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B264" s="83" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C264" s="74" t="s">
-        <v>1090</v>
+        <v>1121</v>
+      </c>
+      <c r="B264" s="91" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C264" s="84" t="s">
+        <v>1123</v>
       </c>
       <c r="D264" s="52" t="s">
-        <v>1091</v>
+        <v>1124</v>
       </c>
       <c r="E264" s="53"/>
       <c r="F264" s="53"/>
@@ -14172,52 +14393,50 @@
       <c r="S264" s="54"/>
       <c r="T264" s="54"/>
     </row>
-    <row customHeight="true" ht="27" r="265">
-      <c r="A265" s="75" t="s">
-        <v>1092</v>
-      </c>
-      <c r="B265" s="76" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C265" s="92" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D265" s="86" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E265" s="77"/>
-      <c r="F265" s="77"/>
-      <c r="G265" s="77"/>
-      <c r="H265" s="77"/>
-      <c r="I265" s="77"/>
-      <c r="J265" s="77"/>
-      <c r="K265" s="77"/>
-      <c r="L265" s="77"/>
-      <c r="M265" s="78"/>
-      <c r="N265" s="78"/>
-      <c r="O265" s="78"/>
-      <c r="P265" s="78"/>
-      <c r="Q265" s="78"/>
-      <c r="R265" s="78"/>
-      <c r="S265" s="78"/>
-      <c r="T265" s="78"/>
+    <row r="265">
+      <c r="A265" s="56" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B265" s="91" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C265" s="84" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D265" s="52" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E265" s="53"/>
+      <c r="F265" s="53"/>
+      <c r="G265" s="53"/>
+      <c r="H265" s="53"/>
+      <c r="I265" s="53"/>
+      <c r="J265" s="53"/>
+      <c r="K265" s="53"/>
+      <c r="L265" s="53"/>
+      <c r="M265" s="54"/>
+      <c r="N265" s="54"/>
+      <c r="O265" s="54"/>
+      <c r="P265" s="54"/>
+      <c r="Q265" s="54"/>
+      <c r="R265" s="54"/>
+      <c r="S265" s="54"/>
+      <c r="T265" s="54"/>
     </row>
     <row r="266">
       <c r="A266" s="56" t="s">
-        <v>1096</v>
-      </c>
-      <c r="B266" s="52" t="s">
-        <v>1097</v>
-      </c>
-      <c r="C266" s="52" t="s">
-        <v>1098</v>
+        <v>1129</v>
+      </c>
+      <c r="B266" s="91" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C266" s="84" t="s">
+        <v>1131</v>
       </c>
       <c r="D266" s="52" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E266" s="93" t="s">
-        <v>1100</v>
-      </c>
+        <v>1132</v>
+      </c>
+      <c r="E266" s="53"/>
       <c r="F266" s="53"/>
       <c r="G266" s="53"/>
       <c r="H266" s="53"/>
@@ -14234,50 +14453,52 @@
       <c r="S266" s="54"/>
       <c r="T266" s="54"/>
     </row>
-    <row r="267">
-      <c r="A267" s="56" t="s">
-        <v>1101</v>
-      </c>
-      <c r="B267" s="52" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C267" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="D267" s="52" t="s">
-        <v>1103</v>
-      </c>
-      <c r="E267" s="53"/>
-      <c r="F267" s="53"/>
-      <c r="G267" s="53"/>
-      <c r="H267" s="53"/>
-      <c r="I267" s="53"/>
-      <c r="J267" s="53"/>
-      <c r="K267" s="53"/>
-      <c r="L267" s="53"/>
-      <c r="M267" s="54"/>
-      <c r="N267" s="54"/>
-      <c r="O267" s="54"/>
-      <c r="P267" s="54"/>
-      <c r="Q267" s="54"/>
-      <c r="R267" s="54"/>
-      <c r="S267" s="54"/>
-      <c r="T267" s="54"/>
+    <row customHeight="true" ht="27" r="267">
+      <c r="A267" s="85" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B267" s="86" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C267" s="93" t="s">
+        <v>1135</v>
+      </c>
+      <c r="D267" s="86" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E267" s="79"/>
+      <c r="F267" s="79"/>
+      <c r="G267" s="79"/>
+      <c r="H267" s="79"/>
+      <c r="I267" s="79"/>
+      <c r="J267" s="79"/>
+      <c r="K267" s="79"/>
+      <c r="L267" s="79"/>
+      <c r="M267" s="80"/>
+      <c r="N267" s="80"/>
+      <c r="O267" s="80"/>
+      <c r="P267" s="80"/>
+      <c r="Q267" s="80"/>
+      <c r="R267" s="80"/>
+      <c r="S267" s="80"/>
+      <c r="T267" s="80"/>
     </row>
     <row r="268">
       <c r="A268" s="56" t="s">
-        <v>1104</v>
+        <v>1137</v>
       </c>
       <c r="B268" s="52" t="s">
-        <v>1093</v>
+        <v>1138</v>
       </c>
       <c r="C268" s="52" t="s">
-        <v>1105</v>
+        <v>1139</v>
       </c>
       <c r="D268" s="52" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E268" s="53"/>
+        <v>1140</v>
+      </c>
+      <c r="E268" s="97" t="s">
+        <v>1141</v>
+      </c>
       <c r="F268" s="53"/>
       <c r="G268" s="53"/>
       <c r="H268" s="53"/>
@@ -14296,16 +14517,16 @@
     </row>
     <row r="269">
       <c r="A269" s="56" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B269" s="55" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C269" s="55" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D269" s="94" t="s">
-        <v>1103</v>
+        <v>1142</v>
+      </c>
+      <c r="B269" s="52" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C269" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D269" s="52" t="s">
+        <v>1144</v>
       </c>
       <c r="E269" s="53"/>
       <c r="F269" s="53"/>
@@ -14324,8 +14545,69 @@
       <c r="S269" s="54"/>
       <c r="T269" s="54"/>
     </row>
+    <row r="270">
+      <c r="A270" s="56" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B270" s="52" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C270" s="52" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D270" s="52" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E270" s="53"/>
+      <c r="F270" s="53"/>
+      <c r="G270" s="53"/>
+      <c r="H270" s="53"/>
+      <c r="I270" s="53"/>
+      <c r="J270" s="53"/>
+      <c r="K270" s="53"/>
+      <c r="L270" s="53"/>
+      <c r="M270" s="54"/>
+      <c r="N270" s="54"/>
+      <c r="O270" s="54"/>
+      <c r="P270" s="54"/>
+      <c r="Q270" s="54"/>
+      <c r="R270" s="54"/>
+      <c r="S270" s="54"/>
+      <c r="T270" s="54"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="56" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B271" s="55" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C271" s="55" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D271" s="72" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E271" s="53"/>
+      <c r="F271" s="53"/>
+      <c r="G271" s="53"/>
+      <c r="H271" s="53"/>
+      <c r="I271" s="53"/>
+      <c r="J271" s="53"/>
+      <c r="K271" s="53"/>
+      <c r="L271" s="53"/>
+      <c r="M271" s="54"/>
+      <c r="N271" s="54"/>
+      <c r="O271" s="54"/>
+      <c r="P271" s="54"/>
+      <c r="Q271" s="54"/>
+      <c r="R271" s="54"/>
+      <c r="S271" s="54"/>
+      <c r="T271" s="54"/>
+    </row>
   </sheetData>
   <mergeCells>
+    <mergeCell ref="B114:D114"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="F24:H24"/>
@@ -14346,7 +14628,6 @@
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B114:D114"/>
   </mergeCells>
 </worksheet>
 </file>